--- a/manuscript/Supplementary-Table-3.xlsx
+++ b/manuscript/Supplementary-Table-3.xlsx
@@ -17,9 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0000000000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -106,7 +107,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -501,7 +502,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Values are WT-referenced MM/GBSA energetic shifts for doravirine-bound RT variants, reported in kJ/mol. For each mutant replicate, the energetic component from that replicate was compared with the corresponding WT replicate, so shifts are calculated as mutant minus matched WT.</t>
+          <t>Values are WT-referenced MM/GBSA energetic shifts for doravirine-bound RT variants, reported in kcal/mol. Each mutant replicate is referenced to the mean of the three WT production replicates, so shifts are calculated as mutant replicate minus the WT replicate mean. This unmatched reference replaces an earlier replicate-index-matched pairing, under which a single outlying WT trajectory propagated a common offset into every mutant.</t>
         </is>
       </c>
     </row>
@@ -515,7 +516,14 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Summary values are the mean across three independent production replicates. SEM is the sample standard deviation divided by the square root of the number of replicates. Positive shifts indicate a less favorable energetic score relative to WT, whereas negative shifts indicate a more favorable score.</t>
+          <t>Summary values are the mean across three independent production replicates. SEM is the sample standard deviation of the mutant replicates divided by the square root of the number of replicates; it reflects mutant-replicate spread only. The uncertainty of the WT reference itself is a common offset shared by every mutation and is reported separately in the note below. Positive shifts indicate a less favorable energetic score relative to WT, whereas negative shifts indicate a more favorable score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>WT reference (mean +/- SEM over three WT production replicates, kcal/mol): total -15.9 +/- 22.0; van der Waals -45.1 +/- 19.8; electrostatic -5.4 +/- 0.8; GB polar solvation 35.2 +/- 1.8; nonpolar SA -0.5 +/- 0.0. These reference uncertainties are common to every row and are not included in the per-mutation SEM values above.</t>
         </is>
       </c>
     </row>
@@ -537,52 +545,52 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Total shift mean (kJ/mol)</t>
+          <t>Total shift mean (kcal/mol)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Total shift SEM (kJ/mol)</t>
+          <t>Total shift SEM (kcal/mol)</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>van der Waals shift mean (kJ/mol)</t>
+          <t>van der Waals shift mean (kcal/mol)</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>van der Waals shift SEM (kJ/mol)</t>
+          <t>van der Waals shift SEM (kcal/mol)</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Electrostatic shift mean (kJ/mol)</t>
+          <t>Electrostatic shift mean (kcal/mol)</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Electrostatic shift SEM (kJ/mol)</t>
+          <t>Electrostatic shift SEM (kcal/mol)</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>GB polar solvation shift mean (kJ/mol)</t>
+          <t>GB polar solvation shift mean (kcal/mol)</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>GB polar solvation shift SEM (kJ/mol)</t>
+          <t>GB polar solvation shift SEM (kcal/mol)</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Nonpolar SA shift mean (kJ/mol)</t>
+          <t>Nonpolar SA shift mean (kcal/mol)</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Nonpolar SA shift SEM (kJ/mol)</t>
+          <t>Nonpolar SA shift SEM (kcal/mol)</t>
         </is>
       </c>
     </row>
@@ -599,34 +607,34 @@
         <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-77.53219793637594</v>
+        <v>-18.53064004215486</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>92.85988068830949</v>
+        <v>0.3052085291463392</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-67.75156545639035</v>
+        <v>-16.19301277638393</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>84.1815570347664</v>
+        <v>2.16629130737256</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>2.083657646179201</v>
+        <v>0.4980061295839381</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>3.900476690556868</v>
+        <v>0.4642236465579634</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-11.82117462158202</v>
+        <v>-2.825328542443122</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>11.54507425806373</v>
+        <v>1.807008353428545</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>-0.04311550458272283</v>
+        <v>-0.0103048529117406</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.01317055699239958</v>
+        <v>0.001769652766679508</v>
       </c>
     </row>
     <row r="9">
@@ -642,34 +650,34 @@
         <v>3</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>39.52772559920947</v>
+        <v>9.447353154686773</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>102.4870504100171</v>
+        <v>12.32134344256269</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>24.87805011272431</v>
+        <v>5.945996680861448</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>105.3525127342957</v>
+        <v>14.95388723210101</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-7.874788093566894</v>
+        <v>-1.882119525231094</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>3.284351003144139</v>
+        <v>0.0605810247461519</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>22.52523724238079</v>
+        <v>5.383660908790818</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>11.37860412058413</v>
+        <v>2.849377298932321</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>-0.0007736623287200999</v>
+        <v>-0.0001849097343978055</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.01336312849761125</v>
+        <v>0.003023933314929601</v>
       </c>
     </row>
     <row r="10">
@@ -685,34 +693,34 @@
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>-5.366245188315712</v>
+        <v>-1.282563381528613</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>78.84639768439062</v>
+        <v>4.850544495975907</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-19.25739544232684</v>
+        <v>-4.602627973787484</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>66.65450601839584</v>
+        <v>4.430120418342435</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-2.45225798288981</v>
+        <v>-0.5861037244000515</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>4.293416348293139</v>
+        <v>0.1970587936575455</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>16.37222506205241</v>
+        <v>3.913055703167402</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>9.830763478890963</v>
+        <v>1.244520031452134</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>-0.02881682515144343</v>
+        <v>-0.006887386508471233</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.01141235607406957</v>
+        <v>0.0009125816396584528</v>
       </c>
     </row>
     <row r="11">
@@ -728,34 +736,34 @@
         <v>3</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-22.30538145105045</v>
+        <v>-5.331114113539781</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>121.9998624095333</v>
+        <v>11.55269835830883</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-31.59671324094134</v>
+        <v>-7.551795707681968</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>110.2143651901507</v>
+        <v>10.46415712516516</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1.857144927978516</v>
+        <v>0.4438682906258394</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>3.892251553735675</v>
+        <v>0.2312078762700519</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>7.460527960459387</v>
+        <v>1.783108977165246</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>12.19883542709392</v>
+        <v>1.34251639933909</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>-0.0263410985469815</v>
+        <v>-0.006295673648896101</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.009169529556803427</v>
+        <v>0.001548003749072663</v>
       </c>
     </row>
     <row r="12">
@@ -771,34 +779,34 @@
         <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>14.84354466597241</v>
+        <v>3.547692319783079</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>159.7908454299815</v>
+        <v>22.17089552634157</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>22.51233127117159</v>
+        <v>5.380576307641394</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>153.426853856583</v>
+        <v>22.73703606109118</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>1.317354265848796</v>
+        <v>0.3148552260632873</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>6.013535070626641</v>
+        <v>0.8224836407232284</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-8.966037750244141</v>
+        <v>-2.142934452735216</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>7.086752385293875</v>
+        <v>0.9802124465167977</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>-0.0201031208038329</v>
+        <v>-0.004804761186384566</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.03348531260440377</v>
+        <v>0.005851361743682877</v>
       </c>
     </row>
     <row r="13">
@@ -814,34 +822,34 @@
         <v>3</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>37.75927385290463</v>
+        <v>9.024683043237241</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>130.2597550475714</v>
+        <v>15.57780727423912</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>22.30692316691082</v>
+        <v>5.331482592473904</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>116.3339660936193</v>
+        <v>15.06687339724153</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>12.82599519093831</v>
+        <v>3.065486422308392</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.177411699502473</v>
+        <v>0.8275715675517433</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>2.629655202229799</v>
+        <v>0.6285026773971795</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>12.89321276611253</v>
+        <v>1.341850505986341</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>-0.003299707174300932</v>
+        <v>-0.0007886489422325336</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.03287336628707392</v>
+        <v>0.005650519590938755</v>
       </c>
     </row>
     <row r="14">
@@ -857,34 +865,34 @@
         <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-75.37834496498108</v>
+        <v>-18.01585682719433</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>93.84750080385579</v>
+        <v>0.5616339829699335</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-82.61451808611551</v>
+        <v>-19.74534371083067</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>82.82488788505309</v>
+        <v>0.7201328023198564</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-10.6331392288208</v>
+        <v>-2.541381268838624</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>7.01102236007944</v>
+        <v>0.837434745639805</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>17.90875517527262</v>
+        <v>4.280295213975291</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>8.385301222087126</v>
+        <v>0.4028663081073544</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>-0.03944282531738253</v>
+        <v>-0.009427061500330401</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.009936452137543314</v>
+        <v>0.002570592154330198</v>
       </c>
     </row>
     <row r="15">
@@ -900,34 +908,34 @@
         <v>3</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>-23.96395051081976</v>
+        <v>-5.727521632605104</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>103.4914899937684</v>
+        <v>3.769209160657442</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-61.46148344675698</v>
+        <v>-14.6896470953052</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>94.76269858807457</v>
+        <v>4.806119109554944</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-2.387668164571126</v>
+        <v>-0.5706663873257954</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>7.780910557104107</v>
+        <v>1.075926312132978</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>39.91046619415285</v>
+        <v>9.538830352330988</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>5.524643977619586</v>
+        <v>1.102439115779775</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>-0.02526509364445984</v>
+        <v>-0.006038502305081233</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.003112799651070459</v>
+        <v>0.002927099307363788</v>
       </c>
     </row>
     <row r="16">
@@ -943,163 +951,163 @@
         <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>140.6434633453687</v>
+        <v>33.61459448981088</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>85.67292549484524</v>
+        <v>24.39623161790478</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>90.33328903516134</v>
+        <v>21.59017424358541</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>68.94554371928783</v>
+        <v>20.71661127300783</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>4.624990717569988</v>
+        <v>1.105399311082692</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>2.176136905071338</v>
+        <v>1.25870218348284</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>45.68925387064616</v>
+        <v>10.91999375493455</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>17.14383821837629</v>
+        <v>3.398328508262209</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>-0.004070278008778835</v>
+        <v>-0.0009728197917731335</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.02439176585794589</v>
+        <v>0.004085022874878571</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>K103N+M230L</t>
+          <t>V106A</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>83.26117935379347</v>
+        <v>-14.92594222379688</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>40.49634238995277</v>
+        <v>1.63615323358498</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>72.49198048909507</v>
+        <v>-17.51163737115926</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>40.87543932796971</v>
+        <v>0.3864435086392278</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-8.714505322774249</v>
+        <v>-0.3876943965107117</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>6.408934480331977</v>
+        <v>0.09401933580897835</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>19.48961807886759</v>
+        <v>2.977884248839281</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>2.898535089922663</v>
+        <v>1.465589305860082</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>-0.005913891394932767</v>
+        <v>-0.0044947049661834</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.003847595762244949</v>
+        <v>0.002724143766172271</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>V106A</t>
+          <t>Y318F</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>-62.45014226436613</v>
+        <v>8.808845613529302</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>98.14408795748484</v>
+        <v>24.20917910321731</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>-73.26869076093037</v>
+        <v>7.255964834003255</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>83.21904531502091</v>
+        <v>20.0579645499284</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-1.622113355000814</v>
+        <v>0.1944672157234109</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>3.141191710050221</v>
+        <v>1.104005604726207</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>12.45946769714356</v>
+        <v>1.352592499260689</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>13.67550214990468</v>
+        <v>3.524144284890388</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>-0.01880584557851143</v>
+        <v>0.005821064541946134</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.003448871470803951</v>
+        <v>0.005026435812242096</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Y318F</t>
+          <t>K103N+M230L</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>36.85621004700661</v>
+        <v>19.89989946314375</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>156.8440458782563</v>
+        <v>30.71276464247285</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>30.35895686546963</v>
+        <v>17.32599916087358</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>137.7171237560097</v>
+        <v>28.13893547644331</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.8136508305867528</v>
+        <v>-2.082816759745281</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>8.108485726569816</v>
+        <v>1.560664639894519</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>5.659247016906737</v>
+        <v>4.658130515981736</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>14.71134017898962</v>
+        <v>1.133553611658368</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.02435533404350277</v>
+        <v>-0.001413453966284133</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.02050480125340805</v>
+        <v>0.002002584764904485</v>
       </c>
     </row>
     <row r="20">
@@ -1115,34 +1123,34 @@
         <v>3</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-43.95379864374797</v>
+        <v>-10.50521000089578</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>98.92975537812336</v>
+        <v>2.053105908171661</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-67.40200804074604</v>
+        <v>-16.10946654893548</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>91.80969575270723</v>
+        <v>2.590405189358803</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-1.576253573099771</v>
+        <v>-0.3767336455783399</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>4.671840559115609</v>
+        <v>0.2771352263615741</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>25.02569732666016</v>
+        <v>5.981285211916862</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>5.295807117610093</v>
+        <v>0.7972375077889301</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>-0.001234356562296434</v>
+        <v>-0.0002950182988280584</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.01225568033666366</v>
+        <v>0.001020089919432299</v>
       </c>
     </row>
     <row r="21">
@@ -1158,34 +1166,34 @@
         <v>3</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>183.4067652622859</v>
+        <v>43.83526894414098</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>116.2474705000147</v>
+        <v>23.32146372571729</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>154.5238854805629</v>
+        <v>36.93209500013452</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>125.5058822210464</v>
+        <v>25.47505572499026</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>9.618860562642416</v>
+        <v>2.298962849579926</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>2.391397823420196</v>
+        <v>1.192434619495933</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>19.27077490488687</v>
+        <v>4.60582574208577</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>14.91094214197676</v>
+        <v>4.000381532994306</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>-0.006755685806274365</v>
+        <v>-0.001614647659243467</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.01314718671976709</v>
+        <v>0.003052415633014649</v>
       </c>
     </row>
     <row r="22">
@@ -1201,34 +1209,34 @@
         <v>3</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>-58.8829388320446</v>
+        <v>-14.07336014150206</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>85.03805873845738</v>
+        <v>1.739868955165401</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-75.69228070576983</v>
+        <v>-18.09088927002147</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>77.4276626130447</v>
+        <v>1.292908737498776</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>4.877864519755048</v>
+        <v>1.165837600323863</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>1.685855034245907</v>
+        <v>0.4372420451778273</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>11.96163050333659</v>
+        <v>2.858898303856736</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>6.828281003036616</v>
+        <v>0.1824404498562728</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>-0.03015314936637873</v>
+        <v>-0.007206775661180334</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0113257877364077</v>
+        <v>0.002516748710259599</v>
       </c>
     </row>
     <row r="23">
@@ -1244,34 +1252,34 @@
         <v>3</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>82.37138213337568</v>
+        <v>19.68723282346455</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>213.2840021509554</v>
+        <v>37.06534052455587</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>63.92030384421531</v>
+        <v>15.27731927443004</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>188.6351754551368</v>
+        <v>31.87324351809513</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>10.46016557157958</v>
+        <v>2.500039572557261</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>6.077567342630055</v>
+        <v>1.887769233367017</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>7.968987075487774</v>
+        <v>1.904633622248509</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>18.68788649648199</v>
+        <v>3.331860043803003</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.02192564209302297</v>
+        <v>0.005240354228733933</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.06925236325472692</v>
+        <v>0.01443860158012565</v>
       </c>
     </row>
     <row r="24">
@@ -1287,34 +1295,34 @@
         <v>3</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>-89.32294964790344</v>
+        <v>-21.34869733458495</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>87.38736480480379</v>
+        <v>2.489026530391715</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-82.35081814130145</v>
+        <v>-19.68231791140092</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>83.34489981781081</v>
+        <v>0.7405397859745404</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>4.661852773030598</v>
+        <v>1.114209553783603</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>3.665099010901829</v>
+        <v>1.656509023061626</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-11.5958693186442</v>
+        <v>-2.771479282658747</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>3.653036238365312</v>
+        <v>0.9408091648015244</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>-0.03811496098836264</v>
+        <v>-0.009109694308882</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.02884976895193554</v>
+        <v>0.004679800639852124</v>
       </c>
     </row>
     <row r="25">
@@ -1330,41 +1338,42 @@
         <v>3</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-78.90684104164443</v>
+        <v>-18.85918762945612</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>94.611521954916</v>
+        <v>3.294188717214843</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-76.84933134714761</v>
+        <v>-18.36743101031253</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>84.82612637743574</v>
+        <v>1.278630876580305</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.8814885457356768</v>
+        <v>-0.210680818770478</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>1.993912123225962</v>
+        <v>0.4295403545227645</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-1.148423258463552</v>
+        <v>-0.2744797462867012</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>12.23701733640395</v>
+        <v>2.520112075293427</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.02759789029757163</v>
+        <v>-0.006596054086417633</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.009440698189302155</v>
+        <v>4.406995990587801e-05</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A3:M3"/>
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A5:M5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1423,77 +1432,77 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>Mutant total energy (kJ/mol)</t>
+          <t>Mutant total energy (kcal/mol)</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Matched WT total energy (kJ/mol)</t>
+          <t>WT reference total energy (kcal/mol)</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>Total shift (kJ/mol)</t>
+          <t>Total shift (kcal/mol)</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>Mutant van der Waals (kJ/mol)</t>
+          <t>Mutant van der Waals (kcal/mol)</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>Matched WT van der Waals (kJ/mol)</t>
+          <t>WT reference van der Waals (kcal/mol)</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
-          <t>van der Waals shift (kJ/mol)</t>
+          <t>van der Waals shift (kcal/mol)</t>
         </is>
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
-          <t>Mutant electrostatic (kJ/mol)</t>
+          <t>Mutant electrostatic (kcal/mol)</t>
         </is>
       </c>
       <c r="L1" s="4" t="inlineStr">
         <is>
-          <t>Matched WT electrostatic (kJ/mol)</t>
+          <t>WT reference electrostatic (kcal/mol)</t>
         </is>
       </c>
       <c r="M1" s="4" t="inlineStr">
         <is>
-          <t>Electrostatic shift (kJ/mol)</t>
+          <t>Electrostatic shift (kcal/mol)</t>
         </is>
       </c>
       <c r="N1" s="4" t="inlineStr">
         <is>
-          <t>Mutant GB polar solvation (kJ/mol)</t>
+          <t>Mutant GB polar solvation (kcal/mol)</t>
         </is>
       </c>
       <c r="O1" s="4" t="inlineStr">
         <is>
-          <t>Matched WT GB polar solvation (kJ/mol)</t>
+          <t>WT reference GB polar solvation (kcal/mol)</t>
         </is>
       </c>
       <c r="P1" s="4" t="inlineStr">
         <is>
-          <t>GB polar solvation shift (kJ/mol)</t>
+          <t>GB polar solvation shift (kcal/mol)</t>
         </is>
       </c>
       <c r="Q1" s="4" t="inlineStr">
         <is>
-          <t>Mutant nonpolar SA (kJ/mol)</t>
+          <t>Mutant nonpolar SA (kcal/mol)</t>
         </is>
       </c>
       <c r="R1" s="4" t="inlineStr">
         <is>
-          <t>Matched WT nonpolar SA (kJ/mol)</t>
+          <t>WT reference nonpolar SA (kcal/mol)</t>
         </is>
       </c>
       <c r="S1" s="4" t="inlineStr">
         <is>
-          <t>Nonpolar SA shift (kJ/mol)</t>
+          <t>Nonpolar SA shift (kcal/mol)</t>
         </is>
       </c>
     </row>
@@ -1513,49 +1522,49 @@
         <v>20</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>-141.4232854902744</v>
+        <v>-33.80097645561052</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>12.22611638307572</v>
+        <v>-17.94516341778561</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>-239.9137177467346</v>
+        <v>-57.34075471958285</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>31.47542843818664</v>
+        <v>-12.23170304465552</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>-23.7930679321289</v>
+        <v>-5.686679716091994</v>
       </c>
       <c r="L2" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M2" s="11" t="n">
-        <v>-4.817817306518553</v>
+        <v>-0.2505929702554557</v>
       </c>
       <c r="N2" s="11" t="n">
-        <v>124.3078645706177</v>
+        <v>29.71029267940193</v>
       </c>
       <c r="O2" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P2" s="11" t="n">
-        <v>-14.41387443542479</v>
+        <v>-5.454454838355836</v>
       </c>
       <c r="Q2" s="11" t="n">
-        <v>-2.02436438202858</v>
+        <v>-0.4838346993376146</v>
       </c>
       <c r="R2" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S2" s="11" t="n">
-        <v>-0.0176203131675718</v>
+        <v>-0.008412564518802601</v>
       </c>
     </row>
     <row r="3">
@@ -1574,49 +1583,49 @@
         <v>20</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>-145.7235152244568</v>
+        <v>-34.82875602878986</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>-263.2178041040897</v>
+        <v>-18.97294299096496</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>-258.4164936065674</v>
+        <v>-61.76302428455243</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>-235.157703924179</v>
+        <v>-16.65397260962511</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>-17.10488376617432</v>
+        <v>-4.088165336083728</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M3" s="11" t="n">
-        <v>2.38504791259766</v>
+        <v>1.34792140975281</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>131.8232648849487</v>
+        <v>31.50651646389788</v>
       </c>
       <c r="O3" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P3" s="11" t="n">
-        <v>-30.39501972198485</v>
+        <v>-3.658231053859886</v>
       </c>
       <c r="Q3" s="11" t="n">
-        <v>-2.025402736663819</v>
+        <v>-0.4840828720515818</v>
       </c>
       <c r="R3" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S3" s="11" t="n">
-        <v>-0.0501283705234529</v>
+        <v>-0.0086607372327698</v>
       </c>
     </row>
     <row r="4">
@@ -1635,49 +1644,49 @@
         <v>20</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>-144.4719583451748</v>
+        <v>-34.52962675553891</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>18.39509391188622</v>
+        <v>-18.673813717714</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>-271.1333016395569</v>
+        <v>-64.80241434979848</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>0.4275791168213345</v>
+        <v>-19.69336267487116</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>-21.08483619689941</v>
+        <v>-5.039396796582078</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M4" s="11" t="n">
-        <v>8.683742332458497</v>
+        <v>0.3966899492544602</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>149.793257522583</v>
+        <v>35.80144778264413</v>
       </c>
       <c r="O4" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P4" s="11" t="n">
-        <v>9.345370292663574</v>
+        <v>0.6367002648863576</v>
       </c>
       <c r="Q4" s="11" t="n">
-        <v>-2.047078031301498</v>
+        <v>-0.4892633918024613</v>
       </c>
       <c r="R4" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S4" s="11" t="n">
-        <v>-0.0615978300571438</v>
+        <v>-0.0138412569836494</v>
       </c>
     </row>
     <row r="5">
@@ -1696,49 +1705,49 @@
         <v>20</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>60.59589089155197</v>
+        <v>14.48276550945315</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>214.2452927649021</v>
+        <v>30.33857854727805</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>-53.46412127017975</v>
+        <v>-12.77823166113282</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>217.9250249147415</v>
+        <v>32.33082001379449</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>-30.19920616149902</v>
+        <v>-7.217783499402252</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>-11.22395553588867</v>
+        <v>-1.781696753565714</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>146.2483521461487</v>
+        <v>34.95419506361106</v>
       </c>
       <c r="O5" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P5" s="11" t="n">
-        <v>7.526613140106207</v>
+        <v>-0.2105524541467076</v>
       </c>
       <c r="Q5" s="11" t="n">
-        <v>-1.989133822917938</v>
+        <v>-0.4754143936228342</v>
       </c>
       <c r="R5" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S5" s="11" t="n">
-        <v>0.0176102459430693</v>
+        <v>7.741195977684079e-06</v>
       </c>
     </row>
     <row r="6">
@@ -1757,49 +1766,49 @@
         <v>20</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>-23.15980125665665</v>
+        <v>-5.535325348149295</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>-140.6540901362896</v>
+        <v>10.32048768967561</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>-168.0281283855438</v>
+        <v>-40.15968651662137</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>-144.7693387031555</v>
+        <v>4.949365158305952</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>-30.58382511138916</v>
+        <v>-7.309709634653241</v>
       </c>
       <c r="L6" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>-11.09389343261718</v>
+        <v>-1.873622888816703</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>177.4205921173096</v>
+        <v>42.40453922497839</v>
       </c>
       <c r="O6" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P6" s="11" t="n">
-        <v>15.20230751037599</v>
+        <v>7.239791707220618</v>
       </c>
       <c r="Q6" s="11" t="n">
-        <v>-1.968439877033234</v>
+        <v>-0.4704684218530673</v>
       </c>
       <c r="R6" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S6" s="11" t="n">
-        <v>0.0068344891071319</v>
+        <v>0.0049537129657445</v>
       </c>
     </row>
     <row r="7">
@@ -1818,49 +1827,49 @@
         <v>20</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>-117.8750780880451</v>
+        <v>-28.17281981071824</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>44.99197416901589</v>
+        <v>-12.31700677289334</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>-270.0824166297913</v>
+        <v>-64.55124680444342</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>1.478464126586914</v>
+        <v>-19.4421951295161</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>-31.07509384155274</v>
+        <v>-7.427125679147403</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>-1.306515312194826</v>
+        <v>-1.991038933310866</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>185.2946783065796</v>
+        <v>44.28649099105631</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P7" s="11" t="n">
-        <v>44.84679107666017</v>
+        <v>9.121743473298544</v>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>-2.012245923280716</v>
+        <v>-0.4809383181837275</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>-0.0267657220363615</v>
+        <v>-0.0055161833649156</v>
       </c>
     </row>
     <row r="8">
@@ -1879,49 +1888,49 @@
         <v>20</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>-110.5403502702713</v>
+        <v>-26.41977778926178</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>43.10905160307884</v>
+        <v>-10.56396475143688</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>-238.8724104881287</v>
+        <v>-57.09187631169422</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>32.51673569679264</v>
+        <v>-11.9828246367669</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>-25.51262264251709</v>
+        <v>-6.097663155477316</v>
       </c>
       <c r="L8" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>-6.53737201690674</v>
+        <v>-0.6615764096407784</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>155.8618267059326</v>
+        <v>37.25187062761296</v>
       </c>
       <c r="O8" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P8" s="11" t="n">
-        <v>17.14008769989016</v>
+        <v>2.087123109855192</v>
       </c>
       <c r="Q8" s="11" t="n">
-        <v>-2.017143845558167</v>
+        <v>-0.4821089497031946</v>
       </c>
       <c r="R8" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S8" s="11" t="n">
-        <v>-0.0103997766971586</v>
+        <v>-0.0066868148843827</v>
       </c>
     </row>
     <row r="9">
@@ -1940,49 +1949,49 @@
         <v>20</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>-42.06295204162598</v>
+        <v>-10.05328681683221</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>-159.5572409212589</v>
+        <v>5.802526220992689</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>-174.7895704269409</v>
+        <v>-41.77570994907765</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>-151.5307807445526</v>
+        <v>3.333341725849671</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>-26.44059238433838</v>
+        <v>-6.319453246734795</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>-6.950660705566403</v>
+        <v>-0.8833665008982567</v>
       </c>
       <c r="N9" s="11" t="n">
-        <v>161.1921867370606</v>
+        <v>38.52585725073149</v>
       </c>
       <c r="O9" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P9" s="11" t="n">
-        <v>-1.026097869873041</v>
+        <v>3.361109732973723</v>
       </c>
       <c r="Q9" s="11" t="n">
-        <v>-2.024975967407227</v>
+        <v>-0.4839808717512492</v>
       </c>
       <c r="R9" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S9" s="11" t="n">
-        <v>-0.0497016012668611</v>
+        <v>-0.0085587369324373</v>
       </c>
     </row>
     <row r="10">
@@ -2001,49 +2010,49 @@
         <v>20</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>-62.51759850382805</v>
+        <v>-14.94206465196655</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>100.349453753233</v>
+        <v>0.9137483858583516</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>-210.3190220355987</v>
+        <v>-50.26745268537255</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>61.24185872077945</v>
+        <v>-5.158401010445225</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>-23.6373197555542</v>
+        <v>-5.649455008497657</v>
       </c>
       <c r="L10" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>6.131258773803712</v>
+        <v>-0.2133682626611195</v>
       </c>
       <c r="N10" s="11" t="n">
-        <v>173.4505725860596</v>
+        <v>41.45568178443106</v>
       </c>
       <c r="O10" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P10" s="11" t="n">
-        <v>33.00268535614012</v>
+        <v>6.29093426667329</v>
       </c>
       <c r="Q10" s="11" t="n">
-        <v>-2.011829298734665</v>
+        <v>-0.4808387425274056</v>
       </c>
       <c r="R10" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S10" s="11" t="n">
-        <v>-0.0263490974903106</v>
+        <v>-0.0054166077085937</v>
       </c>
     </row>
     <row r="11">
@@ -2062,49 +2071,49 @@
         <v>20</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>8.013941234350204</v>
+        <v>1.915377924079877</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>161.6633431077003</v>
+        <v>17.77119096190478</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>-132.8285562515259</v>
+        <v>-31.74678686699949</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>138.5605899333954</v>
+        <v>13.36226480792783</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>-22.74183311462403</v>
+        <v>-5.435428564680694</v>
       </c>
       <c r="L11" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>-3.766582489013675</v>
+        <v>0.0006581811558437</v>
       </c>
       <c r="N11" s="11" t="n">
-        <v>165.6081509590149</v>
+        <v>39.58129803035729</v>
       </c>
       <c r="O11" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P11" s="11" t="n">
-        <v>26.88641195297242</v>
+        <v>4.416550512599521</v>
       </c>
       <c r="Q11" s="11" t="n">
-        <v>-2.023820358514786</v>
+        <v>-0.483704674597224</v>
       </c>
       <c r="R11" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S11" s="11" t="n">
-        <v>-0.0170762896537777</v>
+        <v>-0.008282539778412</v>
       </c>
     </row>
     <row r="12">
@@ -2123,49 +2132,49 @@
         <v>20</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>-135.6065875887871</v>
+        <v>-32.41075229177511</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>-253.10087646842</v>
+        <v>-16.55493925395021</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>-261.28689661026</v>
+        <v>-62.44906706746175</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>-238.0281069278717</v>
+        <v>-17.34001539253443</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>-19.48237495422363</v>
+        <v>-4.656399367644272</v>
       </c>
       <c r="L12" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.0075567245483441</v>
+        <v>0.779687378192266</v>
       </c>
       <c r="N12" s="11" t="n">
-        <v>147.182638168335</v>
+        <v>35.17749478210683</v>
       </c>
       <c r="O12" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P12" s="11" t="n">
-        <v>-15.03564643859863</v>
+        <v>0.0127472643490591</v>
       </c>
       <c r="Q12" s="11" t="n">
-        <v>-2.019954192638397</v>
+        <v>-0.4827806387759075</v>
       </c>
       <c r="R12" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S12" s="11" t="n">
-        <v>-0.0446798264980314</v>
+        <v>-0.0073585039570955</v>
       </c>
     </row>
     <row r="13">
@@ -2184,49 +2193,49 @@
         <v>20</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>-138.3456632494926</v>
+        <v>-33.06540708639881</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>24.52138900756836</v>
+        <v>-17.20959404857391</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>-266.883503484726</v>
+        <v>-63.78668821336662</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>4.677377271652233</v>
+        <v>-18.6776365384393</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>-20.43811798095703</v>
+        <v>-4.884827433307129</v>
       </c>
       <c r="L13" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>9.330460548400881</v>
+        <v>0.5512593125294085</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>150.9787055969238</v>
+        <v>36.08477667230493</v>
       </c>
       <c r="O13" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>10.53081836700437</v>
+        <v>0.9200291545471586</v>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>-2.00274738073349</v>
+        <v>-0.4786681120299927</v>
       </c>
       <c r="R13" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S13" s="11" t="n">
-        <v>-0.0172671794891354</v>
+        <v>-0.0032459772111808</v>
       </c>
     </row>
     <row r="14">
@@ -2245,49 +2254,49 @@
         <v>20</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>133.9707780063152</v>
+        <v>32.01978441833538</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>287.6201798796654</v>
+        <v>47.87559745616029</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>24.01529772281647</v>
+        <v>5.739793910806995</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>295.4044439077377</v>
+        <v>50.84884558573432</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>-18.20252952575684</v>
+        <v>-4.350508968871137</v>
       </c>
       <c r="L14" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.7727210998535128</v>
+        <v>1.085577776965401</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>130.1183572769165</v>
+        <v>31.09903376599343</v>
       </c>
       <c r="O14" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P14" s="11" t="n">
-        <v>-8.603381729125971</v>
+        <v>-4.065713751764342</v>
       </c>
       <c r="Q14" s="11" t="n">
-        <v>-1.960347467660904</v>
+        <v>-0.4685342895939063</v>
       </c>
       <c r="R14" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S14" s="11" t="n">
-        <v>0.0463966012001038</v>
+        <v>0.0068878452249055</v>
       </c>
     </row>
     <row r="15">
@@ -2306,49 +2315,49 @@
         <v>20</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>-148.2518131494522</v>
+        <v>-35.43303373552872</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>-265.7461020290851</v>
+        <v>-19.57722069770382</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>-258.7113182067871</v>
+        <v>-61.83348905515944</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>-235.4525285243988</v>
+        <v>-16.72443738023212</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>-28.30532417297363</v>
+        <v>-6.765134840576871</v>
       </c>
       <c r="L15" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>-8.815392494201653</v>
+        <v>-1.329048094740333</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>140.800322341919</v>
+        <v>33.65208468975118</v>
       </c>
       <c r="O15" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P15" s="11" t="n">
-        <v>-21.41796226501464</v>
+        <v>-1.512662828006583</v>
       </c>
       <c r="Q15" s="11" t="n">
-        <v>-2.035493111610413</v>
+        <v>-0.4864945295435977</v>
       </c>
       <c r="R15" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S15" s="11" t="n">
-        <v>-0.0602187454700471</v>
+        <v>-0.0110723947247857</v>
       </c>
     </row>
     <row r="16">
@@ -2367,49 +2376,49 @@
         <v>20</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>-140.210496109724</v>
+        <v>-33.51111283693213</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>22.65655614733697</v>
+        <v>-17.65529979910723</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>-263.9758023262024</v>
+        <v>-63.09173095750534</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>7.585078430175827</v>
+        <v>-17.98267928257802</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>-17.77384433746338</v>
+        <v>-4.248050749871744</v>
       </c>
       <c r="L16" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>11.99473419189453</v>
+        <v>1.188035995964794</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>143.5711179733276</v>
+        <v>34.31432073932304</v>
       </c>
       <c r="O16" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P16" s="11" t="n">
-        <v>3.123230743408186</v>
+        <v>-0.8504267784347235</v>
       </c>
       <c r="Q16" s="11" t="n">
-        <v>-2.03196741938591</v>
+        <v>-0.4856518688780855</v>
       </c>
       <c r="R16" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S16" s="11" t="n">
-        <v>-0.0464872181415554</v>
+        <v>-0.0102297340592735</v>
       </c>
     </row>
     <row r="17">
@@ -2428,49 +2437,49 @@
         <v>20</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>100.6565567433834</v>
+        <v>24.05749444153523</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>254.3059586167336</v>
+        <v>39.91330747936013</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>-44.58128309249878</v>
+        <v>-10.65518238348441</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>226.8078630924225</v>
+        <v>34.45386929144291</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-4.47813606262207</v>
+        <v>-1.070300206171623</v>
       </c>
       <c r="L17" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>14.49711456298828</v>
+        <v>4.365786539664915</v>
       </c>
       <c r="N17" s="11" t="n">
-        <v>151.6622631072998</v>
+        <v>36.24815083826477</v>
       </c>
       <c r="O17" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P17" s="11" t="n">
-        <v>12.94052410125732</v>
+        <v>1.083403320507003</v>
       </c>
       <c r="Q17" s="11" t="n">
-        <v>-1.946287208795547</v>
+        <v>-0.4651738070735055</v>
       </c>
       <c r="R17" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S17" s="11" t="n">
-        <v>0.0604568600654606</v>
+        <v>0.0102483277453064</v>
       </c>
     </row>
     <row r="18">
@@ -2489,49 +2498,49 @@
         <v>20</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-78.45287473797798</v>
+        <v>-18.75068707886663</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>-195.947163617611</v>
+        <v>-2.894874041041728</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>-199.3028004646302</v>
+        <v>-47.63451253934755</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>-176.0440107822419</v>
+        <v>-2.525460864420232</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-16.34948463439941</v>
+        <v>-3.907620610516112</v>
       </c>
       <c r="L18" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>3.140447044372564</v>
+        <v>1.528466135320426</v>
       </c>
       <c r="N18" s="11" t="n">
-        <v>139.2237659454346</v>
+        <v>33.27527866764688</v>
       </c>
       <c r="O18" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P18" s="11" t="n">
-        <v>-22.99451866149903</v>
+        <v>-1.889468850110887</v>
       </c>
       <c r="Q18" s="11" t="n">
-        <v>-2.024355584383011</v>
+        <v>-0.4838325966498591</v>
       </c>
       <c r="R18" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S18" s="11" t="n">
-        <v>-0.0490812182426452</v>
+        <v>-0.008410461831047201</v>
       </c>
     </row>
     <row r="19">
@@ -2550,49 +2559,49 @@
         <v>20</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-107.9480256974697</v>
+        <v>-25.80019734643158</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>54.91902655959129</v>
+        <v>-9.944384308606676</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>-255.4039635658264</v>
+        <v>-61.04301232452829</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>16.15691719055181</v>
+        <v>-15.93396064960097</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-8.928154563903808</v>
+        <v>-2.133880153896703</v>
       </c>
       <c r="L19" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>20.8404239654541</v>
+        <v>3.302206591939834</v>
       </c>
       <c r="N19" s="11" t="n">
-        <v>158.3908473968505</v>
+        <v>37.85632107955319</v>
       </c>
       <c r="O19" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P19" s="11" t="n">
-        <v>17.9429601669311</v>
+        <v>2.691573561795423</v>
       </c>
       <c r="Q19" s="11" t="n">
-        <v>-2.006754964590073</v>
+        <v>-0.4796259475597688</v>
       </c>
       <c r="R19" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S19" s="11" t="n">
-        <v>-0.0212747633457182</v>
+        <v>-0.0042038127409568</v>
       </c>
     </row>
     <row r="20">
@@ -2611,49 +2620,49 @@
         <v>20</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-137.4537552416325</v>
+        <v>-32.85223595641311</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>16.19564663171769</v>
+        <v>-16.99642291858821</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>-266.099254655838</v>
+        <v>-63.59924824470315</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>5.289891529083263</v>
+        <v>-18.49019656977583</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-37.67992935180664</v>
+        <v>-9.005719252343843</v>
       </c>
       <c r="L20" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>-18.70467872619629</v>
+        <v>-3.569632506507305</v>
       </c>
       <c r="N20" s="11" t="n">
-        <v>168.3587032318115</v>
+        <v>40.23869580110217</v>
       </c>
       <c r="O20" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P20" s="11" t="n">
-        <v>29.63696422576905</v>
+        <v>5.073948283344407</v>
       </c>
       <c r="Q20" s="11" t="n">
-        <v>-2.033274465799332</v>
+        <v>-0.4859642604682914</v>
       </c>
       <c r="R20" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S20" s="11" t="n">
-        <v>-0.0265303969383237</v>
+        <v>-0.0105421256494794</v>
       </c>
     </row>
     <row r="21">
@@ -2672,49 +2681,49 @@
         <v>20</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-145.5608445703983</v>
+        <v>-34.78987680936862</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-263.0551334500313</v>
+        <v>-18.93406377154372</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>-271.4170305252075</v>
+        <v>-64.87022718097694</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>-248.1582408428192</v>
+        <v>-19.76117550604961</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-36.01710433959961</v>
+        <v>-8.608294536233176</v>
       </c>
       <c r="L21" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>-16.52717266082763</v>
+        <v>-3.172207790396638</v>
       </c>
       <c r="N21" s="11" t="n">
-        <v>163.8813812255859</v>
+        <v>39.16859015907885</v>
       </c>
       <c r="O21" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P21" s="11" t="n">
-        <v>1.663096618652332</v>
+        <v>4.003842641321086</v>
       </c>
       <c r="Q21" s="11" t="n">
-        <v>-2.008090931177139</v>
+        <v>-0.4799452512373659</v>
       </c>
       <c r="R21" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S21" s="11" t="n">
-        <v>-0.0328165650367735</v>
+        <v>-0.004523116418554</v>
       </c>
     </row>
     <row r="22">
@@ -2733,49 +2742,49 @@
         <v>20</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-142.1426003336906</v>
+        <v>-33.97289682927596</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>20.72445192337037</v>
+        <v>-18.11708379145106</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>-276.5360857009888</v>
+        <v>-66.09371073159387</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>-4.975204944610596</v>
+        <v>-20.98465905666655</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-26.43614482879639</v>
+        <v>-6.318390255448467</v>
       </c>
       <c r="L22" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>3.332433700561523</v>
+        <v>-0.8823035096119289</v>
       </c>
       <c r="N22" s="11" t="n">
-        <v>162.8740919113159</v>
+        <v>38.92784223501815</v>
       </c>
       <c r="O22" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P22" s="11" t="n">
-        <v>22.42620468139648</v>
+        <v>3.76309471726038</v>
       </c>
       <c r="Q22" s="11" t="n">
-        <v>-2.044461715221405</v>
+        <v>-0.4886380772517698</v>
       </c>
       <c r="R22" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S22" s="11" t="n">
-        <v>-0.0589815139770504</v>
+        <v>-0.0132159424329578</v>
       </c>
     </row>
     <row r="23">
@@ -2794,49 +2803,49 @@
         <v>20</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-59.89853761196137</v>
+        <v>-14.31609407551658</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>93.75086426138878</v>
+        <v>1.539718962308325</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>-209.9914470672607</v>
+        <v>-50.18916038892464</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>61.39769911766058</v>
+        <v>-5.080108713997319</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-25.81308288574219</v>
+        <v>-6.169474877089432</v>
       </c>
       <c r="L23" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>-6.837832260131837</v>
+        <v>-0.7333881312528945</v>
       </c>
       <c r="N23" s="11" t="n">
-        <v>177.9442260742188</v>
+        <v>42.52969074431615</v>
       </c>
       <c r="O23" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P23" s="11" t="n">
-        <v>39.22248706817629</v>
+        <v>7.364943226558381</v>
       </c>
       <c r="Q23" s="11" t="n">
-        <v>-2.038233733177185</v>
+        <v>-0.4871495538186389</v>
       </c>
       <c r="R23" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S23" s="11" t="n">
-        <v>-0.0314896643161772</v>
+        <v>-0.0117274189998269</v>
       </c>
     </row>
     <row r="24">
@@ -2855,49 +2864,49 @@
         <v>20</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-112.7681836724281</v>
+        <v>-26.95224275153636</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-230.2624725520611</v>
+        <v>-11.09642971371146</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>-271.1263545036316</v>
+        <v>-64.80075394446261</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>-247.8675648212433</v>
+        <v>-19.69170226953529</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-32.56664714813233</v>
+        <v>-7.783615475175029</v>
       </c>
       <c r="L24" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>-13.07671546936035</v>
+        <v>-2.347528729338491</v>
       </c>
       <c r="N24" s="11" t="n">
-        <v>192.9223431587219</v>
+        <v>46.109546644054</v>
       </c>
       <c r="O24" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P24" s="11" t="n">
-        <v>30.70405855178834</v>
+        <v>10.94479912629623</v>
       </c>
       <c r="Q24" s="11" t="n">
-        <v>-1.997525179386139</v>
+        <v>-0.47741997595271</v>
       </c>
       <c r="R24" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S24" s="11" t="n">
-        <v>-0.0222508132457732</v>
+        <v>-0.0019978411338981</v>
       </c>
     </row>
     <row r="25">
@@ -2916,49 +2925,49 @@
         <v>20</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-98.24729549884796</v>
+        <v>-23.48166718423708</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>64.61975675821304</v>
+        <v>-7.625854146412177</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>-269.4754653930664</v>
+        <v>-64.40618197731033</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>2.085415363311768</v>
+        <v>-19.297130302383</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-17.0170352935791</v>
+        <v>-4.067169047222539</v>
       </c>
       <c r="L25" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>12.75154323577881</v>
+        <v>1.368917698613999</v>
       </c>
       <c r="N25" s="11" t="n">
-        <v>190.2527401924134</v>
+        <v>45.47149622189612</v>
       </c>
       <c r="O25" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P25" s="11" t="n">
-        <v>49.80485296249392</v>
+        <v>10.30674870413835</v>
       </c>
       <c r="Q25" s="11" t="n">
-        <v>-2.007535004615784</v>
+        <v>-0.4798123816003307</v>
       </c>
       <c r="R25" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S25" s="11" t="n">
-        <v>-0.0220548033714291</v>
+        <v>-0.0043902467815187</v>
       </c>
     </row>
     <row r="26">
@@ -2977,49 +2986,49 @@
         <v>20</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>156.5064391136169</v>
+        <v>37.40593669063502</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>310.1558409869671</v>
+        <v>53.26174972845993</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>-44.85465667247773</v>
+        <v>-10.72052023720787</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>226.5344895124435</v>
+        <v>34.38853143771945</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-15.36590728759766</v>
+        <v>-3.672539982695424</v>
       </c>
       <c r="L26" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>3.609343338012694</v>
+        <v>1.763546763141114</v>
       </c>
       <c r="N26" s="11" t="n">
-        <v>218.6901330947876</v>
+        <v>52.26819624636415</v>
       </c>
       <c r="O26" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P26" s="11" t="n">
-        <v>79.96839408874513</v>
+        <v>17.10344872860638</v>
       </c>
       <c r="Q26" s="11" t="n">
-        <v>-1.963130021095276</v>
+        <v>-0.4691993358258308</v>
       </c>
       <c r="R26" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S26" s="11" t="n">
-        <v>0.0436140477657318</v>
+        <v>0.0062227989929811</v>
       </c>
     </row>
     <row r="27">
@@ -3038,49 +3047,49 @@
         <v>20</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>195.0314100146294</v>
+        <v>46.61362572051371</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>77.5371211349964</v>
+        <v>62.46943875833861</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>17.61226646900177</v>
+        <v>4.209432712476523</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>40.87105615139008</v>
+        <v>49.31848438740384</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>-10.69200325012207</v>
+        <v>-2.555450107581757</v>
       </c>
       <c r="L27" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>8.797928428649907</v>
+        <v>2.880636638254781</v>
       </c>
       <c r="N27" s="11" t="n">
-        <v>190.105415725708</v>
+        <v>45.43628482928012</v>
       </c>
       <c r="O27" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P27" s="11" t="n">
-        <v>27.88713111877442</v>
+        <v>10.27153731152235</v>
       </c>
       <c r="Q27" s="11" t="n">
-        <v>-1.994268929958344</v>
+        <v>-0.476641713661172</v>
       </c>
       <c r="R27" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S27" s="11" t="n">
-        <v>-0.018994563817978</v>
+        <v>-0.00121957884236</v>
       </c>
     </row>
     <row r="28">
@@ -3099,598 +3108,598 @@
         <v>20</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>-128.6296243429184</v>
+        <v>-30.74321805519082</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>34.23742791414261</v>
+        <v>-14.88740501736592</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>-267.9665593147278</v>
+        <v>-64.04554476929439</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>3.594321441650436</v>
+        <v>-18.93649309436707</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>-28.30087814331055</v>
+        <v>-6.764072213984356</v>
       </c>
       <c r="L28" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>1.467700386047362</v>
+        <v>-1.327985468147818</v>
       </c>
       <c r="N28" s="11" t="n">
-        <v>169.6601236343384</v>
+        <v>40.54974274243269</v>
       </c>
       <c r="O28" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P28" s="11" t="n">
-        <v>29.21223640441895</v>
+        <v>5.384995224674924</v>
       </c>
       <c r="Q28" s="11" t="n">
-        <v>-2.022310519218445</v>
+        <v>-0.4833438143447525</v>
       </c>
       <c r="R28" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S28" s="11" t="n">
-        <v>-0.0368303179740903</v>
+        <v>-0.0079216795259405</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>K103N+M230L</t>
+          <t>V106A</t>
         </is>
       </c>
       <c r="B29" s="9" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>20</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>-67.33268616199493</v>
+        <v>-28.11579520513177</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>86.31671571135522</v>
+        <v>-12.25998216730687</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>-187.7546764373779</v>
+        <v>-61.86828157413985</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>83.63446974754336</v>
+        <v>-16.75922989921253</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>-39.84068698883057</v>
+        <v>-5.773967082824124</v>
       </c>
       <c r="L29" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>-20.86543636322022</v>
+        <v>-0.3378803369875864</v>
       </c>
       <c r="N29" s="11" t="n">
-        <v>162.2700024604797</v>
+        <v>40.01090280412487</v>
       </c>
       <c r="O29" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P29" s="11" t="n">
-        <v>23.54826345443726</v>
+        <v>4.846155286367107</v>
       </c>
       <c r="Q29" s="11" t="n">
-        <v>-2.007325196266174</v>
+        <v>-0.484449352292668</v>
       </c>
       <c r="R29" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S29" s="11" t="n">
-        <v>-0.0005811274051663</v>
+        <v>-0.009027217473856</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>K103N+M230L</t>
+          <t>V106A</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>20</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>269.3194899737835</v>
+        <v>-33.75805051958127</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>151.8252010941505</v>
+        <v>-17.90223748175637</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>113.7995845794678</v>
+        <v>-62.84383069260853</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>137.0583742618561</v>
+        <v>-17.73477901768121</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>-18.59492568969726</v>
+        <v>-5.691660065951812</v>
       </c>
       <c r="L30" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.8950059890747148</v>
+        <v>-0.2555733201152739</v>
       </c>
       <c r="N30" s="11" t="n">
-        <v>176.0938812255859</v>
+        <v>35.25247259304127</v>
       </c>
       <c r="O30" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P30" s="11" t="n">
-        <v>13.87559661865234</v>
+        <v>0.087725075283501</v>
       </c>
       <c r="Q30" s="11" t="n">
-        <v>-1.979050141572952</v>
+        <v>-0.4750323540621916</v>
       </c>
       <c r="R30" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S30" s="11" t="n">
-        <v>-0.0037757754325864</v>
+        <v>0.0003897807566203</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>K103N+M230L</t>
+          <t>V106A</t>
         </is>
       </c>
       <c r="B31" s="9" t="n">
         <v>3</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="D31" s="9" t="n">
         <v>20</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>-151.2254310011864</v>
+        <v>-30.4714200601523</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>11.64162125587464</v>
+        <v>-14.6156070223274</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>-274.7777832984924</v>
+        <v>-63.14995487151137</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>-3.216902542114212</v>
+        <v>-18.04090319658405</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-35.94166412353515</v>
+        <v>-6.005716278265813</v>
       </c>
       <c r="L31" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>-6.173085594177245</v>
+        <v>-0.5696295324292748</v>
       </c>
       <c r="N31" s="11" t="n">
-        <v>161.4928813934326</v>
+        <v>39.164519902625</v>
       </c>
       <c r="O31" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P31" s="11" t="n">
-        <v>21.04499416351317</v>
+        <v>3.999772384867235</v>
       </c>
       <c r="Q31" s="11" t="n">
-        <v>-1.9988649725914</v>
+        <v>-0.4802688130001264</v>
       </c>
       <c r="R31" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S31" s="11" t="n">
-        <v>-0.0133847713470456</v>
+        <v>-0.0048466781813145</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>V106A</t>
+          <t>Y318F</t>
         </is>
       </c>
       <c r="B32" s="9" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="D32" s="9" t="n">
         <v>20</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>-117.6364871382713</v>
+        <v>-40.21922734710272</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>36.01291473507882</v>
+        <v>-24.36341430927782</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>-258.8568901062011</v>
+        <v>-62.87473111945858</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>12.53225607872014</v>
+        <v>-17.76567944453126</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-24.15827827453614</v>
+        <v>-6.708700934969899</v>
       </c>
       <c r="L32" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>-5.183027648925787</v>
+        <v>-1.272614189133361</v>
       </c>
       <c r="N32" s="11" t="n">
-        <v>167.4056173324585</v>
+        <v>29.83951094501561</v>
       </c>
       <c r="O32" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P32" s="11" t="n">
-        <v>28.68387832641602</v>
+        <v>-5.32523657274216</v>
       </c>
       <c r="Q32" s="11" t="n">
-        <v>-2.026936089992523</v>
+        <v>-0.4753062376898515</v>
       </c>
       <c r="R32" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S32" s="11" t="n">
-        <v>-0.0201920211315154</v>
+        <v>0.0001158971289604</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>V106A</t>
+          <t>Y318F</t>
         </is>
       </c>
       <c r="B33" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="D33" s="9" t="n">
         <v>20</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>-141.2436833739281</v>
+        <v>-21.00513213907099</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>-258.737972253561</v>
+        <v>-5.149319101246089</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>-262.9385876178741</v>
+        <v>-52.49744494148239</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>-239.6797979354859</v>
+        <v>-7.38839326655507</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-23.81390571594238</v>
+        <v>-5.937148188997636</v>
       </c>
       <c r="L33" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>-4.323974037170405</v>
+        <v>-0.501061443161098</v>
       </c>
       <c r="N33" s="11" t="n">
-        <v>147.4963453292847</v>
+        <v>37.90337770436507</v>
       </c>
       <c r="O33" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P33" s="11" t="n">
-        <v>-14.72193927764891</v>
+        <v>2.738630186607303</v>
       </c>
       <c r="Q33" s="11" t="n">
-        <v>-1.98753536939621</v>
+        <v>-0.4739167129560365</v>
       </c>
       <c r="R33" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S33" s="11" t="n">
-        <v>-0.0122610032558441</v>
+        <v>0.0015054218627754</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>V106A</t>
+          <t>Y318F</t>
         </is>
       </c>
       <c r="B34" s="9" t="n">
         <v>3</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="D34" s="9" t="n">
         <v>20</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>-127.4924215316772</v>
+        <v>40.08345721328691</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>35.37463072538377</v>
+        <v>55.93927025111181</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>-264.2194111824036</v>
+        <v>1.812915538168774</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>7.341469573974621</v>
+        <v>46.9219672130961</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-25.12791690826416</v>
+        <v>-3.079009466371846</v>
       </c>
       <c r="L34" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>4.640661621093749</v>
+        <v>2.357077279464692</v>
       </c>
       <c r="N34" s="11" t="n">
-        <v>163.864351272583</v>
+        <v>41.80913140167469</v>
       </c>
       <c r="O34" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P34" s="11" t="n">
-        <v>23.41646404266356</v>
+        <v>6.644383883916923</v>
       </c>
       <c r="Q34" s="11" t="n">
-        <v>-2.009444713592529</v>
+        <v>-0.4595802601847092</v>
       </c>
       <c r="R34" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S34" s="11" t="n">
-        <v>-0.0239645123481748</v>
+        <v>0.0158418746341026</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Y318F</t>
+          <t>K103N+M230L</t>
         </is>
       </c>
       <c r="B35" s="9" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="10" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D35" s="9" t="n">
         <v>20</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>-168.2772472202778</v>
+        <v>-16.09289822227412</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>-14.62784534692764</v>
+        <v>-0.2370851844492207</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>-263.0678750038147</v>
+        <v>-44.87444465520505</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>8.321271181106567</v>
+        <v>0.2346070197222758</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-28.06920471191406</v>
+        <v>-9.522152721995834</v>
       </c>
       <c r="L35" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>-9.093954086303713</v>
+        <v>-4.086065976159296</v>
       </c>
       <c r="N35" s="11" t="n">
-        <v>124.8485137939453</v>
+        <v>38.78346139112804</v>
       </c>
       <c r="O35" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P35" s="11" t="n">
-        <v>-13.87322521209715</v>
+        <v>3.618713873370275</v>
       </c>
       <c r="Q35" s="11" t="n">
-        <v>-1.988681298494339</v>
+        <v>-0.4797622362012844</v>
       </c>
       <c r="R35" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S35" s="11" t="n">
-        <v>0.0180627703666689</v>
+        <v>-0.0043401013824724</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Y318F</t>
+          <t>K103N+M230L</t>
         </is>
       </c>
       <c r="B36" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D36" s="9" t="n">
         <v>20</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>-87.88547286987304</v>
+        <v>64.36890295740523</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>-205.379761749506</v>
+        <v>80.22471599523013</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>-219.6493096351624</v>
+        <v>27.19875348457643</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>-196.390519952774</v>
+        <v>72.30780515950374</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-24.84102802276611</v>
+        <v>-4.444293902891315</v>
       </c>
       <c r="L36" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>-5.351096343994133</v>
+        <v>0.9917928429452232</v>
       </c>
       <c r="N36" s="11" t="n">
-        <v>158.5877323150635</v>
+        <v>42.08744771166012</v>
       </c>
       <c r="O36" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P36" s="11" t="n">
-        <v>-3.630552291870117</v>
+        <v>6.922700193902351</v>
       </c>
       <c r="Q36" s="11" t="n">
-        <v>-1.982867527008057</v>
+        <v>-0.4730043359399981</v>
       </c>
       <c r="R36" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S36" s="11" t="n">
-        <v>-0.0075931608676913</v>
+        <v>0.0024177988788138</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Y318F</t>
+          <t>K103N+M230L</t>
         </is>
       </c>
       <c r="B37" s="9" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>20</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>167.7091849803925</v>
+        <v>-36.14374545917456</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>330.5762372374535</v>
+        <v>-20.28793242134966</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>7.58523861169815</v>
+        <v>-65.6734663715326</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>279.1461193680764</v>
+        <v>-20.56441469660528</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-12.8825756072998</v>
+        <v>-8.590263891858307</v>
       </c>
       <c r="L37" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>16.8860029220581</v>
+        <v>-3.154177146021769</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>174.9294057846069</v>
+        <v>38.59772499843035</v>
       </c>
       <c r="O37" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P37" s="11" t="n">
-        <v>34.48151855468748</v>
+        <v>3.432977480672584</v>
       </c>
       <c r="Q37" s="11" t="n">
-        <v>-1.922883808612824</v>
+        <v>-0.4777401942140057</v>
       </c>
       <c r="R37" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S37" s="11" t="n">
-        <v>0.0625963926315307</v>
+        <v>-0.0023180593951938</v>
       </c>
     </row>
     <row r="38">
@@ -3709,49 +3718,49 @@
         <v>20</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>-112.9577533125877</v>
+        <v>-26.99755098293205</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>40.6916485607624</v>
+        <v>-11.14173794510715</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>-258.1093069076538</v>
+        <v>-61.6896049014469</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>13.27983927726746</v>
+        <v>-16.58055322651958</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-25.40261287689209</v>
+        <v>-6.07137019046178</v>
       </c>
       <c r="L38" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>-6.427362251281739</v>
+        <v>-0.6352834446252418</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>172.5376497268677</v>
+        <v>41.237487984433</v>
       </c>
       <c r="O38" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P38" s="11" t="n">
-        <v>33.8159107208252</v>
+        <v>6.072740466675228</v>
       </c>
       <c r="Q38" s="11" t="n">
-        <v>-1.983483254909515</v>
+        <v>-0.474063875456385</v>
       </c>
       <c r="R38" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S38" s="11" t="n">
-        <v>0.0232608139514927</v>
+        <v>0.0013582593624268</v>
       </c>
     </row>
     <row r="39">
@@ -3770,49 +3779,49 @@
         <v>20</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>-123.6617048859596</v>
+        <v>-29.55585680830775</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>-241.1559937655926</v>
+        <v>-13.70004377048285</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>-273.8474085330963</v>
+        <v>-65.4511014658452</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>-250.588618850708</v>
+        <v>-20.34204979091788</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-25.55643463134766</v>
+        <v>-6.108134472119421</v>
       </c>
       <c r="L39" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>-6.066502952575679</v>
+        <v>-0.6720477262828828</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>177.7316659927368</v>
+        <v>42.47888766556807</v>
       </c>
       <c r="O39" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P39" s="11" t="n">
-        <v>15.51338138580323</v>
+        <v>7.314140147810306</v>
       </c>
       <c r="Q39" s="11" t="n">
-        <v>-1.989527714252472</v>
+        <v>-0.4755085359112027</v>
       </c>
       <c r="R39" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S39" s="11" t="n">
-        <v>-0.0142533481121065</v>
+        <v>-8.640109239077542e-05</v>
       </c>
     </row>
     <row r="40">
@@ -3831,49 +3840,49 @@
         <v>20</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>-94.26410298347471</v>
+        <v>-22.52966132492226</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>68.60294927358629</v>
+        <v>-6.673848287097353</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>-236.4581253051758</v>
+        <v>-56.51484830429631</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>35.10275545120243</v>
+        <v>-11.40579662936899</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-22.00347404479981</v>
+        <v>-5.258956511663433</v>
       </c>
       <c r="L40" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>7.765104484558105</v>
+        <v>0.1771302341731049</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>166.1956871032715</v>
+        <v>39.72172253902282</v>
       </c>
       <c r="O40" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P40" s="11" t="n">
-        <v>25.74779987335205</v>
+        <v>4.556975021265053</v>
       </c>
       <c r="Q40" s="11" t="n">
-        <v>-1.99819073677063</v>
+        <v>-0.4775790479853322</v>
       </c>
       <c r="R40" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S40" s="11" t="n">
-        <v>-0.0127105355262755</v>
+        <v>-0.0021569131665202</v>
       </c>
     </row>
     <row r="41">
@@ -3892,49 +3901,49 @@
         <v>20</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>260.3846950650215</v>
+        <v>62.23343572299749</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>414.0340969383717</v>
+        <v>78.08924876082239</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>133.8492451190949</v>
+        <v>31.99073736116034</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>405.2383913040161</v>
+        <v>77.09978903608766</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>-4.626162910461426</v>
+        <v>-1.105679471907607</v>
       </c>
       <c r="L41" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>14.34908771514892</v>
+        <v>4.330407273928931</v>
       </c>
       <c r="N41" s="11" t="n">
-        <v>133.1576406478882</v>
+        <v>31.82543992540348</v>
       </c>
       <c r="O41" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P41" s="11" t="n">
-        <v>-5.564098358154297</v>
+        <v>-3.339307592354288</v>
       </c>
       <c r="Q41" s="11" t="n">
-        <v>-1.996027791500092</v>
+        <v>-0.4770620916587217</v>
       </c>
       <c r="R41" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S41" s="11" t="n">
-        <v>0.0107162773609161</v>
+        <v>-0.0016399568399098</v>
       </c>
     </row>
     <row r="42">
@@ -3953,49 +3962,49 @@
         <v>20</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>160.117825961113</v>
+        <v>38.2690788625987</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>42.62353708148001</v>
+        <v>54.1248919004236</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>-4.668396687507629</v>
+        <v>-1.115773586880408</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>18.59039299488067</v>
+        <v>43.99327808804691</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>-12.84860935211182</v>
+        <v>-3.070891336546801</v>
       </c>
       <c r="L42" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>6.641322326660161</v>
+        <v>2.365195409289737</v>
       </c>
       <c r="N42" s="11" t="n">
-        <v>179.6085805892944</v>
+        <v>42.92748102038586</v>
       </c>
       <c r="O42" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P42" s="11" t="n">
-        <v>17.39029598236084</v>
+        <v>7.762733502628088</v>
       </c>
       <c r="Q42" s="11" t="n">
-        <v>-1.973748588562012</v>
+        <v>-0.4717372343599454</v>
       </c>
       <c r="R42" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S42" s="11" t="n">
-        <v>0.0015257775783539</v>
+        <v>0.0036849004588664</v>
       </c>
     </row>
     <row r="43">
@@ -4014,49 +4023,49 @@
         <v>20</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>-69.30439049005508</v>
+        <v>-16.56414686664796</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>93.56266176700592</v>
+        <v>-0.7083338288230614</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>-231.8180086135864</v>
+        <v>-55.40583379865831</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>39.74287214279181</v>
+        <v>-10.29678212373099</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>-21.90240688323975</v>
+        <v>-5.234800880315427</v>
       </c>
       <c r="L43" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>7.866171646118165</v>
+        <v>0.2012858655211111</v>
       </c>
       <c r="N43" s="11" t="n">
-        <v>186.4340143203735</v>
+        <v>44.55879883374128</v>
       </c>
       <c r="O43" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P43" s="11" t="n">
-        <v>45.98612709045406</v>
+        <v>9.394051315983511</v>
       </c>
       <c r="Q43" s="11" t="n">
-        <v>-2.017989313602448</v>
+        <v>-0.4823110214154989</v>
       </c>
       <c r="R43" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S43" s="11" t="n">
-        <v>-0.0325091123580931</v>
+        <v>-0.006888886596687</v>
       </c>
     </row>
     <row r="44">
@@ -4075,49 +4084,49 @@
         <v>20</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>-127.9830656647682</v>
+        <v>-30.58868682236334</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>25.66633620858192</v>
+        <v>-14.73287378453844</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>-268.0186996936798</v>
+        <v>-64.05800661894833</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>3.370446491241466</v>
+        <v>-18.948954944021</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>-15.87874927520752</v>
+        <v>-3.795112159466424</v>
       </c>
       <c r="L44" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>3.09650135040283</v>
+        <v>1.640974586370114</v>
       </c>
       <c r="N44" s="11" t="n">
-        <v>157.9344451904297</v>
+        <v>37.74723833423272</v>
       </c>
       <c r="O44" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P44" s="11" t="n">
-        <v>19.21270618438723</v>
+        <v>2.582490816474952</v>
       </c>
       <c r="Q44" s="11" t="n">
-        <v>-2.020061886310577</v>
+        <v>-0.4828063781813043</v>
       </c>
       <c r="R44" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S44" s="11" t="n">
-        <v>-0.0133178174495696</v>
+        <v>-0.0073842433624923</v>
       </c>
     </row>
     <row r="45">
@@ -4136,49 +4145,49 @@
         <v>20</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>-111.4638327360153</v>
+        <v>-26.64049539579716</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>-228.9581216156483</v>
+        <v>-10.78468235797226</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>-253.7948040485382</v>
+        <v>-60.65841396953589</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>-230.5360143661499</v>
+        <v>-15.54936229460857</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-16.20057506561279</v>
+        <v>-3.872030369410323</v>
       </c>
       <c r="L45" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>3.289356613159186</v>
+        <v>1.564056376426215</v>
       </c>
       <c r="N45" s="11" t="n">
-        <v>160.5322671890259</v>
+        <v>38.36813269336182</v>
       </c>
       <c r="O45" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P45" s="11" t="n">
-        <v>-1.68601741790772</v>
+        <v>3.203385175604055</v>
       </c>
       <c r="Q45" s="11" t="n">
-        <v>-2.000720810890198</v>
+        <v>-0.4781837502127624</v>
       </c>
       <c r="R45" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S45" s="11" t="n">
-        <v>-0.0254464447498323</v>
+        <v>-0.0027616153939504</v>
       </c>
     </row>
     <row r="46">
@@ -4197,49 +4206,49 @@
         <v>20</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>-136.2240833461285</v>
+        <v>-32.55833731982037</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>26.64296891093255</v>
+        <v>-16.70252428199547</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>-271.4721549987793</v>
+        <v>-64.88340224636215</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>0.0887257575989224</v>
+        <v>-19.77435057143483</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-21.52084293365478</v>
+        <v>-5.143604907661277</v>
       </c>
       <c r="L46" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>8.247735595703126</v>
+        <v>0.2924818381752612</v>
       </c>
       <c r="N46" s="11" t="n">
-        <v>158.8060899734497</v>
+        <v>37.95556643724897</v>
       </c>
       <c r="O46" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P46" s="11" t="n">
-        <v>18.35820274353026</v>
+        <v>2.790818919491201</v>
       </c>
       <c r="Q46" s="11" t="n">
-        <v>-2.037175387144089</v>
+        <v>-0.4868966030459102</v>
       </c>
       <c r="R46" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S46" s="11" t="n">
-        <v>-0.0516951858997343</v>
+        <v>-0.0114744682270983</v>
       </c>
     </row>
     <row r="47">
@@ -4258,49 +4267,49 @@
         <v>20</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>326.118227750692</v>
+        <v>77.94412709146557</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>479.7676296240421</v>
+        <v>93.79994012929048</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>141.8975933754498</v>
+        <v>33.91433876086277</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>413.2867395603711</v>
+        <v>79.02339043579009</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>3.24866020503415</v>
+        <v>0.7764484237653322</v>
       </c>
       <c r="L47" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>22.2239108306445</v>
+        <v>6.21253516960187</v>
       </c>
       <c r="N47" s="11" t="n">
-        <v>182.8183934926987</v>
+        <v>43.69464471622817</v>
       </c>
       <c r="O47" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P47" s="11" t="n">
-        <v>44.09665448665621</v>
+        <v>8.529897198470401</v>
       </c>
       <c r="Q47" s="11" t="n">
-        <v>-1.846419322490692</v>
+        <v>-0.4413048093907007</v>
       </c>
       <c r="R47" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S47" s="11" t="n">
-        <v>0.1603247463703159</v>
+        <v>0.0341173254281111</v>
       </c>
     </row>
     <row r="48">
@@ -4319,49 +4328,49 @@
         <v>20</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>-133.0984706997871</v>
+        <v>-31.81129796840036</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>-250.5927595794201</v>
+        <v>-15.95548493057546</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>-257.3384035110474</v>
+        <v>-61.50535456764995</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>-234.079613828659</v>
+        <v>-16.39630289272262</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-17.56139297485351</v>
+        <v>-4.197273655557723</v>
       </c>
       <c r="L48" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>1.928538703918463</v>
+        <v>1.238813090278815</v>
       </c>
       <c r="N48" s="11" t="n">
-        <v>143.8285575866699</v>
+        <v>34.37585028362091</v>
       </c>
       <c r="O48" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P48" s="11" t="n">
-        <v>-18.38972702026368</v>
+        <v>-0.7888972341368543</v>
       </c>
       <c r="Q48" s="11" t="n">
-        <v>-2.027231800556183</v>
+        <v>-0.4845200288136191</v>
       </c>
       <c r="R48" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S48" s="11" t="n">
-        <v>-0.0519574344158171</v>
+        <v>-0.009097893994807199</v>
       </c>
     </row>
     <row r="49">
@@ -4380,49 +4389,49 @@
         <v>20</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>-144.927775901556</v>
+        <v>-34.63856976614627</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>17.939276355505</v>
+        <v>-18.78275672832137</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>-259.0070949554444</v>
+        <v>-61.90418139470467</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>12.55378580093384</v>
+        <v>-16.79512971977735</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-22.54053134918213</v>
+        <v>-5.387316288045441</v>
       </c>
       <c r="L49" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>7.228047180175782</v>
+        <v>0.0487704577910967</v>
       </c>
       <c r="N49" s="11" t="n">
-        <v>138.6479209899902</v>
+        <v>33.13764842016975</v>
       </c>
       <c r="O49" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P49" s="11" t="n">
-        <v>-1.799966239929205</v>
+        <v>-2.027099097588021</v>
       </c>
       <c r="Q49" s="11" t="n">
-        <v>-2.028070586919784</v>
+        <v>-0.484720503565914</v>
       </c>
       <c r="R49" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S49" s="11" t="n">
-        <v>-0.0425903856754299</v>
+        <v>-0.0092983687471021</v>
       </c>
     </row>
     <row r="50">
@@ -4441,49 +4450,49 @@
         <v>20</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>-144.4165625393391</v>
+        <v>-34.51638684018619</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>9.232839334011089</v>
+        <v>-18.66057380236129</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>-265.2542047023773</v>
+        <v>-63.39727645850318</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>6.134941482543979</v>
+        <v>-18.28822478357586</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-7.798470306396484</v>
+        <v>-1.863879136328032</v>
       </c>
       <c r="L50" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>11.17678031921386</v>
+        <v>3.572207609508506</v>
       </c>
       <c r="N50" s="11" t="n">
-        <v>130.6261938095093</v>
+        <v>31.22040961030337</v>
       </c>
       <c r="O50" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P50" s="11" t="n">
-        <v>-8.09554519653318</v>
+        <v>-3.944337907454401</v>
       </c>
       <c r="Q50" s="11" t="n">
-        <v>-1.990081340074539</v>
+        <v>-0.4756408556583506</v>
       </c>
       <c r="R50" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S50" s="11" t="n">
-        <v>0.0166627287864686</v>
+        <v>-0.0002187208395387</v>
       </c>
     </row>
     <row r="51">
@@ -4502,49 +4511,49 @@
         <v>20</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>-146.1054429590702</v>
+        <v>-34.92003894815254</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>-263.5997318387032</v>
+        <v>-19.06422591032764</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>-272.1914419174194</v>
+        <v>-65.05531594584593</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>-248.9326522350311</v>
+        <v>-19.94626427091861</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-15.1759651184082</v>
+        <v>-3.627142714724714</v>
       </c>
       <c r="L51" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>4.313966560363774</v>
+        <v>1.808944031111824</v>
       </c>
       <c r="N51" s="11" t="n">
-        <v>143.3184419631958</v>
+        <v>34.25392972351716</v>
       </c>
       <c r="O51" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P51" s="11" t="n">
-        <v>-18.8998426437378</v>
+        <v>-0.9108177942406072</v>
       </c>
       <c r="Q51" s="11" t="n">
-        <v>-2.05647788643837</v>
+        <v>-0.4915100110990367</v>
       </c>
       <c r="R51" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S51" s="11" t="n">
-        <v>-0.0812035202980043</v>
+        <v>-0.0160878762802247</v>
       </c>
     </row>
     <row r="52">
@@ -4563,49 +4572,49 @@
         <v>20</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>-176.4690086960792</v>
+        <v>-42.17710532889083</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>-13.60195643901824</v>
+        <v>-26.32129229106593</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>-275.8156244277954</v>
+        <v>-65.92151635463561</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>-4.254743671417202</v>
+        <v>-20.81246467970829</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-31.27376708984375</v>
+        <v>-7.474609725106059</v>
       </c>
       <c r="L52" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>-1.505188560485841</v>
+        <v>-2.038522979269521</v>
       </c>
       <c r="N52" s="11" t="n">
-        <v>132.6556671142578</v>
+        <v>31.70546537147654</v>
       </c>
       <c r="O52" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P52" s="11" t="n">
-        <v>-7.792220115661621</v>
+        <v>-3.459282146281232</v>
       </c>
       <c r="Q52" s="11" t="n">
-        <v>-2.035284292697907</v>
+        <v>-0.4864446206256946</v>
       </c>
       <c r="R52" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S52" s="11" t="n">
-        <v>-0.0498040914535522</v>
+        <v>-0.0110224858068826</v>
       </c>
     </row>
     <row r="53">
@@ -4624,49 +4633,49 @@
         <v>20</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>-167.7552683234215</v>
+        <v>-40.09447139661125</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>-153.6494018733501</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G53" s="11" t="n">
-        <v>-14.10586645007135</v>
+        <v>-24.23865835878635</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>-272.2847489833832</v>
+        <v>-65.07761686983345</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>-271.3891461849213</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>-0.89560279846188</v>
+        <v>-19.96856519490613</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-20.65841369628906</v>
+        <v>-4.937479372918036</v>
       </c>
       <c r="L53" s="11" t="n">
-        <v>-18.97525062561035</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>-1.683163070678713</v>
+        <v>0.4986073729185021</v>
       </c>
       <c r="N53" s="11" t="n">
-        <v>127.2042903900146</v>
+        <v>30.40255506453504</v>
       </c>
       <c r="O53" s="11" t="n">
-        <v>138.7217390060425</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P53" s="11" t="n">
-        <v>-11.51744861602784</v>
+        <v>-4.762192453222724</v>
       </c>
       <c r="Q53" s="11" t="n">
-        <v>-2.016396033763885</v>
+        <v>-0.48193021839481</v>
       </c>
       <c r="R53" s="11" t="n">
-        <v>-2.006744068861008</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S53" s="11" t="n">
-        <v>-0.0096519649028774</v>
+        <v>-0.006508083575998</v>
       </c>
     </row>
     <row r="54">
@@ -4685,49 +4694,49 @@
         <v>20</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>-147.7761698782444</v>
+        <v>-35.31935226535477</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>117.494288879633</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>-265.2704587578773</v>
+        <v>-19.46353922752987</v>
       </c>
       <c r="H54" s="11" t="n">
-        <v>-269.4611189365387</v>
+        <v>-64.40275309190694</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>-23.2587896823883</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>-246.2023292541504</v>
+        <v>-19.29370141697962</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-23.353635597229</v>
+        <v>-5.581652867406549</v>
       </c>
       <c r="L54" s="11" t="n">
-        <v>-19.48993167877198</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>-3.863703918457027</v>
+        <v>-0.1455661215700114</v>
       </c>
       <c r="N54" s="11" t="n">
-        <v>147.0555130004883</v>
+        <v>35.147111137784</v>
       </c>
       <c r="O54" s="11" t="n">
-        <v>162.2182846069336</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P54" s="11" t="n">
-        <v>-15.16277160644532</v>
+        <v>-0.0176363799737657</v>
       </c>
       <c r="Q54" s="11" t="n">
-        <v>-2.016928344964981</v>
+        <v>-0.4820574438252822</v>
       </c>
       <c r="R54" s="11" t="n">
-        <v>-1.975274366140366</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S54" s="11" t="n">
-        <v>-0.0416539788246155</v>
+        <v>-0.0066353090064703</v>
       </c>
     </row>
     <row r="55">
@@ -4746,49 +4755,49 @@
         <v>20</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>-120.2112501740456</v>
+        <v>-28.73117833987704</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>-162.867052257061</v>
+        <v>-15.8558130378249</v>
       </c>
       <c r="G55" s="11" t="n">
-        <v>42.65580208301544</v>
+        <v>-12.87536530205214</v>
       </c>
       <c r="H55" s="11" t="n">
-        <v>-255.0109427452088</v>
+        <v>-60.94907809397915</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>-271.5608807563782</v>
+        <v>-45.10905167492732</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>16.54993801116944</v>
+        <v>-15.84002641905182</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>-26.8661771774292</v>
+        <v>-6.421170453496463</v>
       </c>
       <c r="L55" s="11" t="n">
-        <v>-29.76857852935791</v>
+        <v>-5.436086745836538</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>2.90240135192871</v>
+        <v>-0.9850837076599248</v>
       </c>
       <c r="N55" s="11" t="n">
-        <v>163.6828376770019</v>
+        <v>39.12113711209415</v>
       </c>
       <c r="O55" s="11" t="n">
-        <v>140.4478872299194</v>
+        <v>35.16474751775777</v>
       </c>
       <c r="P55" s="11" t="n">
-        <v>23.2349504470825</v>
+        <v>3.956389594336386</v>
       </c>
       <c r="Q55" s="11" t="n">
-        <v>-2.016967928409577</v>
+        <v>-0.4820669044955966</v>
       </c>
       <c r="R55" s="11" t="n">
-        <v>-1.985480201244354</v>
+        <v>-0.4754221348188119</v>
       </c>
       <c r="S55" s="11" t="n">
-        <v>-0.031487727165222</v>
+        <v>-0.0066447696767846</v>
       </c>
     </row>
   </sheetData>

--- a/manuscript/Supplementary-Table-3.xlsx
+++ b/manuscript/Supplementary-Table-3.xlsx
@@ -523,7 +523,7 @@
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>WT reference (mean +/- SEM over three WT production replicates, kcal/mol): total -15.9 +/- 22.0; van der Waals -45.1 +/- 19.8; electrostatic -5.4 +/- 0.8; GB polar solvation 35.2 +/- 1.8; nonpolar SA -0.5 +/- 0.0. These reference uncertainties are common to every row and are not included in the per-mutation SEM values above.</t>
+          <t>WT reference (mean +/- SEM over three WT production replicates, kcal/mol): total -35.7 +/- 2.4; van der Waals -64.8 +/- 0.4; electrostatic -5.2 +/- 0.9; GB polar solvation 34.7 +/- 1.5; nonpolar SA -0.5 +/- 0.0. These reference uncertainties are common to every row and are not included in the per-mutation SEM values above.</t>
         </is>
       </c>
     </row>
@@ -607,34 +607,34 @@
         <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-18.53064004215486</v>
+        <v>-0.05238713454632915</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.3052085291463392</v>
+        <v>0.9125305541459536</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-16.19301277638393</v>
+        <v>2.235303680464857</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>2.16629130737256</v>
+        <v>1.287165527988693</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4980061295839381</v>
+        <v>0.4011915552848208</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.4642236465579634</v>
+        <v>0.4194401104123121</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-2.825328542443122</v>
+        <v>-2.681888925793678</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>1.807008353428545</v>
+        <v>1.944060948929719</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>-0.0103048529117406</v>
+        <v>-0.006993444502315667</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.001769652766679508</v>
+        <v>0.001295605404048191</v>
       </c>
     </row>
     <row r="9">
@@ -650,34 +650,34 @@
         <v>3</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>9.447353154686773</v>
+        <v>5.806655068842297</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>12.32134344256269</v>
+        <v>1.136675390260942</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>5.945996680861448</v>
+        <v>0.05490682226514328</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>14.95388723210101</v>
+        <v>0.3573697589949265</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-1.882119525231094</v>
+        <v>-2.444541331508713</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.0605810247461519</v>
+        <v>0.1841296228215511</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>5.383660908790818</v>
+        <v>8.199068884928563</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>2.849377298932321</v>
+        <v>0.7418867430189463</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>-0.0001849097343978055</v>
+        <v>-0.002779306842689667</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.003023933314929601</v>
+        <v>0.001199066715497238</v>
       </c>
     </row>
     <row r="10">
@@ -693,34 +693,34 @@
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>-1.282563381528613</v>
+        <v>4.862661685758479</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>4.850544495975907</v>
+        <v>2.103989569711314</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-4.602627973787484</v>
+        <v>1.234796681506981</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>4.430120418342435</v>
+        <v>0.5921406090367471</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.5861037244000515</v>
+        <v>-1.242455822878262</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1970587936575455</v>
+        <v>0.4336258984029359</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>3.913055703167402</v>
+        <v>4.873304862061294</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>1.244520031452134</v>
+        <v>1.422736297565476</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>-0.006887386508471233</v>
+        <v>-0.0029840349315305</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0009125816396584528</v>
+        <v>0.0009120239229448135</v>
       </c>
     </row>
     <row r="11">
@@ -736,34 +736,34 @@
         <v>3</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-5.331114113539781</v>
+        <v>3.028572749303636</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>11.55269835830883</v>
+        <v>0.3558233686394046</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-7.551795707681968</v>
+        <v>1.394224870626114</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>10.46415712516516</v>
+        <v>0.4023767148360863</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.4438682906258394</v>
+        <v>0.458141159554368</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.2312078762700519</v>
+        <v>0.11989944424127</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>1.783108977165246</v>
+        <v>1.179362931321419</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>1.34251639933909</v>
+        <v>0.5818034446178386</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>-0.006295673648896101</v>
+        <v>-0.003156212198270801</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.001548003749072663</v>
+        <v>0.001848566357390913</v>
       </c>
     </row>
     <row r="12">
@@ -779,34 +779,34 @@
         <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>3.547692319783079</v>
+        <v>-1.798187956018791</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>22.17089552634157</v>
+        <v>2.869787913409791</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>5.380576307641394</v>
+        <v>0.8491361900956633</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>22.73703606109118</v>
+        <v>1.303946904866994</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.3148552260632873</v>
+        <v>0.2121857635096009</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.8224836407232284</v>
+        <v>0.8578428573851646</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-2.142934452735216</v>
+        <v>-2.854092499873991</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.9802124465167977</v>
+        <v>2.012984547955172</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>-0.004804761186384566</v>
+        <v>-0.005417409750061267</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.005851361743682877</v>
+        <v>0.001655583966277393</v>
       </c>
     </row>
     <row r="13">
@@ -822,34 +822,34 @@
         <v>3</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>9.024683043237241</v>
+        <v>4.837298105137122</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>15.57780727423912</v>
+        <v>3.538191771528978</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>5.331482592473904</v>
+        <v>2.574334575682625</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>15.06687339724153</v>
+        <v>1.705710338418336</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3.065486422308392</v>
+        <v>1.573722768358007</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.8275715675517433</v>
+        <v>0.7950049241243449</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.6285026773971795</v>
+        <v>0.6927656758887579</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>1.341850505986341</v>
+        <v>1.388303407483793</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>-0.0007886489422325336</v>
+        <v>-0.0035249147922693</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.005650519590938755</v>
+        <v>0.00227962247929318</v>
       </c>
     </row>
     <row r="14">
@@ -865,34 +865,34 @@
         <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-18.01585682719433</v>
+        <v>1.535459002067081</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0.5616339829699335</v>
+        <v>0.5958717368130245</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-19.74534371083067</v>
+        <v>-0.2870888175385294</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7201328023198564</v>
+        <v>0.7154315619543382</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-2.541381268838624</v>
+        <v>-2.768696110550643</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.837434745639805</v>
+        <v>0.8062594292626113</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>4.280295213975291</v>
+        <v>4.598044325319189</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.4028663081073544</v>
+        <v>0.4001569595990181</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>-0.009427061500330401</v>
+        <v>-0.006800395162945834</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.002570592154330198</v>
+        <v>0.002258569129692241</v>
       </c>
     </row>
     <row r="15">
@@ -908,34 +908,34 @@
         <v>3</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>-5.727521632605104</v>
+        <v>11.4516783196498</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>3.769209160657442</v>
+        <v>1.59721610265158</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-14.6896470953052</v>
+        <v>1.840079347496129</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>4.806119109554944</v>
+        <v>1.96860684903629</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.5706663873257954</v>
+        <v>-0.7939478829446872</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.075926312132978</v>
+        <v>1.110707609483983</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>9.538830352330988</v>
+        <v>10.40831124843344</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>1.102439115779775</v>
+        <v>0.5189592006962404</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>-0.006038502305081233</v>
+        <v>-0.002764393335090767</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.002927099307363788</v>
+        <v>0.00233614573003459</v>
       </c>
     </row>
     <row r="16">
@@ -951,34 +951,34 @@
         <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>33.61459448981088</v>
+        <v>11.80088887137738</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>24.39623161790478</v>
+        <v>3.688166579680861</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>21.59017424358541</v>
+        <v>2.577057549102546</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>20.71661127300783</v>
+        <v>1.04323494136814</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>1.105399311082692</v>
+        <v>-1.214849900161836</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.25870218348284</v>
+        <v>1.005480033009597</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>10.91999375493455</v>
+        <v>10.44661019393939</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>3.398328508262209</v>
+        <v>2.373078317228523</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>-0.0009728197917731335</v>
+        <v>-0.007928971502718533</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.004085022874878571</v>
+        <v>0.002283553501600496</v>
       </c>
     </row>
     <row r="17">
@@ -994,34 +994,34 @@
         <v>3</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>-14.92594222379688</v>
+        <v>4.708979066077102</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.63615323358498</v>
+        <v>1.703570843988201</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-17.51163737115926</v>
+        <v>1.996285973046615</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.3864435086392278</v>
+        <v>0.4011029143612933</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.3876943965107117</v>
+        <v>-0.5869536608134199</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.09401933580897835</v>
+        <v>0.1004880804895641</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>2.977884248839281</v>
+        <v>3.300948379296564</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>1.465589305860082</v>
+        <v>1.463402805434132</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>-0.0044947049661834</v>
+        <v>-0.001301625452655467</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.002724143766172271</v>
+        <v>0.002638243944846054</v>
       </c>
     </row>
     <row r="18">
@@ -1037,34 +1037,34 @@
         <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>8.808845613529302</v>
+        <v>0.7028812218159478</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>24.20917910321731</v>
+        <v>2.691142254729207</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>7.255964834003255</v>
+        <v>1.280213134851391</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>20.0579645499284</v>
+        <v>0.3031386311520005</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.1944672157234109</v>
+        <v>-0.5249851979265995</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.104005604726207</v>
+        <v>0.4008642736351215</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>1.352592499260689</v>
+        <v>-0.05157293123831982</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>3.524144284890388</v>
+        <v>2.469146610198421</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.005821064541946134</v>
+        <v>-0.0007737838705304667</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.005026435812242096</v>
+        <v>0.003466839219265127</v>
       </c>
     </row>
     <row r="19">
@@ -1080,34 +1080,34 @@
         <v>3</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>19.89989946314375</v>
+        <v>0.01095575198476695</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>30.71276464247285</v>
+        <v>1.247039164893308</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>17.32599916087358</v>
+        <v>-0.9285727018863241</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>28.13893547644331</v>
+        <v>0.2601354488945047</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-2.082816759745281</v>
+        <v>-3.995449890677254</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1.560664639894519</v>
+        <v>0.3557272831386033</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>4.658130515981736</v>
+        <v>4.93600173426555</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>1.133553611658368</v>
+        <v>1.085057669130857</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>-0.001413453966284133</v>
+        <v>-0.001023389717208935</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.002002584764904485</v>
+        <v>0.0006364248773646464</v>
       </c>
     </row>
     <row r="20">
@@ -1123,34 +1123,34 @@
         <v>3</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-10.50521000089578</v>
+        <v>7.079978936704184</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>2.053105908171661</v>
+        <v>0.7631571345093443</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-16.10946654893548</v>
+        <v>1.238816338625564</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>2.590405189358803</v>
+        <v>1.133759487855488</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.3767336455783399</v>
+        <v>-0.5914720557096637</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.2771352263615741</v>
+        <v>0.1435253558759029</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>5.981285211916862</v>
+        <v>6.430232378614408</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.7972375077889301</v>
+        <v>0.6408953628997889</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>-0.0002950182988280584</v>
+        <v>0.0024022751738874</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.001020089919432299</v>
+        <v>0.0009789860536761424</v>
       </c>
     </row>
     <row r="21">
@@ -1166,34 +1166,34 @@
         <v>3</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>43.83526894414098</v>
+        <v>3.328589491250172</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>23.32146372571729</v>
+        <v>3.576682359984304</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>36.93209500013452</v>
+        <v>0.5329837996507246</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>25.47505572499026</v>
+        <v>0.5619296701445975</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2.298962849579926</v>
+        <v>-0.3742723141160604</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1.192434619495933</v>
+        <v>0.3435118249214728</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>4.60582574208577</v>
+        <v>3.174527812870231</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>4.000381532994306</v>
+        <v>2.956095979877142</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>-0.001614647659243467</v>
+        <v>-0.004649807154714366</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.003052415633014649</v>
+        <v>0.001558007027567261</v>
       </c>
     </row>
     <row r="22">
@@ -1209,34 +1209,34 @@
         <v>3</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>-14.07336014150206</v>
+        <v>5.439255060544501</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1.739868955165401</v>
+        <v>1.730108287004759</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-18.09088927002147</v>
+        <v>1.388533821610243</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>1.292908737498776</v>
+        <v>1.288153788809753</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>1.165837600323863</v>
+        <v>0.8893487637933966</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.4372420451778273</v>
+        <v>0.4411509488922162</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>2.858898303856736</v>
+        <v>3.165886294241533</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.1824404498562728</v>
+        <v>0.1638087192115123</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>-0.007206775661180334</v>
+        <v>-0.0045138191006759</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.002516748710259599</v>
+        <v>0.00214724662670713</v>
       </c>
     </row>
     <row r="23">
@@ -1252,34 +1252,34 @@
         <v>3</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>19.68723282346455</v>
+        <v>3.046446550181448</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>37.06534052455587</v>
+        <v>0.7975580696874073</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>15.27731927443004</v>
+        <v>2.593875459904709</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>31.87324351809513</v>
+        <v>0.3088581429585468</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2.500039572557261</v>
+        <v>0.7217297430187642</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>1.887769233367017</v>
+        <v>0.4448115456002675</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.904633622248509</v>
+        <v>-0.2652612326629959</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>3.331860043803003</v>
+        <v>0.5262891689295762</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.005240354228733933</v>
+        <v>-0.003897420079028833</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.01443860158012565</v>
+        <v>0.002032673444657346</v>
       </c>
     </row>
     <row r="24">
@@ -1295,34 +1295,34 @@
         <v>3</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>-21.34869733458495</v>
+        <v>-1.824827576971558</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>2.489026530391715</v>
+        <v>2.466801968448917</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-19.68231791140092</v>
+        <v>-0.1784778775742926</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.7405397859745404</v>
+        <v>0.7330247853812301</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>1.114209553783603</v>
+        <v>0.8137375665573727</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>1.656509023061626</v>
+        <v>1.660557628457894</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-2.771479282658747</v>
+        <v>-2.453963928651177</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.9408091648015244</v>
+        <v>0.8675228944046971</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>-0.009109694308882</v>
+        <v>-0.006123337303475266</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.004679800639852124</v>
+        <v>0.004675930145460181</v>
       </c>
     </row>
     <row r="25">
@@ -1338,34 +1338,34 @@
         <v>3</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-18.85918762945612</v>
+        <v>0.7449164580692091</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3.294188717214843</v>
+        <v>3.373615011604691</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-18.36743101031253</v>
+        <v>1.123483387538554</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1.278630876580305</v>
+        <v>1.286196219755488</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.210680818770478</v>
+        <v>-0.4620142622131951</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.4295403545227645</v>
+        <v>0.3999122251790134</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.2744797462867012</v>
+        <v>0.08670942771198635</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>2.520112075293427</v>
+        <v>2.558765493367119</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.006596054086417633</v>
+        <v>-0.003262094968135633</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>4.406995990587801e-05</v>
+        <v>9.765569307943893e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1522,49 +1522,49 @@
         <v>20</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>-33.80097645561052</v>
+        <v>-37.54359791288206</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>-17.94516341778561</v>
+        <v>-1.876438196368511</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>-57.34075471958285</v>
+        <v>-60.68648093880522</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>-12.23170304465552</v>
+        <v>4.067937663709216</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>-5.686679716091994</v>
+        <v>-5.38043783690434</v>
       </c>
       <c r="L2" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M2" s="11" t="n">
-        <v>-0.2505929702554557</v>
+        <v>-0.222722465254006</v>
       </c>
       <c r="N2" s="11" t="n">
-        <v>29.71029267940193</v>
+        <v>29.00487811342024</v>
       </c>
       <c r="O2" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P2" s="11" t="n">
-        <v>-5.454454838355836</v>
+        <v>-5.715682350426746</v>
       </c>
       <c r="Q2" s="11" t="n">
-        <v>-0.4838346993376146</v>
+        <v>-0.4815572505927222</v>
       </c>
       <c r="R2" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S2" s="11" t="n">
-        <v>-0.008412564518802601</v>
+        <v>-0.005971044396959</v>
       </c>
     </row>
     <row r="3">
@@ -1583,49 +1583,49 @@
         <v>20</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>-34.82875602878986</v>
+        <v>-34.86009821287546</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>-18.97294299096496</v>
+        <v>0.8070615036380886</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>-61.76302428455243</v>
+        <v>-61.86971329210508</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>-16.65397260962511</v>
+        <v>2.884705310409359</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>-4.088165336083728</v>
+        <v>-3.958934754127343</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M3" s="11" t="n">
-        <v>1.34792140975281</v>
+        <v>1.198780617522991</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>31.50651646389788</v>
+        <v>31.44957869390229</v>
       </c>
       <c r="O3" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P3" s="11" t="n">
-        <v>-3.658231053859886</v>
+        <v>-3.270981769944701</v>
       </c>
       <c r="Q3" s="11" t="n">
-        <v>-0.4840828720515818</v>
+        <v>-0.4810288605452951</v>
       </c>
       <c r="R3" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S3" s="11" t="n">
-        <v>-0.0086607372327698</v>
+        <v>-0.0054426543495319</v>
       </c>
     </row>
     <row r="4">
@@ -1644,49 +1644,49 @@
         <v>20</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>-34.52962675553891</v>
+        <v>-34.75494442742211</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>-18.673813717714</v>
+        <v>0.912215289091435</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>-64.80241434979848</v>
+        <v>-65.00115053523844</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>-19.69336267487116</v>
+        <v>-0.2467319327240034</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>-5.039396796582078</v>
+        <v>-4.930198858064856</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M4" s="11" t="n">
-        <v>0.3966899492544602</v>
+        <v>0.2275165135854777</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>35.80144778264413</v>
+        <v>35.6615578068374</v>
       </c>
       <c r="O4" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P4" s="11" t="n">
-        <v>0.6367002648863576</v>
+        <v>0.9409973429904142</v>
       </c>
       <c r="Q4" s="11" t="n">
-        <v>-0.4892633918024613</v>
+        <v>-0.4851528409562193</v>
       </c>
       <c r="R4" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S4" s="11" t="n">
-        <v>-0.0138412569836494</v>
+        <v>-0.0095666347604561</v>
       </c>
     </row>
     <row r="5">
@@ -1705,49 +1705,49 @@
         <v>20</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>14.48276550945315</v>
+        <v>-29.09983324775578</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>30.33857854727805</v>
+        <v>6.567326468757763</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>-12.77823166113282</v>
+        <v>-64.05311422769695</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>32.33082001379449</v>
+        <v>0.7013043748174823</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>-7.217783499402252</v>
+        <v>-7.667348533869563</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>-1.781696753565714</v>
+        <v>-2.509633162219229</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>34.95419506361106</v>
+        <v>43.09737288017346</v>
       </c>
       <c r="O5" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P5" s="11" t="n">
-        <v>-0.2105524541467076</v>
+        <v>8.376812416326473</v>
       </c>
       <c r="Q5" s="11" t="n">
-        <v>-0.4754143936228342</v>
+        <v>-0.4767433663627157</v>
       </c>
       <c r="R5" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S5" s="11" t="n">
-        <v>7.741195977684079e-06</v>
+        <v>-0.0011571601669525</v>
       </c>
     </row>
     <row r="6">
@@ -1766,49 +1766,49 @@
         <v>20</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>-5.535325348149295</v>
+        <v>-32.09613738435587</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>10.32048768967561</v>
+        <v>3.571022332157675</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>-40.15968651662137</v>
+        <v>-65.28684515663123</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>4.949365158305952</v>
+        <v>-0.5324265541167961</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>-7.309709634653241</v>
+        <v>-7.883611160824091</v>
       </c>
       <c r="L6" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>-1.873622888816703</v>
+        <v>-2.725895789173757</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>42.40453922497839</v>
+        <v>41.55502514789027</v>
       </c>
       <c r="O6" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P6" s="11" t="n">
-        <v>7.239791707220618</v>
+        <v>6.834464684043283</v>
       </c>
       <c r="Q6" s="11" t="n">
-        <v>-0.4704684218530673</v>
+        <v>-0.4807062147908184</v>
       </c>
       <c r="R6" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S6" s="11" t="n">
-        <v>0.0049537129657445</v>
+        <v>-0.0051200085950551</v>
       </c>
     </row>
     <row r="7">
@@ -1827,49 +1827,49 @@
         <v>20</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>-28.17281981071824</v>
+        <v>-28.38554331090209</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>-12.31700677289334</v>
+        <v>7.281616405611455</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>-64.55124680444342</v>
+        <v>-64.75857595641969</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>-19.4421951295161</v>
+        <v>-0.0041573539052564</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>-7.427125679147403</v>
+        <v>-7.255810414783486</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>-1.991038933310866</v>
+        <v>-2.098095043133152</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>44.28649099105631</v>
+        <v>44.10649001826292</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P7" s="11" t="n">
-        <v>9.121743473298544</v>
+        <v>9.385929554415933</v>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>-0.4809383181837275</v>
+        <v>-0.4776469579618246</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>-0.0055161833649156</v>
+        <v>-0.0020607517660614</v>
       </c>
     </row>
     <row r="8">
@@ -1888,49 +1888,49 @@
         <v>20</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>-26.41977778926178</v>
+        <v>-32.49580928783035</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>-10.56396475143688</v>
+        <v>3.171350428683198</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>-57.09187631169422</v>
+        <v>-63.37597625990824</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>-11.9828246367669</v>
+        <v>1.378442342606192</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>-6.097663155477316</v>
+        <v>-6.088023636963281</v>
       </c>
       <c r="L8" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>-0.6615764096407784</v>
+        <v>-0.9303082653129467</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>37.25187062761296</v>
+        <v>37.44843448325279</v>
       </c>
       <c r="O8" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P8" s="11" t="n">
-        <v>2.087123109855192</v>
+        <v>2.727874019405803</v>
       </c>
       <c r="Q8" s="11" t="n">
-        <v>-0.4821089497031946</v>
+        <v>-0.4802438742116122</v>
       </c>
       <c r="R8" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S8" s="11" t="n">
-        <v>-0.0066868148843827</v>
+        <v>-0.0046576680158489</v>
       </c>
     </row>
     <row r="9">
@@ -1949,49 +1949,49 @@
         <v>20</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>-10.05328681683221</v>
+        <v>-33.29574455872874</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>5.802526220992689</v>
+        <v>2.37141515778481</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>-41.77570994907765</v>
+        <v>-64.6094899104998</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>3.333341725849671</v>
+        <v>0.1449286920146306</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>-6.319453246734795</v>
+        <v>-7.256971158084427</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>-0.8833665008982567</v>
+        <v>-2.099255786434092</v>
       </c>
       <c r="N9" s="11" t="n">
-        <v>38.52585725073149</v>
+        <v>39.04782178069163</v>
       </c>
       <c r="O9" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P9" s="11" t="n">
-        <v>3.361109732973723</v>
+        <v>4.327261316844648</v>
       </c>
       <c r="Q9" s="11" t="n">
-        <v>-0.4839808717512492</v>
+        <v>-0.477105270836139</v>
       </c>
       <c r="R9" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S9" s="11" t="n">
-        <v>-0.0085587369324373</v>
+        <v>-0.0015190646403758</v>
       </c>
     </row>
     <row r="10">
@@ -2010,49 +2010,49 @@
         <v>20</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>-14.94206465196655</v>
+        <v>-26.62194024570612</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.9137483858583516</v>
+        <v>9.045219470807428</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>-50.26745268537255</v>
+        <v>-62.57339959261432</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>-5.158401010445225</v>
+        <v>2.181019009900119</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>-5.649455008497657</v>
+        <v>-5.855518788538082</v>
       </c>
       <c r="L10" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>-0.2133682626611195</v>
+        <v>-0.6978034168877478</v>
       </c>
       <c r="N10" s="11" t="n">
-        <v>41.45568178443106</v>
+        <v>42.28533971378042</v>
       </c>
       <c r="O10" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P10" s="11" t="n">
-        <v>6.29093426667329</v>
+        <v>7.56477924993343</v>
       </c>
       <c r="Q10" s="11" t="n">
-        <v>-0.4808387425274056</v>
+        <v>-0.47836157833413</v>
       </c>
       <c r="R10" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S10" s="11" t="n">
-        <v>-0.0054166077085937</v>
+        <v>-0.0027753721383668</v>
       </c>
     </row>
     <row r="11">
@@ -2071,49 +2071,49 @@
         <v>20</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>1.915377924079877</v>
+        <v>-31.98635599529191</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>17.77119096190478</v>
+        <v>3.68080372122164</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>-31.74678686699949</v>
+        <v>-63.47689049093174</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>13.36226480792783</v>
+        <v>1.277528111582697</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>-5.435428564680694</v>
+        <v>-4.905450335453543</v>
       </c>
       <c r="L11" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.0006581811558437</v>
+        <v>0.2522650361967908</v>
       </c>
       <c r="N11" s="11" t="n">
-        <v>39.58129803035729</v>
+        <v>36.87711985457695</v>
       </c>
       <c r="O11" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P11" s="11" t="n">
-        <v>4.416550512599521</v>
+        <v>2.156559390729967</v>
       </c>
       <c r="Q11" s="11" t="n">
-        <v>-0.483704674597224</v>
+        <v>-0.4811350234835826</v>
       </c>
       <c r="R11" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S11" s="11" t="n">
-        <v>-0.008282539778412</v>
+        <v>-0.0055488172878194</v>
       </c>
     </row>
     <row r="12">
@@ -2132,49 +2132,49 @@
         <v>20</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>-32.41075229177511</v>
+        <v>-32.71817278261615</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>-16.55493925395021</v>
+        <v>2.948986933897394</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>-62.44906706746175</v>
+        <v>-62.61227486159108</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>-17.34001539253443</v>
+        <v>2.142143740923359</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>-4.656399367644272</v>
+        <v>-4.490151895423597</v>
       </c>
       <c r="L12" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.779687378192266</v>
+        <v>0.6675634762267375</v>
       </c>
       <c r="N12" s="11" t="n">
-        <v>35.17749478210683</v>
+        <v>34.8642410272394</v>
       </c>
       <c r="O12" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P12" s="11" t="n">
-        <v>0.0127472643490591</v>
+        <v>0.1436805633924152</v>
       </c>
       <c r="Q12" s="11" t="n">
-        <v>-0.4827806387759075</v>
+        <v>-0.4799870528408947</v>
       </c>
       <c r="R12" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S12" s="11" t="n">
-        <v>-0.0073585039570955</v>
+        <v>-0.0044008466451315</v>
       </c>
     </row>
     <row r="13">
@@ -2193,49 +2193,49 @@
         <v>20</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>-33.06540708639881</v>
+        <v>-33.21123212372167</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>-17.20959404857391</v>
+        <v>2.455927592791873</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>-63.78668821336662</v>
+        <v>-63.99141584314215</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>-18.6776365384393</v>
+        <v>0.7630027593722843</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>-4.884827433307129</v>
+        <v>-4.703120405410758</v>
       </c>
       <c r="L13" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.5512593125294085</v>
+        <v>0.4545949662395756</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>36.08477667230493</v>
+        <v>35.95840930368886</v>
       </c>
       <c r="O13" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>0.9200291545471586</v>
+        <v>1.237848839841874</v>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>-0.4786681120299927</v>
+        <v>-0.4751051788576246</v>
       </c>
       <c r="R13" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S13" s="11" t="n">
-        <v>-0.0032459772111808</v>
+        <v>0.0004810273381385</v>
       </c>
     </row>
     <row r="14">
@@ -2254,49 +2254,49 @@
         <v>20</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>32.01978441833538</v>
+        <v>-43.10998509648838</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>47.87559745616029</v>
+        <v>-7.442825379974835</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>5.739793910806995</v>
+        <v>-66.41449406147009</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>50.84884558573432</v>
+        <v>-1.66007545895566</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>-4.350508968871137</v>
+        <v>-4.067670983253389</v>
       </c>
       <c r="L14" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>1.085577776965401</v>
+        <v>1.090044388396945</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>31.09903376599343</v>
+        <v>27.84993564193609</v>
       </c>
       <c r="O14" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P14" s="11" t="n">
-        <v>-4.065713751764342</v>
+        <v>-6.870624821910898</v>
       </c>
       <c r="Q14" s="11" t="n">
-        <v>-0.4685342895939063</v>
+        <v>-0.4777556937009836</v>
       </c>
       <c r="R14" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S14" s="11" t="n">
-        <v>0.0068878452249055</v>
+        <v>-0.0021694875052204</v>
       </c>
     </row>
     <row r="15">
@@ -2315,49 +2315,49 @@
         <v>20</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>-35.43303373552872</v>
+        <v>-35.54336182561863</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>-19.57722069770382</v>
+        <v>0.1237978908949202</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>-61.83348905515944</v>
+        <v>-62.03527000088295</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>-16.72443738023212</v>
+        <v>2.719148601631488</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>-6.765134840576871</v>
+        <v>-6.661058419226562</v>
       </c>
       <c r="L15" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>-1.329048094740333</v>
+        <v>-1.503343047576228</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>33.65208468975118</v>
+        <v>33.63615195792218</v>
       </c>
       <c r="O15" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P15" s="11" t="n">
-        <v>-1.512662828006583</v>
+        <v>-1.084408505924806</v>
       </c>
       <c r="Q15" s="11" t="n">
-        <v>-0.4864945295435977</v>
+        <v>-0.4831853634312776</v>
       </c>
       <c r="R15" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S15" s="11" t="n">
-        <v>-0.0110723947247857</v>
+        <v>-0.0075991572355144</v>
       </c>
     </row>
     <row r="16">
@@ -2376,49 +2376,49 @@
         <v>20</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>-33.51111283693213</v>
+        <v>-33.74269609549</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>-17.65529979910723</v>
+        <v>1.924463621023541</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>-63.09173095750534</v>
+        <v>-63.26608317490327</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>-17.98267928257802</v>
+        <v>1.488335427611162</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>-4.248050749871744</v>
+        <v>-4.107859421942248</v>
       </c>
       <c r="L16" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>1.188035995964794</v>
+        <v>1.049855949708086</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>34.31432073932304</v>
+        <v>34.11331629206072</v>
       </c>
       <c r="O16" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P16" s="11" t="n">
-        <v>-0.8504267784347235</v>
+        <v>-0.6072441717862702</v>
       </c>
       <c r="Q16" s="11" t="n">
-        <v>-0.4856518688780855</v>
+        <v>-0.4820697907052122</v>
       </c>
       <c r="R16" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S16" s="11" t="n">
-        <v>-0.0102297340592735</v>
+        <v>-0.006483584509449</v>
       </c>
     </row>
     <row r="17">
@@ -2437,49 +2437,49 @@
         <v>20</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>24.05749444153523</v>
+        <v>-29.04065097873226</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>39.91330747936013</v>
+        <v>6.62650873778129</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>-10.65518238348441</v>
+        <v>-59.90483063441364</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>34.45386929144291</v>
+        <v>4.849587968100792</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-1.070300206171623</v>
+        <v>-4.037275460294275</v>
       </c>
       <c r="L17" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>4.365786539664915</v>
+        <v>1.120439911356059</v>
       </c>
       <c r="N17" s="11" t="n">
-        <v>36.24815083826477</v>
+        <v>35.3787468450703</v>
       </c>
       <c r="O17" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P17" s="11" t="n">
-        <v>1.083403320507003</v>
+        <v>0.6581863812233166</v>
       </c>
       <c r="Q17" s="11" t="n">
-        <v>-0.4651738070735055</v>
+        <v>-0.4772917290946493</v>
       </c>
       <c r="R17" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S17" s="11" t="n">
-        <v>0.0102483277453064</v>
+        <v>-0.0017055228988861</v>
       </c>
     </row>
     <row r="18">
@@ -2498,49 +2498,49 @@
         <v>20</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-18.75068707886663</v>
+        <v>-37.65366982693976</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>-2.894874041041728</v>
+        <v>-1.986510110426217</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>-47.63451253934755</v>
+        <v>-65.51901937381633</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>-2.525460864420232</v>
+        <v>-0.7646007713019003</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-3.907620610516112</v>
+        <v>-4.677199452741126</v>
       </c>
       <c r="L18" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>1.528466135320426</v>
+        <v>0.4805159189092078</v>
       </c>
       <c r="N18" s="11" t="n">
-        <v>33.27527866764688</v>
+        <v>33.02619023031303</v>
       </c>
       <c r="O18" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P18" s="11" t="n">
-        <v>-1.889468850110887</v>
+        <v>-1.694370233533952</v>
       </c>
       <c r="Q18" s="11" t="n">
-        <v>-0.4838325966498591</v>
+        <v>-0.4836412306953342</v>
       </c>
       <c r="R18" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S18" s="11" t="n">
-        <v>-0.008410461831047201</v>
+        <v>-0.008055024499571</v>
       </c>
     </row>
     <row r="19">
@@ -2559,49 +2559,49 @@
         <v>20</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-25.80019734643158</v>
+        <v>-25.79526402845726</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>-9.944384308606676</v>
+        <v>9.871895688056291</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>-61.04301232452829</v>
+        <v>-61.11640207226545</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>-15.93396064960097</v>
+        <v>3.638016530248983</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-2.133880153896703</v>
+        <v>-2.037502896841582</v>
       </c>
       <c r="L19" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>3.302206591939834</v>
+        <v>3.120212474808753</v>
       </c>
       <c r="N19" s="11" t="n">
-        <v>37.85632107955319</v>
+        <v>37.8350413438239</v>
       </c>
       <c r="O19" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P19" s="11" t="n">
-        <v>2.691573561795423</v>
+        <v>3.114480879976909</v>
       </c>
       <c r="Q19" s="11" t="n">
-        <v>-0.4796259475597688</v>
+        <v>-0.476400403174114</v>
       </c>
       <c r="R19" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S19" s="11" t="n">
-        <v>-0.0042038127409568</v>
+        <v>-0.0008141969783508</v>
       </c>
     </row>
     <row r="20">
@@ -2620,49 +2620,49 @@
         <v>20</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-32.85223595641311</v>
+        <v>-33.05611532149674</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-16.99642291858821</v>
+        <v>2.611044395016805</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>-63.59924824470315</v>
+        <v>-63.74071036001545</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>-18.49019656977583</v>
+        <v>1.013708242498986</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-9.005719252343843</v>
+        <v>-8.937913586252879</v>
       </c>
       <c r="L20" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>-3.569632506507305</v>
+        <v>-3.780198214602545</v>
       </c>
       <c r="N20" s="11" t="n">
-        <v>40.23869580110217</v>
+        <v>40.10617960365506</v>
       </c>
       <c r="O20" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P20" s="11" t="n">
-        <v>5.073948283344407</v>
+        <v>5.385619139808078</v>
       </c>
       <c r="Q20" s="11" t="n">
-        <v>-0.4859642604682914</v>
+        <v>-0.4836709788834843</v>
       </c>
       <c r="R20" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S20" s="11" t="n">
-        <v>-0.0105421256494794</v>
+        <v>-0.008084772687721099</v>
       </c>
     </row>
     <row r="21">
@@ -2681,49 +2681,49 @@
         <v>20</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-34.78987680936862</v>
+        <v>-35.11393286354969</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>-18.93406377154372</v>
+        <v>0.5532268529638529</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>-64.87022718097694</v>
+        <v>-65.17569648099004</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>-19.76117550604961</v>
+        <v>-0.4212778784756068</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-8.608294536233176</v>
+        <v>-8.508231311519568</v>
       </c>
       <c r="L21" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>-3.172207790396638</v>
+        <v>-3.350515939869234</v>
       </c>
       <c r="N21" s="11" t="n">
-        <v>39.16859015907885</v>
+        <v>39.04798885034557</v>
       </c>
       <c r="O21" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P21" s="11" t="n">
-        <v>4.003842641321086</v>
+        <v>4.327428386498582</v>
       </c>
       <c r="Q21" s="11" t="n">
-        <v>-0.4799452512373659</v>
+        <v>-0.4779939213856684</v>
       </c>
       <c r="R21" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S21" s="11" t="n">
-        <v>-0.004523116418554</v>
+        <v>-0.0024077151899052</v>
       </c>
     </row>
     <row r="22">
@@ -2742,49 +2742,49 @@
         <v>20</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-33.97289682927596</v>
+        <v>-34.22505395829296</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-18.11708379145106</v>
+        <v>1.442105758220585</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>-66.09371073159387</v>
+        <v>-66.2081154191534</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>-20.98465905666655</v>
+        <v>-1.453696816638967</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-6.318390255448467</v>
+        <v>-6.333089548830483</v>
       </c>
       <c r="L22" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>-0.8823035096119289</v>
+        <v>-1.175374177180148</v>
       </c>
       <c r="N22" s="11" t="n">
-        <v>38.92784223501815</v>
+        <v>38.80164591349789</v>
       </c>
       <c r="O22" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P22" s="11" t="n">
-        <v>3.76309471726038</v>
+        <v>4.081085449650907</v>
       </c>
       <c r="Q22" s="11" t="n">
-        <v>-0.4886380772517698</v>
+        <v>-0.4854949038069744</v>
       </c>
       <c r="R22" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S22" s="11" t="n">
-        <v>-0.0132159424329578</v>
+        <v>-0.009908697611211201</v>
       </c>
     </row>
     <row r="23">
@@ -2803,49 +2803,49 @@
         <v>20</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-14.31609407551658</v>
+        <v>-21.78320449715924</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>1.539718962308325</v>
+        <v>13.8839552193543</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>-50.18916038892464</v>
+        <v>-58.9858808087252</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>-5.080108713997319</v>
+        <v>5.768537793789235</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-6.169474877089432</v>
+        <v>-6.466641502156</v>
       </c>
       <c r="L23" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>-0.7333881312528945</v>
+        <v>-1.308926130505666</v>
       </c>
       <c r="N23" s="11" t="n">
-        <v>42.52969074431615</v>
+        <v>44.15207367326288</v>
       </c>
       <c r="O23" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P23" s="11" t="n">
-        <v>7.364943226558381</v>
+        <v>9.43151320941589</v>
       </c>
       <c r="Q23" s="11" t="n">
-        <v>-0.4871495538186389</v>
+        <v>-0.4827558595409356</v>
       </c>
       <c r="R23" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S23" s="11" t="n">
-        <v>-0.0117274189998269</v>
+        <v>-0.0071696533451724</v>
       </c>
     </row>
     <row r="24">
@@ -2864,49 +2864,49 @@
         <v>20</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-26.95224275153636</v>
+        <v>-27.22502990804648</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>-11.09642971371146</v>
+        <v>8.442129808467065</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>-64.80075394446261</v>
+        <v>-65.10583364273928</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>-19.69170226953529</v>
+        <v>-0.3514150402248504</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-7.783615475175029</v>
+        <v>-7.565567257525522</v>
       </c>
       <c r="L24" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>-2.347528729338491</v>
+        <v>-2.407851885875188</v>
       </c>
       <c r="N24" s="11" t="n">
-        <v>46.109546644054</v>
+        <v>45.92117063174056</v>
       </c>
       <c r="O24" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P24" s="11" t="n">
-        <v>10.94479912629623</v>
+        <v>11.20061016789357</v>
       </c>
       <c r="Q24" s="11" t="n">
-        <v>-0.47741997595271</v>
+        <v>-0.4747996395222315</v>
       </c>
       <c r="R24" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S24" s="11" t="n">
-        <v>-0.0019978411338981</v>
+        <v>0.0007865666735316</v>
       </c>
     </row>
     <row r="25">
@@ -2925,49 +2925,49 @@
         <v>20</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-23.48166718423708</v>
+        <v>-23.63820978538552</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>-7.625854146412177</v>
+        <v>12.02894993112802</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>-64.40618197731033</v>
+        <v>-64.65130331359043</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>-19.297130302383</v>
+        <v>0.1031152889240019</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-4.067169047222539</v>
+        <v>-3.822781004103541</v>
       </c>
       <c r="L25" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>1.368917698613999</v>
+        <v>1.334934367546793</v>
       </c>
       <c r="N25" s="11" t="n">
-        <v>45.47149622189612</v>
+        <v>45.31337083183784</v>
       </c>
       <c r="O25" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P25" s="11" t="n">
-        <v>10.30674870413835</v>
+        <v>10.59281036799085</v>
       </c>
       <c r="Q25" s="11" t="n">
-        <v>-0.4798123816003307</v>
+        <v>-0.4774962995293947</v>
       </c>
       <c r="R25" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S25" s="11" t="n">
-        <v>-0.0043902467815187</v>
+        <v>-0.0019100933336315</v>
       </c>
     </row>
     <row r="26">
@@ -2986,49 +2986,49 @@
         <v>20</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>37.40593669063502</v>
+        <v>-18.24107440237752</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>53.26174972845993</v>
+        <v>17.42608531413602</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>-10.72052023720787</v>
+        <v>-61.64262997512676</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>34.38853143771945</v>
+        <v>3.111788627387675</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-3.672539982695424</v>
+        <v>-4.498734262847835</v>
       </c>
       <c r="L26" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>1.763546763141114</v>
+        <v>0.6589811088024993</v>
       </c>
       <c r="N26" s="11" t="n">
-        <v>52.26819624636415</v>
+        <v>48.3882125659381</v>
       </c>
       <c r="O26" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P26" s="11" t="n">
-        <v>17.10344872860638</v>
+        <v>13.66765210209111</v>
       </c>
       <c r="Q26" s="11" t="n">
-        <v>-0.4691993358258308</v>
+        <v>-0.4879227303410123</v>
       </c>
       <c r="R26" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S26" s="11" t="n">
-        <v>0.0062227989929811</v>
+        <v>-0.0123365241452491</v>
       </c>
     </row>
     <row r="27">
@@ -3047,49 +3047,49 @@
         <v>20</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>46.61362572051371</v>
+        <v>-22.54660674501336</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>62.46943875833861</v>
+        <v>13.12055297150018</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>4.209432712476523</v>
+        <v>-60.69814008335682</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>49.31848438740384</v>
+        <v>4.056278519157615</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>-2.555450107581757</v>
+        <v>-7.941571199197357</v>
       </c>
       <c r="L27" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>2.880636638254781</v>
+        <v>-2.783855827547023</v>
       </c>
       <c r="N27" s="11" t="n">
-        <v>45.43628482928012</v>
+        <v>46.57545225912024</v>
       </c>
       <c r="O27" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P27" s="11" t="n">
-        <v>10.27153731152235</v>
+        <v>11.85489179527325</v>
       </c>
       <c r="Q27" s="11" t="n">
-        <v>-0.476641713661172</v>
+        <v>-0.4823477215794258</v>
       </c>
       <c r="R27" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S27" s="11" t="n">
-        <v>-0.00121957884236</v>
+        <v>-0.0067615153836625</v>
       </c>
     </row>
     <row r="28">
@@ -3108,49 +3108,49 @@
         <v>20</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>-30.74321805519082</v>
+        <v>-30.8111313880176</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>-14.88740501736592</v>
+        <v>4.856028328495942</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>-64.04554476929439</v>
+        <v>-64.19131310175209</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>-18.93649309436707</v>
+        <v>0.5631055007623473</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>-6.764072213984356</v>
+        <v>-6.677390353391319</v>
       </c>
       <c r="L28" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>-1.327985468147818</v>
+        <v>-1.519674981740985</v>
       </c>
       <c r="N28" s="11" t="n">
-        <v>40.54974274243269</v>
+        <v>40.53784714830081</v>
       </c>
       <c r="O28" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P28" s="11" t="n">
-        <v>5.384995224674924</v>
+        <v>5.817286684453819</v>
       </c>
       <c r="Q28" s="11" t="n">
-        <v>-0.4833438143447525</v>
+        <v>-0.4802750811750073</v>
       </c>
       <c r="R28" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S28" s="11" t="n">
-        <v>-0.0079216795259405</v>
+        <v>-0.004688874979244</v>
       </c>
     </row>
     <row r="29">
@@ -3169,49 +3169,49 @@
         <v>20</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>-28.11579520513177</v>
+        <v>-28.18432505777292</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>-12.25998216730687</v>
+        <v>7.482834658740629</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>-61.86828157413985</v>
+        <v>-61.97343171829943</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>-16.75922989921253</v>
+        <v>2.780986884215004</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>-5.773967082824124</v>
+        <v>-5.590393793305743</v>
       </c>
       <c r="L29" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>-0.3378803369875864</v>
+        <v>-0.4326784216554085</v>
       </c>
       <c r="N29" s="11" t="n">
-        <v>40.01090280412487</v>
+        <v>39.86100418845736</v>
       </c>
       <c r="O29" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P29" s="11" t="n">
-        <v>4.846155286367107</v>
+        <v>5.140443724610378</v>
       </c>
       <c r="Q29" s="11" t="n">
-        <v>-0.484449352292668</v>
+        <v>-0.4815037346250923</v>
       </c>
       <c r="R29" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S29" s="11" t="n">
-        <v>-0.009027217473856</v>
+        <v>-0.005917528429329</v>
       </c>
     </row>
     <row r="30">
@@ -3230,49 +3230,49 @@
         <v>20</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>-33.75805051958127</v>
+        <v>-34.05851287210012</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>-17.90223748175637</v>
+        <v>1.608646844413428</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>-62.84383069260853</v>
+        <v>-63.00614319543035</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>-17.73477901768121</v>
+        <v>1.748275407084087</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>-5.691660065951812</v>
+        <v>-5.710258788331772</v>
       </c>
       <c r="L30" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>-0.2555733201152739</v>
+        <v>-0.5525434166814378</v>
       </c>
       <c r="N30" s="11" t="n">
-        <v>35.25247259304127</v>
+        <v>35.13025515508013</v>
       </c>
       <c r="O30" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P30" s="11" t="n">
-        <v>0.087725075283501</v>
+        <v>0.4096946912331418</v>
       </c>
       <c r="Q30" s="11" t="n">
-        <v>-0.4750323540621916</v>
+        <v>-0.472366043418133</v>
       </c>
       <c r="R30" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S30" s="11" t="n">
-        <v>0.0003897807566203</v>
+        <v>0.0032201627776302</v>
       </c>
     </row>
     <row r="31">
@@ -3291,49 +3291,49 @@
         <v>20</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>-30.4714200601523</v>
+        <v>-30.6317040214363</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>-14.6156070223274</v>
+        <v>5.03545569507725</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>-63.14995487151137</v>
+        <v>-63.29482297467368</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>-18.04090319658405</v>
+        <v>1.459595627840756</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-6.005716278265813</v>
+        <v>-5.933354515753748</v>
       </c>
       <c r="L31" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>-0.5696295324292748</v>
+        <v>-0.7756391441034136</v>
       </c>
       <c r="N31" s="11" t="n">
-        <v>39.164519902625</v>
+        <v>39.07326718589316</v>
       </c>
       <c r="O31" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P31" s="11" t="n">
-        <v>3.999772384867235</v>
+        <v>4.352706722046172</v>
       </c>
       <c r="Q31" s="11" t="n">
-        <v>-0.4802688130001264</v>
+        <v>-0.4767937169020308</v>
       </c>
       <c r="R31" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S31" s="11" t="n">
-        <v>-0.0048466781813145</v>
+        <v>-0.0012075107062676</v>
       </c>
     </row>
     <row r="32">
@@ -3352,49 +3352,49 @@
         <v>20</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>-40.21922734710272</v>
+        <v>-40.34333539775993</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>-24.36341430927782</v>
+        <v>-4.676175681246384</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>-62.87473111945858</v>
+        <v>-63.16150952874906</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>-17.76567944453126</v>
+        <v>1.592909073765369</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-6.708700934969899</v>
+        <v>-6.480474057332458</v>
       </c>
       <c r="L32" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>-1.272614189133361</v>
+        <v>-1.322758685682124</v>
       </c>
       <c r="N32" s="11" t="n">
-        <v>29.83951094501561</v>
+        <v>29.7713180772433</v>
       </c>
       <c r="O32" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P32" s="11" t="n">
-        <v>-5.32523657274216</v>
+        <v>-4.949242386603682</v>
       </c>
       <c r="Q32" s="11" t="n">
-        <v>-0.4753062376898515</v>
+        <v>-0.472669888921723</v>
       </c>
       <c r="R32" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S32" s="11" t="n">
-        <v>0.0001158971289604</v>
+        <v>0.0029163172740401</v>
       </c>
     </row>
     <row r="33">
@@ -3413,49 +3413,49 @@
         <v>20</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>-21.00513213907099</v>
+        <v>-32.4361502624355</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>-5.149319101246089</v>
+        <v>3.231009454078048</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>-52.49744494148239</v>
+        <v>-63.18072566293289</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>-7.38839326655507</v>
+        <v>1.573692939581541</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-5.937148188997636</v>
+        <v>-5.352694841275529</v>
       </c>
       <c r="L33" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>-0.501061443161098</v>
+        <v>-0.1949794696251947</v>
       </c>
       <c r="N33" s="11" t="n">
-        <v>37.90337770436507</v>
+        <v>36.57039155467746</v>
       </c>
       <c r="O33" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P33" s="11" t="n">
-        <v>2.738630186607303</v>
+        <v>1.84983109083047</v>
       </c>
       <c r="Q33" s="11" t="n">
-        <v>-0.4739167129560365</v>
+        <v>-0.4731213129045402</v>
       </c>
       <c r="R33" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S33" s="11" t="n">
-        <v>0.0015054218627754</v>
+        <v>0.0024648932912229</v>
       </c>
     </row>
     <row r="34">
@@ -3474,49 +3474,49 @@
         <v>20</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>40.08345721328691</v>
+        <v>-32.11334982389737</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>55.93927025111181</v>
+        <v>3.553809892616179</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>1.812915538168774</v>
+        <v>-64.08038121130717</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>46.9219672130961</v>
+        <v>0.6740373912072641</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-3.079009466371846</v>
+        <v>-5.214932810122814</v>
       </c>
       <c r="L34" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>2.357077279464692</v>
+        <v>-0.0572174384724801</v>
       </c>
       <c r="N34" s="11" t="n">
-        <v>41.80913140167469</v>
+        <v>37.66525296590524</v>
       </c>
       <c r="O34" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P34" s="11" t="n">
-        <v>6.644383883916923</v>
+        <v>2.944692502058253</v>
       </c>
       <c r="Q34" s="11" t="n">
-        <v>-0.4595802601847092</v>
+        <v>-0.4832887683726177</v>
       </c>
       <c r="R34" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S34" s="11" t="n">
-        <v>0.0158418746341026</v>
+        <v>-0.0077025621768544</v>
       </c>
     </row>
     <row r="35">
@@ -3535,49 +3535,49 @@
         <v>20</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>-16.09289822227412</v>
+        <v>-37.43642670715465</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>-0.2370851844492207</v>
+        <v>-1.769266990641107</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>-44.87444465520505</v>
+        <v>-65.98428133486048</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>0.2346070197222758</v>
+        <v>-1.229862732346049</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-9.522152721995834</v>
+        <v>-9.575069981870502</v>
       </c>
       <c r="L35" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>-4.086065976159296</v>
+        <v>-4.417354610220168</v>
       </c>
       <c r="N35" s="11" t="n">
-        <v>38.78346139112804</v>
+        <v>38.60072027428884</v>
       </c>
       <c r="O35" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P35" s="11" t="n">
-        <v>3.618713873370275</v>
+        <v>3.880159810441853</v>
       </c>
       <c r="Q35" s="11" t="n">
-        <v>-0.4797622362012844</v>
+        <v>-0.4777956647125301</v>
       </c>
       <c r="R35" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S35" s="11" t="n">
-        <v>-0.0043401013824724</v>
+        <v>-0.0022094585167669</v>
       </c>
     </row>
     <row r="36">
@@ -3596,49 +3596,49 @@
         <v>20</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>64.36890295740523</v>
+        <v>-33.25333839100333</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>80.22471599523013</v>
+        <v>2.413821325510213</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>27.19875348457643</v>
+        <v>-65.16501865139527</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>72.30780515950374</v>
+        <v>-0.4106000488808377</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-4.444293902891315</v>
+        <v>-9.438320759405906</v>
       </c>
       <c r="L36" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.9917928429452232</v>
+        <v>-4.280605387755572</v>
       </c>
       <c r="N36" s="11" t="n">
-        <v>42.08744771166012</v>
+        <v>41.82641763190238</v>
       </c>
       <c r="O36" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P36" s="11" t="n">
-        <v>6.922700193902351</v>
+        <v>7.105857168055394</v>
       </c>
       <c r="Q36" s="11" t="n">
-        <v>-0.4730043359399981</v>
+        <v>-0.4764166121045216</v>
       </c>
       <c r="R36" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S36" s="11" t="n">
-        <v>0.0024177988788138</v>
+        <v>-0.0008304059087583</v>
       </c>
     </row>
     <row r="37">
@@ -3657,49 +3657,49 @@
         <v>20</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>-36.14374545917456</v>
+        <v>-36.27884679542835</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>-20.28793242134966</v>
+        <v>-0.6116870789148052</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>-65.6734663715326</v>
+        <v>-65.89967392694652</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>-20.56441469660528</v>
+        <v>-1.145255324432085</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-8.590263891858307</v>
+        <v>-8.446105045706355</v>
       </c>
       <c r="L37" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>-3.154177146021769</v>
+        <v>-3.288389674056021</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>38.59772499843035</v>
+        <v>38.54254868814639</v>
       </c>
       <c r="O37" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P37" s="11" t="n">
-        <v>3.432977480672584</v>
+        <v>3.821988224299403</v>
       </c>
       <c r="Q37" s="11" t="n">
-        <v>-0.4777401942140057</v>
+        <v>-0.4756165109218648</v>
       </c>
       <c r="R37" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S37" s="11" t="n">
-        <v>-0.0023180593951938</v>
+        <v>-3.030472610160428e-05</v>
       </c>
     </row>
     <row r="38">
@@ -3718,49 +3718,49 @@
         <v>20</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>-26.99755098293205</v>
+        <v>-27.17333898332586</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>-11.14173794510715</v>
+        <v>8.493820733187686</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>-61.6896049014469</v>
+        <v>-61.90727971114386</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>-16.58055322651958</v>
+        <v>2.84713889137057</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-6.07137019046178</v>
+        <v>-5.875180623305511</v>
       </c>
       <c r="L38" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>-0.6352834446252418</v>
+        <v>-0.7174652516551774</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>41.237487984433</v>
+        <v>41.08093746761519</v>
       </c>
       <c r="O38" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P38" s="11" t="n">
-        <v>6.072740466675228</v>
+        <v>6.3603770037682</v>
       </c>
       <c r="Q38" s="11" t="n">
-        <v>-0.474063875456385</v>
+        <v>-0.4718161164916496</v>
       </c>
       <c r="R38" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S38" s="11" t="n">
-        <v>0.0013582593624268</v>
+        <v>0.0037700897041135</v>
       </c>
     </row>
     <row r="39">
@@ -3779,49 +3779,49 @@
         <v>20</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>-29.55585680830775</v>
+        <v>-29.79211268871731</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>-13.70004377048285</v>
+        <v>5.875047027796235</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>-65.4511014658452</v>
+        <v>-65.70403434240085</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>-20.34204979091788</v>
+        <v>-0.9496157398864112</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-6.108134472119421</v>
+        <v>-5.909557947086983</v>
       </c>
       <c r="L39" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>-0.6720477262828828</v>
+        <v>-0.7518425754366485</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>42.47888766556807</v>
+        <v>42.29413415688174</v>
       </c>
       <c r="O39" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P39" s="11" t="n">
-        <v>7.314140147810306</v>
+        <v>7.573573693034753</v>
       </c>
       <c r="Q39" s="11" t="n">
-        <v>-0.4755085359112027</v>
+        <v>-0.4726545561112135</v>
       </c>
       <c r="R39" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S39" s="11" t="n">
-        <v>-8.640109239077542e-05</v>
+        <v>0.0029316500845496</v>
       </c>
     </row>
     <row r="40">
@@ -3840,49 +3840,49 @@
         <v>20</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>-22.52966132492226</v>
+        <v>-28.79609066738491</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>-6.673848287097353</v>
+        <v>6.871069049128632</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>-56.51484830429631</v>
+        <v>-62.9354927381219</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>-11.40579662936899</v>
+        <v>1.818925864392533</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-5.258956511663433</v>
+        <v>-5.462823711687499</v>
       </c>
       <c r="L40" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.1771302341731049</v>
+        <v>-0.3051083400371652</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>39.72172253902282</v>
+        <v>40.07730690288726</v>
       </c>
       <c r="O40" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P40" s="11" t="n">
-        <v>4.556975021265053</v>
+        <v>5.356746439040272</v>
       </c>
       <c r="Q40" s="11" t="n">
-        <v>-0.4775790479853322</v>
+        <v>-0.475081120462764</v>
       </c>
       <c r="R40" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S40" s="11" t="n">
-        <v>-0.0021569131665202</v>
+        <v>0.0005050857329991</v>
       </c>
     </row>
     <row r="41">
@@ -3901,49 +3901,49 @@
         <v>20</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>62.23343572299749</v>
+        <v>-35.8891214450185</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>78.08924876082239</v>
+        <v>-0.2219617285049508</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>31.99073736116034</v>
+        <v>-63.74590132526794</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>77.09978903608766</v>
+        <v>1.00851727724649</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>-1.105679471907607</v>
+        <v>-5.791598628589125</v>
       </c>
       <c r="L41" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>4.330407273928931</v>
+        <v>-0.6338832569387911</v>
       </c>
       <c r="N41" s="11" t="n">
-        <v>31.82543992540348</v>
+        <v>34.12564042421418</v>
       </c>
       <c r="O41" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P41" s="11" t="n">
-        <v>-3.339307592354288</v>
+        <v>-0.5949200396328109</v>
       </c>
       <c r="Q41" s="11" t="n">
-        <v>-0.4770620916587217</v>
+        <v>-0.47726191537558</v>
       </c>
       <c r="R41" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S41" s="11" t="n">
-        <v>-0.0016399568399098</v>
+        <v>-0.0016757091798168</v>
       </c>
     </row>
     <row r="42">
@@ -3962,49 +3962,49 @@
         <v>20</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>38.2690788625987</v>
+        <v>-35.94132024191366</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>54.1248919004236</v>
+        <v>-0.2741605254001129</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>-1.115773586880408</v>
+        <v>-65.34107216501329</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>43.99327808804691</v>
+        <v>-0.5866535624988529</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>-3.070891336546801</v>
+        <v>-5.953047661045654</v>
       </c>
       <c r="L42" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>2.365195409289737</v>
+        <v>-0.7953322893953194</v>
       </c>
       <c r="N42" s="11" t="n">
-        <v>42.92748102038586</v>
+        <v>35.83532776363037</v>
       </c>
       <c r="O42" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P42" s="11" t="n">
-        <v>7.762733502628088</v>
+        <v>1.114767299783381</v>
       </c>
       <c r="Q42" s="11" t="n">
-        <v>-0.4717372343599454</v>
+        <v>-0.4825281794850731</v>
       </c>
       <c r="R42" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S42" s="11" t="n">
-        <v>0.0036849004588664</v>
+        <v>-0.0069419732893098</v>
       </c>
     </row>
     <row r="43">
@@ -4023,49 +4023,49 @@
         <v>20</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>-16.56414686664796</v>
+        <v>-25.18526898885797</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>-0.7083338288230614</v>
+        <v>10.48189072765558</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>-55.40583379865831</v>
+        <v>-63.5773309183099</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>-10.29678212373099</v>
+        <v>1.177087684204537</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>-5.234800880315427</v>
+        <v>-4.851316767664405</v>
       </c>
       <c r="L43" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.2012858655211111</v>
+        <v>0.3063986039859294</v>
       </c>
       <c r="N43" s="11" t="n">
-        <v>44.55879883374128</v>
+        <v>43.72429664230711</v>
       </c>
       <c r="O43" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P43" s="11" t="n">
-        <v>9.394051315983511</v>
+        <v>9.003736178460123</v>
       </c>
       <c r="Q43" s="11" t="n">
-        <v>-0.4823110214154989</v>
+        <v>-0.4809179451907797</v>
       </c>
       <c r="R43" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S43" s="11" t="n">
-        <v>-0.006888886596687</v>
+        <v>-0.0053317389950165</v>
       </c>
     </row>
     <row r="44">
@@ -4084,49 +4084,49 @@
         <v>20</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>-30.58868682236334</v>
+        <v>-30.87829373746672</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>-14.73287378453844</v>
+        <v>4.788865979046825</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>-64.05800661894833</v>
+        <v>-64.21470227366517</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>-18.948954944021</v>
+        <v>0.5397163288492663</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>-3.795112159466424</v>
+        <v>-3.814387828445404</v>
       </c>
       <c r="L44" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>1.640974586370114</v>
+        <v>1.34332754320493</v>
       </c>
       <c r="N44" s="11" t="n">
-        <v>37.74723833423272</v>
+        <v>37.6310898343646</v>
       </c>
       <c r="O44" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P44" s="11" t="n">
-        <v>2.582490816474952</v>
+        <v>2.910529370517615</v>
       </c>
       <c r="Q44" s="11" t="n">
-        <v>-0.4828063781813043</v>
+        <v>-0.4802934697207711</v>
       </c>
       <c r="R44" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S44" s="11" t="n">
-        <v>-0.0073842433624923</v>
+        <v>-0.0047072635250078</v>
       </c>
     </row>
     <row r="45">
@@ -4145,49 +4145,49 @@
         <v>20</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>-26.64049539579716</v>
+        <v>-26.95948576320606</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>-10.78468235797226</v>
+        <v>8.707673953307484</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>-60.65841396953589</v>
+        <v>-60.83490246617581</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>-15.54936229460857</v>
+        <v>3.919516136338629</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-3.872030369410323</v>
+        <v>-3.840169054768116</v>
       </c>
       <c r="L45" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>1.564056376426215</v>
+        <v>1.317546316882218</v>
       </c>
       <c r="N45" s="11" t="n">
-        <v>38.36813269336182</v>
+        <v>38.19187369560875</v>
       </c>
       <c r="O45" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P45" s="11" t="n">
-        <v>3.203385175604055</v>
+        <v>3.471313231761769</v>
       </c>
       <c r="Q45" s="11" t="n">
-        <v>-0.4781837502127624</v>
+        <v>-0.4762879378709009</v>
       </c>
       <c r="R45" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S45" s="11" t="n">
-        <v>-0.0027616153939504</v>
+        <v>-0.0007017316751377</v>
       </c>
     </row>
     <row r="46">
@@ -4206,49 +4206,49 @@
         <v>20</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>-32.55833731982037</v>
+        <v>-32.84593446723435</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>-16.70252428199547</v>
+        <v>2.821225249279195</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>-64.88340224636215</v>
+        <v>-65.0480496028716</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>-19.77435057143483</v>
+        <v>-0.2936310003571662</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-5.143604907661277</v>
+        <v>-5.150542940357292</v>
       </c>
       <c r="L46" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.2924818381752612</v>
+        <v>0.0071724312930419</v>
       </c>
       <c r="N46" s="11" t="n">
-        <v>37.95556643724897</v>
+        <v>37.8363767442922</v>
       </c>
       <c r="O46" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P46" s="11" t="n">
-        <v>2.790818919491201</v>
+        <v>3.115816280445216</v>
       </c>
       <c r="Q46" s="11" t="n">
-        <v>-0.4868966030459102</v>
+        <v>-0.4837186682976455</v>
       </c>
       <c r="R46" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S46" s="11" t="n">
-        <v>-0.0114744682270983</v>
+        <v>-0.008132462101882201</v>
       </c>
     </row>
     <row r="47">
@@ -4267,49 +4267,49 @@
         <v>20</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>77.94412709146557</v>
+        <v>-31.63099246176284</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>93.79994012929048</v>
+        <v>4.036167254750708</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>33.91433876086277</v>
+        <v>-62.73820750551622</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>79.02339043579009</v>
+        <v>2.016211096998212</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0.7764484237653322</v>
+        <v>-3.86568842203821</v>
       </c>
       <c r="L47" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>6.21253516960187</v>
+        <v>1.292026949612125</v>
       </c>
       <c r="N47" s="11" t="n">
-        <v>43.69464471622817</v>
+        <v>35.4483372964549</v>
       </c>
       <c r="O47" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P47" s="11" t="n">
-        <v>8.529897198470401</v>
+        <v>0.7277768326079155</v>
       </c>
       <c r="Q47" s="11" t="n">
-        <v>-0.4413048093907007</v>
+        <v>-0.4754338306633053</v>
       </c>
       <c r="R47" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S47" s="11" t="n">
-        <v>0.0341173254281111</v>
+        <v>0.0001523755324578</v>
       </c>
     </row>
     <row r="48">
@@ -4328,49 +4328,49 @@
         <v>20</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>-31.81129796840036</v>
+        <v>-32.03222855103682</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>-15.95548493057546</v>
+        <v>3.634931165476722</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>-61.50535456764995</v>
+        <v>-61.68221697632772</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>-16.39630289272262</v>
+        <v>3.072201626186711</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-4.197273655557723</v>
+        <v>-4.129828257485446</v>
       </c>
       <c r="L48" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>1.238813090278815</v>
+        <v>1.027887114164888</v>
       </c>
       <c r="N48" s="11" t="n">
-        <v>34.37585028362091</v>
+        <v>34.26101755343705</v>
       </c>
       <c r="O48" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P48" s="11" t="n">
-        <v>-0.7888972341368543</v>
+        <v>-0.4595429104099366</v>
       </c>
       <c r="Q48" s="11" t="n">
-        <v>-0.4845200288136191</v>
+        <v>-0.4812008706607052</v>
       </c>
       <c r="R48" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S48" s="11" t="n">
-        <v>-0.009097893994807199</v>
+        <v>-0.005614664464942</v>
       </c>
     </row>
     <row r="49">
@@ -4389,49 +4389,49 @@
         <v>20</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>-34.63856976614627</v>
+        <v>-34.19891848619663</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>-18.78275672832137</v>
+        <v>1.468241230316913</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>-61.90418139470467</v>
+        <v>-62.06120494598523</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>-16.79512971977735</v>
+        <v>2.693213656529202</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-5.387316288045441</v>
+        <v>-5.312440206371054</v>
       </c>
       <c r="L49" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.0487704577910967</v>
+        <v>-0.1547248347207199</v>
       </c>
       <c r="N49" s="11" t="n">
-        <v>33.13764842016975</v>
+        <v>33.65654284366002</v>
       </c>
       <c r="O49" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P49" s="11" t="n">
-        <v>-2.027099097588021</v>
+        <v>-1.064017620186966</v>
       </c>
       <c r="Q49" s="11" t="n">
-        <v>-0.484720503565914</v>
+        <v>-0.4818161775003655</v>
       </c>
       <c r="R49" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S49" s="11" t="n">
-        <v>-0.0092983687471021</v>
+        <v>-0.0062299713046023</v>
       </c>
     </row>
     <row r="50">
@@ -4450,49 +4450,49 @@
         <v>20</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>-34.51638684018619</v>
+        <v>-34.8244516817598</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>-18.66057380236129</v>
+        <v>0.8427080347537412</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>-63.39727645850318</v>
+        <v>-63.57125952354222</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>-18.28822478357586</v>
+        <v>1.183159078972217</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-1.863879136328032</v>
+        <v>-1.930816826139262</v>
       </c>
       <c r="L50" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>3.572207609508506</v>
+        <v>3.226898545511072</v>
       </c>
       <c r="N50" s="11" t="n">
-        <v>31.22040961030337</v>
+        <v>31.15061932950357</v>
       </c>
       <c r="O50" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P50" s="11" t="n">
-        <v>-3.944337907454401</v>
+        <v>-3.56994113434342</v>
       </c>
       <c r="Q50" s="11" t="n">
-        <v>-0.4756408556583506</v>
+        <v>-0.4729946615819038</v>
       </c>
       <c r="R50" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S50" s="11" t="n">
-        <v>-0.0002187208395387</v>
+        <v>0.0025915446138594</v>
       </c>
     </row>
     <row r="51">
@@ -4511,49 +4511,49 @@
         <v>20</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>-34.92003894815254</v>
+        <v>-35.23151996864701</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>-19.06422591032764</v>
+        <v>0.4356397478665315</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>-65.05531594584593</v>
+        <v>-65.14314657132917</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>-19.94626427091861</v>
+        <v>-0.3887279688147345</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-3.627142714724714</v>
+        <v>-3.574490107605979</v>
       </c>
       <c r="L51" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>1.808944031111824</v>
+        <v>1.583225264044355</v>
       </c>
       <c r="N51" s="11" t="n">
-        <v>34.25392972351716</v>
+        <v>33.97512156694386</v>
       </c>
       <c r="O51" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P51" s="11" t="n">
-        <v>-0.9108177942406072</v>
+        <v>-0.7454388969031243</v>
       </c>
       <c r="Q51" s="11" t="n">
-        <v>-0.4915100110990367</v>
+        <v>-0.4890048566557481</v>
       </c>
       <c r="R51" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S51" s="11" t="n">
-        <v>-0.0160878762802247</v>
+        <v>-0.0134186504599849</v>
       </c>
     </row>
     <row r="52">
@@ -4572,49 +4572,49 @@
         <v>20</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>-42.17710532889083</v>
+        <v>-42.41999023004849</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>-26.32129229106593</v>
+        <v>-6.752830513534946</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>-65.92151635463561</v>
+        <v>-66.08428334539479</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>-20.81246467970829</v>
+        <v>-1.32986474288036</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-7.474609725106059</v>
+        <v>-7.526626481533643</v>
       </c>
       <c r="L52" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>-2.038522979269521</v>
+        <v>-2.368911109883309</v>
       </c>
       <c r="N52" s="11" t="n">
-        <v>31.70546537147654</v>
+        <v>31.67404870914</v>
       </c>
       <c r="O52" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P52" s="11" t="n">
-        <v>-3.459282146281232</v>
+        <v>-3.046511754706987</v>
       </c>
       <c r="Q52" s="11" t="n">
-        <v>-0.4864446206256946</v>
+        <v>-0.4831291122600635</v>
       </c>
       <c r="R52" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S52" s="11" t="n">
-        <v>-0.0110224858068826</v>
+        <v>-0.0075429060643003</v>
       </c>
     </row>
     <row r="53">
@@ -4633,49 +4633,49 @@
         <v>20</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>-40.09447139661125</v>
+        <v>-40.40611279466181</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G53" s="11" t="n">
-        <v>-24.23865835878635</v>
+        <v>-4.738953078148263</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>-65.07761686983345</v>
+        <v>-65.2535351830397</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>-19.96856519490613</v>
+        <v>-0.4991165805252677</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-4.937479372918036</v>
+        <v>-4.929266779652279</v>
       </c>
       <c r="L53" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.4986073729185021</v>
+        <v>0.2284485919980552</v>
       </c>
       <c r="N53" s="11" t="n">
-        <v>30.40255506453504</v>
+        <v>30.25536244275693</v>
       </c>
       <c r="O53" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P53" s="11" t="n">
-        <v>-4.762192453222724</v>
+        <v>-4.465198021090057</v>
       </c>
       <c r="Q53" s="11" t="n">
-        <v>-0.48193021839481</v>
+        <v>-0.4786732747267582</v>
       </c>
       <c r="R53" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S53" s="11" t="n">
-        <v>-0.006508083575998</v>
+        <v>-0.0030870685309949</v>
       </c>
     </row>
     <row r="54">
@@ -4694,49 +4694,49 @@
         <v>20</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>-35.31935226535477</v>
+        <v>-35.58460223821974</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>-19.46353922752987</v>
+        <v>0.08255747829380761</v>
       </c>
       <c r="H54" s="11" t="n">
-        <v>-64.40275309190694</v>
+        <v>-64.54829921068942</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>-19.29370141697962</v>
+        <v>0.2061193918250126</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-5.581652867406549</v>
+        <v>-5.615339624614445</v>
       </c>
       <c r="L54" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>-0.1455661215700114</v>
+        <v>-0.457624252964111</v>
       </c>
       <c r="N54" s="11" t="n">
-        <v>35.147111137784</v>
+        <v>35.0578973500724</v>
       </c>
       <c r="O54" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P54" s="11" t="n">
-        <v>-0.0176363799737657</v>
+        <v>0.3373368862254153</v>
       </c>
       <c r="Q54" s="11" t="n">
-        <v>-0.4820574438252822</v>
+        <v>-0.4788607529882719</v>
       </c>
       <c r="R54" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S54" s="11" t="n">
-        <v>-0.0066353090064703</v>
+        <v>-0.0032745467925087</v>
       </c>
     </row>
     <row r="55">
@@ -4755,49 +4755,49 @@
         <v>20</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>-28.73117833987704</v>
+        <v>-28.77601474245147</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>-15.8558130378249</v>
+        <v>-35.66715971651355</v>
       </c>
       <c r="G55" s="11" t="n">
-        <v>-12.87536530205214</v>
+        <v>6.891144974062083</v>
       </c>
       <c r="H55" s="11" t="n">
-        <v>-60.94907809397915</v>
+        <v>-61.09097125119852</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>-45.10905167492732</v>
+        <v>-64.75441860251443</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>-15.84002641905182</v>
+        <v>3.663447351315917</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>-6.421170453496463</v>
+        <v>-6.314582497323864</v>
       </c>
       <c r="L55" s="11" t="n">
-        <v>-5.436086745836538</v>
+        <v>-5.157715371650334</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>-0.9850837076599248</v>
+        <v>-1.15686712567353</v>
       </c>
       <c r="N55" s="11" t="n">
-        <v>39.12113711209415</v>
+        <v>39.10854988184759</v>
       </c>
       <c r="O55" s="11" t="n">
-        <v>35.16474751775777</v>
+        <v>34.72056046384699</v>
       </c>
       <c r="P55" s="11" t="n">
-        <v>3.956389594336386</v>
+        <v>4.3879894180006</v>
       </c>
       <c r="Q55" s="11" t="n">
-        <v>-0.4820669044955966</v>
+        <v>-0.4790108757766665</v>
       </c>
       <c r="R55" s="11" t="n">
-        <v>-0.4754221348188119</v>
+        <v>-0.4755862061957632</v>
       </c>
       <c r="S55" s="11" t="n">
-        <v>-0.0066447696767846</v>
+        <v>-0.0034246695809033</v>
       </c>
     </row>
   </sheetData>

--- a/manuscript/Supplementary-Table-3.xlsx
+++ b/manuscript/Supplementary-Table-3.xlsx
@@ -523,7 +523,7 @@
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>WT reference (mean +/- SEM over three WT production replicates, kcal/mol): total -35.7 +/- 2.4; van der Waals -64.8 +/- 0.4; electrostatic -5.2 +/- 0.9; GB polar solvation 34.7 +/- 1.5; nonpolar SA -0.5 +/- 0.0. These reference uncertainties are common to every row and are not included in the per-mutation SEM values above.</t>
+          <t>WT reference (mean +/- SEM over three WT production replicates, kcal/mol): total -61.3 +/- 0.6; van der Waals -64.8 +/- 0.4; electrostatic -5.2 +/- 0.9; GB polar solvation 16.4 +/- 0.6; nonpolar SA -7.8 +/- 0.0. These reference uncertainties are common to every row and are not included in the per-mutation SEM values above.</t>
         </is>
       </c>
     </row>
@@ -607,34 +607,34 @@
         <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-0.05238713454632915</v>
+        <v>2.635000233182159</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.9125305541459536</v>
+        <v>1.336090023784523</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>2.235303680464857</v>
+        <v>2.235347345589477</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>1.287165527988693</v>
+        <v>1.287169456368881</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4011915552848208</v>
+        <v>0.401166564451836</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.4194401104123121</v>
+        <v>0.4194256299927143</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-2.681888925793678</v>
+        <v>0.02720852882866608</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>1.944060948929719</v>
+        <v>0.1496673668066849</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>-0.006993444502315667</v>
+        <v>-0.02872220568781536</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.001295605404048191</v>
+        <v>0.06037098224984301</v>
       </c>
     </row>
     <row r="9">
@@ -650,34 +650,34 @@
         <v>3</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5.806655068842297</v>
+        <v>0.3714224221639431</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1.136675390260942</v>
+        <v>0.5046188451846568</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.05490682226514328</v>
+        <v>0.05494346480673568</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.3573697589949265</v>
+        <v>0.3573699188568015</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-2.444541331508713</v>
+        <v>-2.444628999344898</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.1841296228215511</v>
+        <v>0.1841907079470252</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>8.199068884928563</v>
+        <v>2.812913878849921</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.7418867430189463</v>
+        <v>0.07974330262640504</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>-0.002779306842689667</v>
+        <v>-0.05180592214780094</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.001199066715497238</v>
+        <v>0.01348316601927346</v>
       </c>
     </row>
     <row r="10">
@@ -693,34 +693,34 @@
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>4.862661685758479</v>
+        <v>1.729890693703872</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2.103989569711314</v>
+        <v>0.6293250484500691</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.234796681506981</v>
+        <v>1.234837109635177</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.5921406090367471</v>
+        <v>0.5921396468363338</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-1.242455822878262</v>
+        <v>-1.242485454002906</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.4336258984029359</v>
+        <v>0.4336759369391803</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>4.873304862061294</v>
+        <v>1.734811580431849</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>1.422736297565476</v>
+        <v>0.4762198817659357</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>-0.0029840349315305</v>
+        <v>0.0027274576397443</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0009120239229448135</v>
+        <v>0.02145232981332985</v>
       </c>
     </row>
     <row r="11">
@@ -736,34 +736,34 @@
         <v>3</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3.028572749303636</v>
+        <v>1.938994902648173</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.3558233686394046</v>
+        <v>0.5091108204889837</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1.394224870626114</v>
+        <v>1.393370903977157</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.4023767148360863</v>
+        <v>0.4030730665469203</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.458141159554368</v>
+        <v>0.4581742482205445</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.11989944424127</v>
+        <v>0.1199162031212087</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>1.179362931321419</v>
+        <v>0.1339328752497018</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.5818034446178386</v>
+        <v>0.2234324777555118</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>-0.003156212198270801</v>
+        <v>-0.04648312479922393</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.001848566357390913</v>
+        <v>0.01374776883481284</v>
       </c>
     </row>
     <row r="12">
@@ -779,34 +779,34 @@
         <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>-1.798187956018791</v>
+        <v>1.906002272024997</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>2.869787913409791</v>
+        <v>1.104865616446548</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.8491361900956633</v>
+        <v>0.8491752204683819</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>1.303946904866994</v>
+        <v>1.303946316679889</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.2121857635096009</v>
+        <v>0.2121168448142748</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.8578428573851646</v>
+        <v>0.8578394304865836</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-2.854092499873991</v>
+        <v>0.84076441344826</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>2.012984547955172</v>
+        <v>0.6479798467861302</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>-0.005417409750061267</v>
+        <v>0.003945793294086268</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.001655583966277393</v>
+        <v>0.01702742797686927</v>
       </c>
     </row>
     <row r="13">
@@ -822,34 +822,34 @@
         <v>3</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4.837298105137122</v>
+        <v>4.242247566287548</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>3.538191771528978</v>
+        <v>2.009832592506257</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>2.574334575682625</v>
+        <v>2.574624592176486</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.705710338418336</v>
+        <v>1.705464609700796</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1.573722768358007</v>
+        <v>1.572767720738297</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.7950049241243449</v>
+        <v>0.7956307663184026</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.6927656758887579</v>
+        <v>0.1081088912798537</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>1.388303407483793</v>
+        <v>0.58015793031581</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>-0.0035249147922693</v>
+        <v>-0.01325363790707737</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.00227962247929318</v>
+        <v>0.03474585348088199</v>
       </c>
     </row>
     <row r="14">
@@ -865,34 +865,34 @@
         <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.535459002067081</v>
+        <v>0.07792385687960274</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0.5958717368130245</v>
+        <v>0.547981120898354</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.2870888175385294</v>
+        <v>-0.2870503677094807</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7154315619543382</v>
+        <v>0.7154316156786654</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-2.768696110550643</v>
+        <v>-2.768752043562901</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8062594292626113</v>
+        <v>0.8062665767193125</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>4.598044325319189</v>
+        <v>3.187959189624678</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.4001569595990181</v>
+        <v>0.4353295672143369</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>-0.006800395162945834</v>
+        <v>-0.05423292147269913</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.002258569129692241</v>
+        <v>0.02617248248189058</v>
       </c>
     </row>
     <row r="15">
@@ -908,34 +908,34 @@
         <v>3</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>11.4516783196498</v>
+        <v>2.913905228615145</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1.59721610265158</v>
+        <v>1.970682348363874</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1.840079347496129</v>
+        <v>1.840119154769271</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1.96860684903629</v>
+        <v>1.968610008386864</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.7939478829446872</v>
+        <v>-0.7939665666248508</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.110707609483983</v>
+        <v>1.110699105880201</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>10.40831124843344</v>
+        <v>1.917873939334245</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.5189592006962404</v>
+        <v>0.9146741888259851</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>-0.002764393335090767</v>
+        <v>-0.05012129886352457</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.00233614573003459</v>
+        <v>0.02003420807984905</v>
       </c>
     </row>
     <row r="16">
@@ -951,34 +951,34 @@
         <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>11.80088887137738</v>
+        <v>3.710417651906492</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>3.688166579680861</v>
+        <v>1.108660499563166</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>2.577057549102546</v>
+        <v>2.577079494328842</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1.04323494136814</v>
+        <v>1.043225541787711</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-1.214849900161836</v>
+        <v>-1.214937893961283</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.005480033009597</v>
+        <v>1.005475798084441</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>10.44661019393939</v>
+        <v>2.428769092790787</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>2.373078317228523</v>
+        <v>0.5458497475701581</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>-0.007928971502718533</v>
+        <v>-0.08049304125185877</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.002283553501600496</v>
+        <v>0.0313938726980511</v>
       </c>
     </row>
     <row r="17">
@@ -994,34 +994,34 @@
         <v>3</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>4.708979066077102</v>
+        <v>3.20332700304454</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1.703570843988201</v>
+        <v>0.2690081935916681</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1.996285973046615</v>
+        <v>1.996323562279019</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.4011029143612933</v>
+        <v>0.4011034420955784</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.5869536608134199</v>
+        <v>-0.5870213236242888</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.1004880804895641</v>
+        <v>0.1004687910739855</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>3.300948379296564</v>
+        <v>1.73851861704528</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>1.463402805434132</v>
+        <v>0.2091774753954047</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>-0.001301625452655467</v>
+        <v>0.05550614734452643</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.002638243944846054</v>
+        <v>0.0156454452033292</v>
       </c>
     </row>
     <row r="18">
@@ -1037,34 +1037,34 @@
         <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.7028812218159478</v>
+        <v>1.299552182867802</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>2.691142254729207</v>
+        <v>0.2207381564678061</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1.280213134851391</v>
+        <v>1.279580944672591</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.3031386311520005</v>
+        <v>0.3028153981175196</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.5249851979265995</v>
+        <v>-0.5247817278024124</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.4008642736351215</v>
+        <v>0.4009516650974376</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.05157293123831982</v>
+        <v>0.6333649120488852</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>2.469146610198421</v>
+        <v>0.09186974931778824</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>-0.0007737838705304667</v>
+        <v>-0.0886119460512529</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.003466839219265127</v>
+        <v>0.01743642466468951</v>
       </c>
     </row>
     <row r="19">
@@ -1080,34 +1080,34 @@
         <v>3</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.01095575198476695</v>
+        <v>-1.191044730255198</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>1.247039164893308</v>
+        <v>0.3155397544463588</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.9285727018863241</v>
+        <v>-0.9280266069776199</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.2601354488945047</v>
+        <v>0.2604072524641287</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-3.995449890677254</v>
+        <v>-3.995228171499674</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.3557272831386033</v>
+        <v>0.3555657163394705</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>4.93600173426555</v>
+        <v>3.769557699418661</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>1.085057669130857</v>
+        <v>0.5378149448753599</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>-0.001023389717208935</v>
+        <v>-0.03734765119655993</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0006364248773646464</v>
+        <v>0.04064925962088046</v>
       </c>
     </row>
     <row r="20">
@@ -1123,34 +1123,34 @@
         <v>3</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>7.079978936704184</v>
+        <v>1.65754308903422</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.7631571345093443</v>
+        <v>1.111110304418562</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1.238816338625564</v>
+        <v>1.237908251432152</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>1.133759487855488</v>
+        <v>1.133088155340096</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.5914720557096637</v>
+        <v>-0.5895154781269802</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.1435253558759029</v>
+        <v>0.1426588577447152</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>6.430232378614408</v>
+        <v>0.9806495779558991</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.6408953628997889</v>
+        <v>0.1634007793198529</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.0024022751738874</v>
+        <v>0.02850073777314907</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0009789860536761424</v>
+        <v>0.01490892817215448</v>
       </c>
     </row>
     <row r="21">
@@ -1166,34 +1166,34 @@
         <v>3</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>3.328589491250172</v>
+        <v>0.7459239060097644</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>3.576682359984304</v>
+        <v>0.7163439970877713</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.5329837996507246</v>
+        <v>0.5330216621458088</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.5619296701445975</v>
+        <v>0.5619295783731191</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.3742723141160604</v>
+        <v>-0.374289476141844</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.3435118249214728</v>
+        <v>0.3435122945510153</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>3.174527812870231</v>
+        <v>0.6156071802094315</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>2.956095979877142</v>
+        <v>0.1586110972146757</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>-0.004649807154714366</v>
+        <v>-0.02841546020361936</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.001558007027567261</v>
+        <v>0.03520481296417037</v>
       </c>
     </row>
     <row r="22">
@@ -1209,34 +1209,34 @@
         <v>3</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5.439255060544501</v>
+        <v>3.221202766775578</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1.730108287004759</v>
+        <v>1.335303181522811</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1.388533821610243</v>
+        <v>1.388573421162472</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>1.288153788809753</v>
+        <v>1.288154130324197</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.8893487637933966</v>
+        <v>0.8893047698485385</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.4411509488922162</v>
+        <v>0.4411606439540546</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>3.165886294241533</v>
+        <v>0.9356882102630794</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.1638087192115123</v>
+        <v>0.5289984741322014</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>-0.0045138191006759</v>
+        <v>0.007636365501495799</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.00214724662670713</v>
+        <v>0.04036180377094331</v>
       </c>
     </row>
     <row r="23">
@@ -1252,34 +1252,34 @@
         <v>3</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3.046446550181448</v>
+        <v>3.125842295614511</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.7975580696874073</v>
+        <v>0.5115101901203302</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>2.593875459904709</v>
+        <v>2.593913814021219</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.3088581429585468</v>
+        <v>0.3088569239966527</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.7217297430187642</v>
+        <v>0.7216475092577824</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.4448115456002675</v>
+        <v>0.4448180593092901</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.2652612326629959</v>
+        <v>-0.1332496213943355</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.5262891689295762</v>
+        <v>0.1091686590954851</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>-0.003897420079028833</v>
+        <v>-0.05646940627016073</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.002032673444657346</v>
+        <v>0.02414992592267355</v>
       </c>
     </row>
     <row r="24">
@@ -1295,34 +1295,34 @@
         <v>3</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>-1.824827576971558</v>
+        <v>2.120223032071299</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>2.466801968448917</v>
+        <v>1.041054922227592</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-0.1784778775742926</v>
+        <v>-0.178438667706987</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.7330247853812301</v>
+        <v>0.7330250478130573</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.8137375665573727</v>
+        <v>0.8137015721112926</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>1.660557628457894</v>
+        <v>1.660554800986427</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-2.453963928651177</v>
+        <v>1.518794273099299</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.8675228944046971</v>
+        <v>1.337283459143715</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>-0.006123337303475266</v>
+        <v>-0.03383414543229674</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.004675930145460181</v>
+        <v>0.05278404871289426</v>
       </c>
     </row>
     <row r="25">
@@ -1338,34 +1338,34 @@
         <v>3</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.7449164580692091</v>
+        <v>2.781422649320945</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3.373615011604691</v>
+        <v>1.268506277977478</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1.123483387538554</v>
+        <v>1.123521836241816</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1.286196219755488</v>
+        <v>1.286196736247881</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.4620142622131951</v>
+        <v>-0.4620506242747207</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.3999122251790134</v>
+        <v>0.3999114872154343</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.08670942771198635</v>
+        <v>2.202476506935252</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>2.558765493367119</v>
+        <v>0.3827906622691564</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>-0.003262094968135633</v>
+        <v>-0.08252506958139137</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>9.765569307943893e-05</v>
+        <v>0.02092703410362843</v>
       </c>
     </row>
   </sheetData>
@@ -1522,49 +1522,49 @@
         <v>20</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>-37.54359791288206</v>
+        <v>-57.19561263398745</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>-1.876438196368511</v>
+        <v>4.1060848802667</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>-60.68648093880522</v>
+        <v>-60.68646407616738</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>4.067937663709216</v>
+        <v>4.067993026295937</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>-5.38043783690434</v>
+        <v>-5.380375502205564</v>
       </c>
       <c r="L2" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M2" s="11" t="n">
-        <v>-0.222722465254006</v>
+        <v>-0.222714765352487</v>
       </c>
       <c r="N2" s="11" t="n">
-        <v>29.00487811342024</v>
+        <v>16.6023499195252</v>
       </c>
       <c r="O2" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P2" s="11" t="n">
-        <v>-5.715682350426746</v>
+        <v>0.2151346571358843</v>
       </c>
       <c r="Q2" s="11" t="n">
-        <v>-0.4815572505927222</v>
+        <v>-7.731122975139726</v>
       </c>
       <c r="R2" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S2" s="11" t="n">
-        <v>-0.005971044396959</v>
+        <v>0.0456719621873498</v>
       </c>
     </row>
     <row r="3">
@@ -1583,49 +1583,49 @@
         <v>20</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>-34.86009821287546</v>
+        <v>-57.47031255480009</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>0.8070615036380886</v>
+        <v>3.831384959454062</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>-61.86971329210508</v>
+        <v>-61.86971455589018</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>2.884705310409359</v>
+        <v>2.884742546573143</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>-3.958934754127343</v>
+        <v>-3.958927476457138</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M3" s="11" t="n">
-        <v>1.198780617522991</v>
+        <v>1.198733260395938</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>31.44957869390229</v>
+        <v>16.11868414322687</v>
       </c>
       <c r="O3" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P3" s="11" t="n">
-        <v>-3.270981769944701</v>
+        <v>-0.26853111916245</v>
       </c>
       <c r="Q3" s="11" t="n">
-        <v>-0.4810288605452951</v>
+        <v>-7.760354665679639</v>
       </c>
       <c r="R3" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S3" s="11" t="n">
-        <v>-0.0054426543495319</v>
+        <v>0.0164402716474372</v>
       </c>
     </row>
     <row r="4">
@@ -1644,49 +1644,49 @@
         <v>20</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>-34.75494442742211</v>
+        <v>-61.33416665442844</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.912215289091435</v>
+        <v>-0.0324691401742853</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>-65.00115053523844</v>
+        <v>-65.00115063856397</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>-0.2467319327240034</v>
+        <v>-0.2466935361006506</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>-4.930198858064856</v>
+        <v>-4.930179538541021</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M4" s="11" t="n">
-        <v>0.2275165135854777</v>
+        <v>0.2274811983120566</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>35.6615578068374</v>
+        <v>16.52223731090188</v>
       </c>
       <c r="O4" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P4" s="11" t="n">
-        <v>0.9409973429904142</v>
+        <v>0.1350220485125639</v>
       </c>
       <c r="Q4" s="11" t="n">
-        <v>-0.4851528409562193</v>
+        <v>-7.925073788225309</v>
       </c>
       <c r="R4" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S4" s="11" t="n">
-        <v>-0.0095666347604561</v>
+        <v>-0.1482788508982331</v>
       </c>
     </row>
     <row r="5">
@@ -1705,49 +1705,49 @@
         <v>20</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>-29.09983324775578</v>
+        <v>-60.168913383796</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>6.567326468757763</v>
+        <v>1.132784130458148</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>-64.05311422769695</v>
+        <v>-64.05311617132142</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>0.7013043748174823</v>
+        <v>0.7013409311418997</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>-7.667348533869563</v>
+        <v>-7.667382054346826</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>-2.509633162219229</v>
+        <v>-2.509721317493748</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>43.09737288017346</v>
+        <v>19.35825525688623</v>
       </c>
       <c r="O5" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P5" s="11" t="n">
-        <v>8.376812416326473</v>
+        <v>2.971039994496916</v>
       </c>
       <c r="Q5" s="11" t="n">
-        <v>-0.4767433663627157</v>
+        <v>-7.806670415013972</v>
       </c>
       <c r="R5" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S5" s="11" t="n">
-        <v>-0.0011571601669525</v>
+        <v>-0.0298754776868959</v>
       </c>
     </row>
     <row r="6">
@@ -1766,49 +1766,49 @@
         <v>20</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>-32.09613738435587</v>
+        <v>-61.88468654382122</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>3.571022332157675</v>
+        <v>-0.5829890295670666</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>-65.28684515663123</v>
+        <v>-65.28684777804509</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>-0.5324265541167961</v>
+        <v>-0.532390675581766</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>-7.883611160824091</v>
+        <v>-7.883751368859018</v>
       </c>
       <c r="L6" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>-2.725895789173757</v>
+        <v>-2.726090632005941</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>41.55502514789027</v>
+        <v>19.13906835005342</v>
       </c>
       <c r="O6" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P6" s="11" t="n">
-        <v>6.834464684043283</v>
+        <v>2.751853087664106</v>
       </c>
       <c r="Q6" s="11" t="n">
-        <v>-0.4807062147908184</v>
+        <v>-7.853155746970532</v>
       </c>
       <c r="R6" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S6" s="11" t="n">
-        <v>-0.0051200085950551</v>
+        <v>-0.0763608096434556</v>
       </c>
     </row>
     <row r="7">
@@ -1827,49 +1827,49 @@
         <v>20</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>-28.38554331090209</v>
+        <v>-60.7372253486534</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>7.281616405611455</v>
+        <v>0.5644721656007476</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>-64.75857595641969</v>
+        <v>-64.75857696360325</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>-0.0041573539052564</v>
+        <v>-0.0041198611399266</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>-7.255810414783486</v>
+        <v>-7.25573578538808</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>-2.098095043133152</v>
+        <v>-2.098075048535003</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>44.10649001826292</v>
+        <v>19.10306381677806</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P7" s="11" t="n">
-        <v>9.385929554415933</v>
+        <v>2.715848554388742</v>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>-0.4776469579618246</v>
+        <v>-7.825976416440128</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>-0.0020607517660614</v>
+        <v>-0.0491814791130513</v>
       </c>
     </row>
     <row r="8">
@@ -1888,49 +1888,49 @@
         <v>20</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>-32.49580928783035</v>
+        <v>-59.75790086817192</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>3.171350428683198</v>
+        <v>1.543796646082235</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>-63.37597625990824</v>
+        <v>-63.37596749920134</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>1.378442342606192</v>
+        <v>1.378489603261976</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>-6.088023636963281</v>
+        <v>-6.087912342844292</v>
       </c>
       <c r="L8" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>-0.9303082653129467</v>
+        <v>-0.9302516059912148</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>37.44843448325279</v>
+        <v>17.52294801161348</v>
       </c>
       <c r="O8" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P8" s="11" t="n">
-        <v>2.727874019405803</v>
+        <v>1.135732749224164</v>
       </c>
       <c r="Q8" s="11" t="n">
-        <v>-0.4802438742116122</v>
+        <v>-7.81696903773977</v>
       </c>
       <c r="R8" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S8" s="11" t="n">
-        <v>-0.0046576680158489</v>
+        <v>-0.0401741004126936</v>
       </c>
     </row>
     <row r="9">
@@ -1949,49 +1949,49 @@
         <v>20</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>-33.29574455872874</v>
+        <v>-60.55680284036058</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>2.37141515778481</v>
+        <v>0.7448946738935689</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>-64.6094899104998</v>
+        <v>-64.60948899653954</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>0.1449286920146306</v>
+        <v>0.1449681059237804</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>-7.256971158084427</v>
+        <v>-7.257053363764513</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>-2.099255786434092</v>
+        <v>-2.099392626911436</v>
       </c>
       <c r="N9" s="11" t="n">
-        <v>39.04782178069163</v>
+        <v>19.06280298761838</v>
       </c>
       <c r="O9" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P9" s="11" t="n">
-        <v>4.327261316844648</v>
+        <v>2.675587725229061</v>
       </c>
       <c r="Q9" s="11" t="n">
-        <v>-0.477105270836139</v>
+        <v>-7.75306346767491</v>
       </c>
       <c r="R9" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S9" s="11" t="n">
-        <v>-0.0015190646403758</v>
+        <v>0.0237314696521657</v>
       </c>
     </row>
     <row r="10">
@@ -2010,49 +2010,49 @@
         <v>20</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>-26.62194024570612</v>
+        <v>-58.40071675311834</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>9.045219470807428</v>
+        <v>2.900980761135813</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>-62.57339959261432</v>
+        <v>-62.57340348274354</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>2.181019009900119</v>
+        <v>2.181053619719776</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>-5.855518788538082</v>
+        <v>-5.855472865959143</v>
       </c>
       <c r="L10" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>-0.6978034168877478</v>
+        <v>-0.6978121291060662</v>
       </c>
       <c r="N10" s="11" t="n">
-        <v>42.28533971378042</v>
+        <v>17.78032952923164</v>
       </c>
       <c r="O10" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P10" s="11" t="n">
-        <v>7.56477924993343</v>
+        <v>1.393114266842321</v>
       </c>
       <c r="Q10" s="11" t="n">
-        <v>-0.47836157833413</v>
+        <v>-7.752169933647315</v>
       </c>
       <c r="R10" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S10" s="11" t="n">
-        <v>-0.0027753721383668</v>
+        <v>0.0246250036797608</v>
       </c>
     </row>
     <row r="11">
@@ -2071,49 +2071,49 @@
         <v>20</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>-31.98635599529191</v>
+        <v>-59.24589060799089</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>3.68080372122164</v>
+        <v>2.055806906263257</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>-63.47689049093174</v>
+        <v>-63.47690988202904</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>1.277528111582697</v>
+        <v>1.277547220434279</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>-4.905450335453543</v>
+        <v>-4.90550281573587</v>
       </c>
       <c r="L11" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.2522650361967908</v>
+        <v>0.2521579211172069</v>
       </c>
       <c r="N11" s="11" t="n">
-        <v>36.87711985457695</v>
+        <v>16.96345290991817</v>
       </c>
       <c r="O11" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P11" s="11" t="n">
-        <v>2.156559390729967</v>
+        <v>0.5762376475288562</v>
       </c>
       <c r="Q11" s="11" t="n">
-        <v>-0.4811350234835826</v>
+        <v>-7.826930820144157</v>
       </c>
       <c r="R11" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S11" s="11" t="n">
-        <v>-0.0055488172878194</v>
+        <v>-0.0501358828170808</v>
       </c>
     </row>
     <row r="12">
@@ -2132,49 +2132,49 @@
         <v>20</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>-32.71817278261615</v>
+        <v>-58.54512476682988</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>2.948986933897394</v>
+        <v>2.756572747424272</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>-62.61227486159108</v>
+        <v>-62.61227469202054</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>2.142143740923359</v>
+        <v>2.142182410442778</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>-4.490151895423597</v>
+        <v>-4.490140927904899</v>
       </c>
       <c r="L12" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.6675634762267375</v>
+        <v>0.6675198089481782</v>
       </c>
       <c r="N12" s="11" t="n">
-        <v>34.8642410272394</v>
+        <v>16.35514176370537</v>
       </c>
       <c r="O12" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P12" s="11" t="n">
-        <v>0.1436805633924152</v>
+        <v>-0.0320734986839532</v>
       </c>
       <c r="Q12" s="11" t="n">
-        <v>-0.4799870528408947</v>
+        <v>-7.797850910609812</v>
       </c>
       <c r="R12" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S12" s="11" t="n">
-        <v>-0.0044008466451315</v>
+        <v>-0.0210559732827357</v>
       </c>
     </row>
     <row r="13">
@@ -2193,49 +2193,49 @@
         <v>20</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>-33.21123212372167</v>
+        <v>-60.29709245999716</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>2.455927592791873</v>
+        <v>1.004605054256992</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>-63.99141584314215</v>
+        <v>-63.99407402140891</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>0.7630027593722843</v>
+        <v>0.7603830810544139</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>-4.703120405410758</v>
+        <v>-4.702815722256829</v>
       </c>
       <c r="L13" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.4545949662395756</v>
+        <v>0.4548450145962484</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>35.95840930368886</v>
+        <v>16.24484973929352</v>
       </c>
       <c r="O13" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>1.237848839841874</v>
+        <v>-0.1423655230957976</v>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>-0.4751051788576246</v>
+        <v>-7.845052455624931</v>
       </c>
       <c r="R13" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S13" s="11" t="n">
-        <v>0.0004810273381385</v>
+        <v>-0.0682575182978553</v>
       </c>
     </row>
     <row r="14">
@@ -2254,49 +2254,49 @@
         <v>20</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>-43.10998509648838</v>
+        <v>-61.57343687057524</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>-7.442825379974835</v>
+        <v>-0.2717393563210919</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>-66.41449406147009</v>
+        <v>-66.41449269240837</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>-1.66007545895566</v>
+        <v>-1.660035589945053</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>-4.067670983253389</v>
+        <v>-4.067676598794622</v>
       </c>
       <c r="L14" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>1.090044388396945</v>
+        <v>1.089984138058456</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>27.84993564193609</v>
+        <v>16.66144093865418</v>
       </c>
       <c r="O14" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P14" s="11" t="n">
-        <v>-6.870624821910898</v>
+        <v>0.2742256762648658</v>
       </c>
       <c r="Q14" s="11" t="n">
-        <v>-0.4777556937009836</v>
+        <v>-7.752708518026434</v>
       </c>
       <c r="R14" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S14" s="11" t="n">
-        <v>-0.0021694875052204</v>
+        <v>0.0240864193006418</v>
       </c>
     </row>
     <row r="15">
@@ -2315,49 +2315,49 @@
         <v>20</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>-35.54336182561863</v>
+        <v>-57.98237852910865</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.1237978908949202</v>
+        <v>3.3193189851455</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>-62.03527000088295</v>
+        <v>-62.03527106405007</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>2.719148601631488</v>
+        <v>2.719186038413248</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>-6.661058419226562</v>
+        <v>-6.661065658252228</v>
       </c>
       <c r="L15" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>-1.503343047576228</v>
+        <v>-1.50340492139915</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>33.63615195792218</v>
+        <v>18.5206592880745</v>
       </c>
       <c r="O15" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P15" s="11" t="n">
-        <v>-1.084408505924806</v>
+        <v>2.133444025685183</v>
       </c>
       <c r="Q15" s="11" t="n">
-        <v>-0.4831853634312776</v>
+        <v>-7.806701094880841</v>
       </c>
       <c r="R15" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S15" s="11" t="n">
-        <v>-0.0075991572355144</v>
+        <v>-0.0299061575537651</v>
       </c>
     </row>
     <row r="16">
@@ -2376,49 +2376,49 @@
         <v>20</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>-33.74269609549</v>
+        <v>-58.63127032700357</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>1.924463621023541</v>
+        <v>2.670427187250582</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>-63.26608317490327</v>
+        <v>-63.26608188952637</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>1.488335427611162</v>
+        <v>1.488375212936951</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>-4.107859421942248</v>
+        <v>-4.107889419069558</v>
       </c>
       <c r="L16" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>1.049855949708086</v>
+        <v>1.049771317783519</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>34.11331629206072</v>
+        <v>16.50183880078405</v>
       </c>
       <c r="O16" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P16" s="11" t="n">
-        <v>-0.6072441717862702</v>
+        <v>0.1146235383947313</v>
       </c>
       <c r="Q16" s="11" t="n">
-        <v>-0.4820697907052122</v>
+        <v>-7.759137819191694</v>
       </c>
       <c r="R16" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S16" s="11" t="n">
-        <v>-0.006483584509449</v>
+        <v>0.0176571181353821</v>
       </c>
     </row>
     <row r="17">
@@ -2437,49 +2437,49 @@
         <v>20</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>-29.04065097873226</v>
+        <v>-54.50895927638678</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>6.62650873778129</v>
+        <v>6.792738237867376</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>-59.90483063441364</v>
+        <v>-59.90482862501473</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>4.849587968100792</v>
+        <v>4.84962847744859</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-4.037275460294275</v>
+        <v>-4.037250787195392</v>
       </c>
       <c r="L17" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>1.120439911356059</v>
+        <v>1.120409949657685</v>
       </c>
       <c r="N17" s="11" t="n">
-        <v>35.3787468450703</v>
+        <v>17.15384295520089</v>
       </c>
       <c r="O17" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P17" s="11" t="n">
-        <v>0.6581863812233166</v>
+        <v>0.7666276928115749</v>
       </c>
       <c r="Q17" s="11" t="n">
-        <v>-0.4772917290946493</v>
+        <v>-7.72072281937754</v>
       </c>
       <c r="R17" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S17" s="11" t="n">
-        <v>-0.0017055228988861</v>
+        <v>0.0560721179495358</v>
       </c>
     </row>
     <row r="18">
@@ -2498,49 +2498,49 @@
         <v>20</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>-37.65366982693976</v>
+        <v>-61.02533259679956</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>-1.986510110426217</v>
+        <v>0.2763649174545932</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>-65.51901937381633</v>
+        <v>-65.51826530061513</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>-0.7646007713019003</v>
+        <v>-0.763808198151807</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-4.677199452741126</v>
+        <v>-4.679931101455661</v>
       </c>
       <c r="L18" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.4805159189092078</v>
+        <v>0.4777296353974156</v>
       </c>
       <c r="N18" s="11" t="n">
-        <v>33.02619023031303</v>
+        <v>16.99341861513331</v>
       </c>
       <c r="O18" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P18" s="11" t="n">
-        <v>-1.694370233533952</v>
+        <v>0.6062033527439894</v>
       </c>
       <c r="Q18" s="11" t="n">
-        <v>-0.4836412306953342</v>
+        <v>-7.820554809862067</v>
       </c>
       <c r="R18" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S18" s="11" t="n">
-        <v>-0.008055024499571</v>
+        <v>-0.0437598725349905</v>
       </c>
     </row>
     <row r="19">
@@ -2559,49 +2559,49 @@
         <v>20</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>-25.79526402845726</v>
+        <v>-55.64405797071347</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>9.871895688056291</v>
+        <v>5.657639543540675</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>-61.11640207226545</v>
+        <v>-61.11640360523064</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>3.638016530248983</v>
+        <v>3.638053497232676</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-2.037502896841582</v>
+        <v>-2.037497159693286</v>
       </c>
       <c r="L19" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>3.120212474808753</v>
+        <v>3.120163577159791</v>
       </c>
       <c r="N19" s="11" t="n">
-        <v>37.8350413438239</v>
+        <v>15.33871089067332</v>
       </c>
       <c r="O19" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P19" s="11" t="n">
-        <v>3.114480879976909</v>
+        <v>-1.048504371716003</v>
       </c>
       <c r="Q19" s="11" t="n">
-        <v>-0.476400403174114</v>
+        <v>-7.828868096462854</v>
       </c>
       <c r="R19" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S19" s="11" t="n">
-        <v>-0.0008141969783508</v>
+        <v>-0.0520731591357774</v>
       </c>
     </row>
     <row r="20">
@@ -2620,49 +2620,49 @@
         <v>20</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>-33.05611532149674</v>
+        <v>-60.15856280054541</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>2.611044395016805</v>
+        <v>1.143134713708747</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>-63.74071036001545</v>
+        <v>-63.74071027614355</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>1.013708242498986</v>
+        <v>1.013746826319768</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-8.937913586252879</v>
+        <v>-8.937973342975797</v>
       </c>
       <c r="L20" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>-3.780198214602545</v>
+        <v>-3.780312606122719</v>
       </c>
       <c r="N20" s="11" t="n">
-        <v>40.10617960365506</v>
+        <v>20.3708685606889</v>
       </c>
       <c r="O20" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P20" s="11" t="n">
-        <v>5.385619139808078</v>
+        <v>3.983653298299582</v>
       </c>
       <c r="Q20" s="11" t="n">
-        <v>-0.4836709788834843</v>
+        <v>-7.85074774211497</v>
       </c>
       <c r="R20" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S20" s="11" t="n">
-        <v>-0.008084772687721099</v>
+        <v>-0.0739528047878934</v>
       </c>
     </row>
     <row r="21">
@@ -2681,49 +2681,49 @@
         <v>20</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-35.11393286354969</v>
+        <v>-61.97963745506794</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.5532268529638529</v>
+        <v>-0.6779399408137934</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>-65.17569648099004</v>
+        <v>-65.17569662796534</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>-0.4212778784756068</v>
+        <v>-0.4212395255020169</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-8.508231311519568</v>
+        <v>-8.508178497891654</v>
       </c>
       <c r="L21" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>-3.350515939869234</v>
+        <v>-3.350517761038577</v>
       </c>
       <c r="N21" s="11" t="n">
-        <v>39.04798885034557</v>
+        <v>19.48341343188605</v>
       </c>
       <c r="O21" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P21" s="11" t="n">
-        <v>4.327428386498582</v>
+        <v>3.096198169496731</v>
       </c>
       <c r="Q21" s="11" t="n">
-        <v>-0.4779939213856684</v>
+        <v>-7.77917576109702</v>
       </c>
       <c r="R21" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S21" s="11" t="n">
-        <v>-0.0024077151899052</v>
+        <v>-0.0023808237699434</v>
       </c>
     </row>
     <row r="22">
@@ -2742,49 +2742,49 @@
         <v>20</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>-34.22505395829296</v>
+        <v>-61.5331207165103</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>1.442105758220585</v>
+        <v>-0.2314232022561455</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>-66.2081154191534</v>
+        <v>-66.20811550640951</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>-1.453696816638967</v>
+        <v>-1.453658403946193</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-6.333089548830483</v>
+        <v>-6.333086500380483</v>
       </c>
       <c r="L22" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>-1.175374177180148</v>
+        <v>-1.175425763527406</v>
       </c>
       <c r="N22" s="11" t="n">
-        <v>38.80164591349789</v>
+        <v>18.87124136346704</v>
       </c>
       <c r="O22" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P22" s="11" t="n">
-        <v>4.081085449650907</v>
+        <v>2.48402610107772</v>
       </c>
       <c r="Q22" s="11" t="n">
-        <v>-0.4854949038069744</v>
+        <v>-7.863160073187337</v>
       </c>
       <c r="R22" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S22" s="11" t="n">
-        <v>-0.009908697611211201</v>
+        <v>-0.08636513586026059</v>
       </c>
     </row>
     <row r="23">
@@ -2803,49 +2803,49 @@
         <v>20</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-21.78320449715924</v>
+        <v>-54.49690429425115</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>13.8839552193543</v>
+        <v>6.804793220003006</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>-58.9858808087252</v>
+        <v>-58.98587325027746</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>5.768537793789235</v>
+        <v>5.768583852185863</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-6.466641502156</v>
+        <v>-6.466531464348951</v>
       </c>
       <c r="L23" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>-1.308926130505666</v>
+        <v>-1.308870727495874</v>
       </c>
       <c r="N23" s="11" t="n">
-        <v>44.15207367326288</v>
+        <v>18.74740693582859</v>
       </c>
       <c r="O23" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P23" s="11" t="n">
-        <v>9.43151320941589</v>
+        <v>2.360191673439274</v>
       </c>
       <c r="Q23" s="11" t="n">
-        <v>-0.4827558595409356</v>
+        <v>-7.791906515453331</v>
       </c>
       <c r="R23" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S23" s="11" t="n">
-        <v>-0.0071696533451724</v>
+        <v>-0.0151115781262545</v>
       </c>
     </row>
     <row r="24">
@@ -2864,49 +2864,49 @@
         <v>20</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>-27.22502990804648</v>
+        <v>-60.87776335441026</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>8.442129808467065</v>
+        <v>0.4239341598438884</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>-65.10583364273928</v>
+        <v>-65.10583651964386</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>-0.3514150402248504</v>
+        <v>-0.3513794171805386</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-7.565567257525522</v>
+        <v>-7.565568498184634</v>
       </c>
       <c r="L24" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>-2.407851885875188</v>
+        <v>-2.407907761331557</v>
       </c>
       <c r="N24" s="11" t="n">
-        <v>45.92117063174056</v>
+        <v>19.62118531732213</v>
       </c>
       <c r="O24" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P24" s="11" t="n">
-        <v>11.20061016789357</v>
+        <v>3.233970054932808</v>
       </c>
       <c r="Q24" s="11" t="n">
-        <v>-0.4747996395222315</v>
+        <v>-7.827543653903909</v>
       </c>
       <c r="R24" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S24" s="11" t="n">
-        <v>0.0007865666735316</v>
+        <v>-0.050748716576833</v>
       </c>
     </row>
     <row r="25">
@@ -2925,49 +2925,49 @@
         <v>20</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-23.63820978538552</v>
+        <v>-59.78870920825561</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>12.02894993112802</v>
+        <v>1.512988305998541</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>-64.65130331359043</v>
+        <v>-64.65130407316083</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>0.1031152889240019</v>
+        <v>0.10315302930249</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-3.822781004103541</v>
+        <v>-3.822781947900198</v>
       </c>
       <c r="L25" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>1.334934367546793</v>
+        <v>1.334878788952878</v>
       </c>
       <c r="N25" s="11" t="n">
-        <v>45.31337083183784</v>
+        <v>16.54667535201997</v>
       </c>
       <c r="O25" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P25" s="11" t="n">
-        <v>10.59281036799085</v>
+        <v>0.1594600896306524</v>
       </c>
       <c r="Q25" s="11" t="n">
-        <v>-0.4774962995293947</v>
+        <v>-7.861298539214563</v>
       </c>
       <c r="R25" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S25" s="11" t="n">
-        <v>-0.0019100933336315</v>
+        <v>-0.08450360188748619</v>
       </c>
     </row>
     <row r="26">
@@ -2986,49 +2986,49 @@
         <v>20</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>-18.24107440237752</v>
+        <v>-56.23167550373125</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>17.42608531413602</v>
+        <v>5.070022010522905</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>-61.64262997512676</v>
+        <v>-61.64263364763021</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>3.111788627387675</v>
+        <v>3.111823454833107</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-4.498734262847835</v>
+        <v>-4.498803788211503</v>
       </c>
       <c r="L26" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.6589811088024993</v>
+        <v>0.6588569486415743</v>
       </c>
       <c r="N26" s="11" t="n">
-        <v>48.3882125659381</v>
+        <v>17.8066688103612</v>
       </c>
       <c r="O26" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P26" s="11" t="n">
-        <v>13.66765210209111</v>
+        <v>1.419453547971884</v>
       </c>
       <c r="Q26" s="11" t="n">
-        <v>-0.4879227303410123</v>
+        <v>-7.896906878250734</v>
       </c>
       <c r="R26" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S26" s="11" t="n">
-        <v>-0.0123365241452491</v>
+        <v>-0.1201119409236577</v>
       </c>
     </row>
     <row r="27">
@@ -3047,49 +3047,49 @@
         <v>20</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>-22.54660674501336</v>
+        <v>-56.75418016582527</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>13.12055297150018</v>
+        <v>4.547517348428883</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>-60.69814008335682</v>
+        <v>-60.69818288034396</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>4.056278519157615</v>
+        <v>4.056274222119363</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>-7.941571199197357</v>
+        <v>-7.941646672994097</v>
       </c>
       <c r="L27" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>-2.783855827547023</v>
+        <v>-2.78398593614102</v>
       </c>
       <c r="N27" s="11" t="n">
-        <v>46.57545225912024</v>
+        <v>19.68094399964604</v>
       </c>
       <c r="O27" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P27" s="11" t="n">
-        <v>11.85489179527325</v>
+        <v>3.293728737256721</v>
       </c>
       <c r="Q27" s="11" t="n">
-        <v>-0.4823477215794258</v>
+        <v>-7.795294612133251</v>
       </c>
       <c r="R27" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S27" s="11" t="n">
-        <v>-0.0067615153836625</v>
+        <v>-0.0184996748061747</v>
       </c>
     </row>
     <row r="28">
@@ -3108,49 +3108,49 @@
         <v>20</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>-30.8111313880176</v>
+        <v>-59.78798391748646</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>4.856028328495942</v>
+        <v>1.513713596767687</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>-64.19131310175209</v>
+        <v>-64.19131629642926</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>0.5631055007623473</v>
+        <v>0.5631408060340561</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>-6.677390353391319</v>
+        <v>-6.677345431237479</v>
       </c>
       <c r="L28" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>-1.519674981740985</v>
+        <v>-1.519684694384402</v>
       </c>
       <c r="N28" s="11" t="n">
-        <v>40.53784714830081</v>
+        <v>18.96034025553308</v>
       </c>
       <c r="O28" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P28" s="11" t="n">
-        <v>5.817286684453819</v>
+        <v>2.573124993143757</v>
       </c>
       <c r="Q28" s="11" t="n">
-        <v>-0.4802750811750073</v>
+        <v>-7.87966244535282</v>
       </c>
       <c r="R28" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S28" s="11" t="n">
-        <v>-0.004688874979244</v>
+        <v>-0.1028675080257439</v>
       </c>
     </row>
     <row r="29">
@@ -3169,49 +3169,49 @@
         <v>20</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>-28.18432505777292</v>
+        <v>-57.59823073785321</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>7.482834658740629</v>
+        <v>3.703466776400937</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>-61.97343171829943</v>
+        <v>-61.97343125366397</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>2.780986884215004</v>
+        <v>2.781025848799345</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>-5.590393793305743</v>
+        <v>-5.590443072906336</v>
       </c>
       <c r="L29" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>-0.4326784216554085</v>
+        <v>-0.4327823360532585</v>
       </c>
       <c r="N29" s="11" t="n">
-        <v>39.86100418845736</v>
+        <v>17.71805327435525</v>
       </c>
       <c r="O29" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P29" s="11" t="n">
-        <v>5.140443724610378</v>
+        <v>1.330838011965927</v>
       </c>
       <c r="Q29" s="11" t="n">
-        <v>-0.4815037346250923</v>
+        <v>-7.752409685638165</v>
       </c>
       <c r="R29" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S29" s="11" t="n">
-        <v>-0.005917528429329</v>
+        <v>0.0243852516889111</v>
       </c>
     </row>
     <row r="30">
@@ -3230,49 +3230,49 @@
         <v>20</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>-34.05851287210012</v>
+        <v>-58.17670985317134</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>1.608646844413428</v>
+        <v>3.124987661082812</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>-63.00614319543035</v>
+        <v>-63.00614600210751</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>1.748275407084087</v>
+        <v>1.748311100355814</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>-5.710258788331772</v>
+        <v>-5.710268218553766</v>
       </c>
       <c r="L30" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>-0.5525434166814378</v>
+        <v>-0.5526074817006892</v>
       </c>
       <c r="N30" s="11" t="n">
-        <v>35.13025515508013</v>
+        <v>18.24825357068793</v>
       </c>
       <c r="O30" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P30" s="11" t="n">
-        <v>0.4096946912331418</v>
+        <v>1.86103830829861</v>
       </c>
       <c r="Q30" s="11" t="n">
-        <v>-0.472366043418133</v>
+        <v>-7.708549203197998</v>
       </c>
       <c r="R30" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S30" s="11" t="n">
-        <v>0.0032201627776302</v>
+        <v>0.0682457341290785</v>
       </c>
     </row>
     <row r="31">
@@ -3291,49 +3291,49 @@
         <v>20</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>-30.6317040214363</v>
+        <v>-58.52017094260428</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>5.03545569507725</v>
+        <v>2.78152657164987</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>-63.29482297467368</v>
+        <v>-63.29482336478142</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>1.459595627840756</v>
+        <v>1.459633737681898</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-5.933354515753748</v>
+        <v>-5.933334889971996</v>
       </c>
       <c r="L31" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>-0.7756391441034136</v>
+        <v>-0.7756741531189189</v>
       </c>
       <c r="N31" s="11" t="n">
-        <v>39.07326718589316</v>
+        <v>18.41089479326062</v>
       </c>
       <c r="O31" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P31" s="11" t="n">
-        <v>4.352706722046172</v>
+        <v>2.023679530871302</v>
       </c>
       <c r="Q31" s="11" t="n">
-        <v>-0.4767937169020308</v>
+        <v>-7.702907481111486</v>
       </c>
       <c r="R31" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S31" s="11" t="n">
-        <v>-0.0012075107062676</v>
+        <v>0.0738874562155897</v>
       </c>
     </row>
     <row r="32">
@@ -3352,49 +3352,49 @@
         <v>20</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>-40.34333539775993</v>
+        <v>-60.30164230872904</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>-4.676175681246384</v>
+        <v>1.000055205525108</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>-63.16150952874906</v>
+        <v>-63.16150760840875</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>1.592909073765369</v>
+        <v>1.592949494054565</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-6.480474057332458</v>
+        <v>-6.480429457127567</v>
       </c>
       <c r="L32" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>-1.322758685682124</v>
+        <v>-1.32276872027449</v>
       </c>
       <c r="N32" s="11" t="n">
-        <v>29.7713180772433</v>
+        <v>17.18025941465826</v>
       </c>
       <c r="O32" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P32" s="11" t="n">
-        <v>-4.949242386603682</v>
+        <v>0.7930441522689442</v>
       </c>
       <c r="Q32" s="11" t="n">
-        <v>-0.472669888921723</v>
+        <v>-7.839964657850976</v>
       </c>
       <c r="R32" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S32" s="11" t="n">
-        <v>0.0029163172740401</v>
+        <v>-0.0631697205239003</v>
       </c>
     </row>
     <row r="33">
@@ -3413,49 +3413,49 @@
         <v>20</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>-32.4361502624355</v>
+        <v>-59.57150153911532</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>3.231009454078048</v>
+        <v>1.730195975138834</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>-63.18072566293289</v>
+        <v>-63.18273796178212</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>1.573692939581541</v>
+        <v>1.571719140681203</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-5.352694841275529</v>
+        <v>-5.352000285819262</v>
       </c>
       <c r="L33" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>-0.1949794696251947</v>
+        <v>-0.1943395489661847</v>
       </c>
       <c r="N33" s="11" t="n">
-        <v>36.57039155467746</v>
+        <v>16.8620191614213</v>
       </c>
       <c r="O33" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P33" s="11" t="n">
-        <v>1.84983109083047</v>
+        <v>0.4748038990319827</v>
       </c>
       <c r="Q33" s="11" t="n">
-        <v>-0.4731213129045402</v>
+        <v>-7.898782452935242</v>
       </c>
       <c r="R33" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S33" s="11" t="n">
-        <v>0.0024648932912229</v>
+        <v>-0.1219875156081657</v>
       </c>
     </row>
     <row r="34">
@@ -3474,49 +3474,49 @@
         <v>20</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>-32.11334982389737</v>
+        <v>-60.13329214631469</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>3.553809892616179</v>
+        <v>1.168405367939464</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>-64.08038121130717</v>
+        <v>-64.08038290318132</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>0.6740373912072641</v>
+        <v>0.6740741992820034</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-5.214932810122814</v>
+        <v>-5.21489765101964</v>
       </c>
       <c r="L34" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>-0.0572174384724801</v>
+        <v>-0.0572369141665625</v>
       </c>
       <c r="N34" s="11" t="n">
-        <v>37.66525296590524</v>
+        <v>17.01946194723505</v>
       </c>
       <c r="O34" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P34" s="11" t="n">
-        <v>2.944692502058253</v>
+        <v>0.6322466848457289</v>
       </c>
       <c r="Q34" s="11" t="n">
-        <v>-0.4832887683726177</v>
+        <v>-7.857473539348769</v>
       </c>
       <c r="R34" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S34" s="11" t="n">
-        <v>-0.0077025621768544</v>
+        <v>-0.08067860202169271</v>
       </c>
     </row>
     <row r="35">
@@ -3535,49 +3535,49 @@
         <v>20</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>-37.43642670715465</v>
+        <v>-62.5613625570908</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>-1.769266990641107</v>
+        <v>-1.259665042836644</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>-65.98428133486048</v>
+        <v>-65.98383724639633</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>-1.229862732346049</v>
+        <v>-1.229380143933014</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-9.575069981870502</v>
+        <v>-9.574870341572057</v>
       </c>
       <c r="L35" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>-4.417354610220168</v>
+        <v>-4.417209604718979</v>
       </c>
       <c r="N35" s="11" t="n">
-        <v>38.60072027428884</v>
+        <v>20.89216795751743</v>
       </c>
       <c r="O35" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P35" s="11" t="n">
-        <v>3.880159810441853</v>
+        <v>4.504952695128111</v>
       </c>
       <c r="Q35" s="11" t="n">
-        <v>-0.4777956647125301</v>
+        <v>-7.894822926639827</v>
       </c>
       <c r="R35" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S35" s="11" t="n">
-        <v>-0.0022094585167669</v>
+        <v>-0.1180279893127504</v>
       </c>
     </row>
     <row r="36">
@@ -3596,49 +3596,49 @@
         <v>20</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>-33.25333839100333</v>
+        <v>-61.91514169677578</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>2.413821325510213</v>
+        <v>-0.6134441825216257</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>-65.16501865139527</v>
+        <v>-65.16394100651007</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>-0.4106000488808377</v>
+        <v>-0.4094839040467519</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-9.438320759405906</v>
+        <v>-9.437609487177889</v>
       </c>
       <c r="L36" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>-4.280605387755572</v>
+        <v>-4.279948750324812</v>
       </c>
       <c r="N36" s="11" t="n">
-        <v>41.82641763190238</v>
+        <v>20.46887719608402</v>
       </c>
       <c r="O36" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P36" s="11" t="n">
-        <v>7.105857168055394</v>
+        <v>4.081661933694697</v>
       </c>
       <c r="Q36" s="11" t="n">
-        <v>-0.4764166121045216</v>
+        <v>-7.782468399171847</v>
       </c>
       <c r="R36" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S36" s="11" t="n">
-        <v>-0.0008304059087583</v>
+        <v>-0.0056734618447711</v>
       </c>
     </row>
     <row r="37">
@@ -3657,49 +3657,49 @@
         <v>20</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>-36.27884679542835</v>
+        <v>-63.00172247966147</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>-0.6116870789148052</v>
+        <v>-1.700024965407323</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>-65.89967392694652</v>
+        <v>-65.89967287541641</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>-1.145255324432085</v>
+        <v>-1.145215772953094</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-8.446105045706355</v>
+        <v>-8.446186896308308</v>
       </c>
       <c r="L37" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>-3.288389674056021</v>
+        <v>-3.288526159455231</v>
       </c>
       <c r="N37" s="11" t="n">
-        <v>38.54254868814639</v>
+        <v>19.1092737318225</v>
       </c>
       <c r="O37" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P37" s="11" t="n">
-        <v>3.821988224299403</v>
+        <v>2.722058469433176</v>
       </c>
       <c r="Q37" s="11" t="n">
-        <v>-0.4756165109218648</v>
+        <v>-7.765136439759234</v>
       </c>
       <c r="R37" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S37" s="11" t="n">
-        <v>-3.030472610160428e-05</v>
+        <v>0.0116584975678417</v>
       </c>
     </row>
     <row r="38">
@@ -3718,49 +3718,49 @@
         <v>20</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>-27.17333898332586</v>
+        <v>-58.06026504696791</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>8.493820733187686</v>
+        <v>3.241432467286238</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>-61.90727971114386</v>
+        <v>-61.91012103099054</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>2.84713889137057</v>
+        <v>2.844336071472782</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-5.875180623305511</v>
+        <v>-5.86924772749036</v>
       </c>
       <c r="L38" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>-0.7174652516551774</v>
+        <v>-0.7115869906372829</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>41.08093746761519</v>
+        <v>17.44520755388541</v>
       </c>
       <c r="O38" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P38" s="11" t="n">
-        <v>6.3603770037682</v>
+        <v>1.057992291496088</v>
       </c>
       <c r="Q38" s="11" t="n">
-        <v>-0.4718161164916496</v>
+        <v>-7.726103842372419</v>
       </c>
       <c r="R38" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S38" s="11" t="n">
-        <v>0.0037700897041135</v>
+        <v>0.050691094954657</v>
       </c>
     </row>
     <row r="39">
@@ -3779,49 +3779,49 @@
         <v>20</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>-29.79211268871731</v>
+        <v>-61.78597657317346</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>5.875047027796235</v>
+        <v>-0.4842790589193129</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>-65.70403434240085</v>
+        <v>-65.70403460847369</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>-0.9496157398864112</v>
+        <v>-0.9495775060103711</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-5.909557947086983</v>
+        <v>-5.909475539834359</v>
       </c>
       <c r="L39" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>-0.7518425754366485</v>
+        <v>-0.7518148029812819</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>42.29413415688174</v>
+        <v>17.60417170551949</v>
       </c>
       <c r="O39" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P39" s="11" t="n">
-        <v>7.573573693034753</v>
+        <v>1.216956443130172</v>
       </c>
       <c r="Q39" s="11" t="n">
-        <v>-0.4726545561112135</v>
+        <v>-7.776638130384922</v>
       </c>
       <c r="R39" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S39" s="11" t="n">
-        <v>0.0029316500845496</v>
+        <v>0.0001568069421544</v>
       </c>
     </row>
     <row r="40">
@@ -3840,49 +3840,49 @@
         <v>20</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>-28.79609066738491</v>
+        <v>-59.08622165551841</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>6.871069049128632</v>
+        <v>2.215475858735736</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>-62.9354927381219</v>
+        <v>-62.93549091362927</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>1.818925864392533</v>
+        <v>1.818966188834047</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-5.462823711687499</v>
+        <v>-5.462805377615453</v>
       </c>
       <c r="L40" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>-0.3051083400371652</v>
+        <v>-0.3051446407623759</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>40.07730690288726</v>
+        <v>17.05421526163076</v>
       </c>
       <c r="O40" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P40" s="11" t="n">
-        <v>5.356746439040272</v>
+        <v>0.6669999992414368</v>
       </c>
       <c r="Q40" s="11" t="n">
-        <v>-0.475081120462764</v>
+        <v>-7.74214062590444</v>
       </c>
       <c r="R40" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S40" s="11" t="n">
-        <v>0.0005050857329991</v>
+        <v>0.0346543114226358</v>
       </c>
     </row>
     <row r="41">
@@ -3901,49 +3901,49 @@
         <v>20</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>-35.8891214450185</v>
+        <v>-60.53319473292832</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>-0.2219617285049508</v>
+        <v>0.7685027813258358</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>-63.74590132526794</v>
+        <v>-63.7459013867914</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>1.00851727724649</v>
+        <v>1.008555715671925</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>-5.791598628589125</v>
+        <v>-5.791564171422675</v>
       </c>
       <c r="L41" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>-0.6338832569387911</v>
+        <v>-0.6339034345695982</v>
       </c>
       <c r="N41" s="11" t="n">
-        <v>34.12564042421418</v>
+        <v>16.74756547916916</v>
       </c>
       <c r="O41" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P41" s="11" t="n">
-        <v>-0.5949200396328109</v>
+        <v>0.3603502167798389</v>
       </c>
       <c r="Q41" s="11" t="n">
-        <v>-0.47726191537558</v>
+        <v>-7.743294653883399</v>
       </c>
       <c r="R41" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S41" s="11" t="n">
-        <v>-0.0016757091798168</v>
+        <v>0.0335002834436775</v>
       </c>
     </row>
     <row r="42">
@@ -3962,49 +3962,49 @@
         <v>20</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>-35.94132024191366</v>
+        <v>-61.80765315237722</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>-0.2741605254001129</v>
+        <v>-0.5059556381230692</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>-65.34107216501329</v>
+        <v>-65.34107268208079</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>-0.5866535624988529</v>
+        <v>-0.5866155796174723</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>-5.953047661045654</v>
+        <v>-5.953008493136918</v>
       </c>
       <c r="L42" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>-0.7953322893953194</v>
+        <v>-0.7953477562838414</v>
       </c>
       <c r="N42" s="11" t="n">
-        <v>35.83532776363037</v>
+        <v>17.29356239676247</v>
       </c>
       <c r="O42" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P42" s="11" t="n">
-        <v>1.114767299783381</v>
+        <v>0.9063471343731564</v>
       </c>
       <c r="Q42" s="11" t="n">
-        <v>-0.4825281794850731</v>
+        <v>-7.807134373921965</v>
       </c>
       <c r="R42" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S42" s="11" t="n">
-        <v>-0.0069419732893098</v>
+        <v>-0.0303394365948888</v>
       </c>
     </row>
     <row r="43">
@@ -4023,49 +4023,49 @@
         <v>20</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>-25.18526898885797</v>
+        <v>-59.32647293942762</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>10.48189072765558</v>
+        <v>1.975224574826527</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>-63.5773309183099</v>
+        <v>-63.57733225208035</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>1.177087684204537</v>
+        <v>1.177124850382974</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>-4.851316767664405</v>
+        <v>-4.85127797442517</v>
       </c>
       <c r="L43" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.3063986039859294</v>
+        <v>0.3063827624279076</v>
       </c>
       <c r="N43" s="11" t="n">
-        <v>43.72429664230711</v>
+        <v>16.96733945186462</v>
       </c>
       <c r="O43" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P43" s="11" t="n">
-        <v>9.003736178460123</v>
+        <v>0.5801241894752991</v>
       </c>
       <c r="Q43" s="11" t="n">
-        <v>-0.4809179451907797</v>
+        <v>-7.865202164786723</v>
       </c>
       <c r="R43" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S43" s="11" t="n">
-        <v>-0.0053317389950165</v>
+        <v>-0.0884072274596468</v>
       </c>
     </row>
     <row r="44">
@@ -4084,49 +4084,49 @@
         <v>20</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>-30.87829373746672</v>
+        <v>-59.18165058214841</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>4.788865979046825</v>
+        <v>2.120046932105744</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>-64.21470227366517</v>
+        <v>-64.21470099582221</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>0.5397163288492663</v>
+        <v>0.5397561066411072</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>-3.814387828445404</v>
+        <v>-3.814380327908014</v>
       </c>
       <c r="L44" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>1.34332754320493</v>
+        <v>1.343280408945064</v>
       </c>
       <c r="N44" s="11" t="n">
-        <v>37.6310898343646</v>
+        <v>16.65965029204097</v>
       </c>
       <c r="O44" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P44" s="11" t="n">
-        <v>2.910529370517615</v>
+        <v>0.2724350296516498</v>
       </c>
       <c r="Q44" s="11" t="n">
-        <v>-0.4802934697207711</v>
+        <v>-7.812219550459153</v>
       </c>
       <c r="R44" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S44" s="11" t="n">
-        <v>-0.0047072635250078</v>
+        <v>-0.0354246131320765</v>
       </c>
     </row>
     <row r="45">
@@ -4145,49 +4145,49 @@
         <v>20</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>-26.95948576320606</v>
+        <v>-55.42285830447707</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>8.707673953307484</v>
+        <v>5.878839209777084</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>-60.83490246617581</v>
+        <v>-60.83490077532724</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>3.919516136338629</v>
+        <v>3.919556327136078</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-3.840169054768116</v>
+        <v>-3.840135628291593</v>
       </c>
       <c r="L45" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>1.317546316882218</v>
+        <v>1.317525108561484</v>
       </c>
       <c r="N45" s="11" t="n">
-        <v>38.19187369560875</v>
+        <v>16.94067463592179</v>
       </c>
       <c r="O45" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P45" s="11" t="n">
-        <v>3.471313231761769</v>
+        <v>0.5534593735324727</v>
       </c>
       <c r="Q45" s="11" t="n">
-        <v>-0.4762879378709009</v>
+        <v>-7.688496536780041</v>
       </c>
       <c r="R45" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S45" s="11" t="n">
-        <v>-0.0007017316751377</v>
+        <v>0.0882984005470355</v>
       </c>
     </row>
     <row r="46">
@@ -4206,49 +4206,49 @@
         <v>20</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>-32.84593446723435</v>
+        <v>-59.63697535581024</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>2.821225249279195</v>
+        <v>1.664722158443908</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>-65.0480496028716</v>
+        <v>-65.04804927275309</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>-0.2936310003571662</v>
+        <v>-0.2935921702897701</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-5.150542940357292</v>
+        <v>-5.150551944814009</v>
       </c>
       <c r="L46" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.0071724312930419</v>
+        <v>0.0071087920390677</v>
       </c>
       <c r="N46" s="11" t="n">
-        <v>37.8363767442922</v>
+        <v>18.36838548999443</v>
       </c>
       <c r="O46" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P46" s="11" t="n">
-        <v>3.115816280445216</v>
+        <v>1.981170227605116</v>
       </c>
       <c r="Q46" s="11" t="n">
-        <v>-0.4837186682976455</v>
+        <v>-7.806759628237548</v>
       </c>
       <c r="R46" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S46" s="11" t="n">
-        <v>-0.008132462101882201</v>
+        <v>-0.0299646909104716</v>
       </c>
     </row>
     <row r="47">
@@ -4267,49 +4267,49 @@
         <v>20</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>-31.63099246176284</v>
+        <v>-58.31968520485806</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>4.036167254750708</v>
+        <v>2.98201230939609</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>-62.73820750551622</v>
+        <v>-62.73820438972925</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>2.016211096998212</v>
+        <v>2.016252712734065</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-3.86568842203821</v>
+        <v>-3.865719143570169</v>
       </c>
       <c r="L47" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>1.292026949612125</v>
+        <v>1.291941593282908</v>
       </c>
       <c r="N47" s="11" t="n">
-        <v>35.4483372964549</v>
+        <v>16.06952902463836</v>
       </c>
       <c r="O47" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P47" s="11" t="n">
-        <v>0.7277768326079155</v>
+        <v>-0.317686237750955</v>
       </c>
       <c r="Q47" s="11" t="n">
-        <v>-0.4754338306633053</v>
+        <v>-7.785290696196985</v>
       </c>
       <c r="R47" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S47" s="11" t="n">
-        <v>0.0001523755324578</v>
+        <v>-0.008495758869909</v>
       </c>
     </row>
     <row r="48">
@@ -4328,49 +4328,49 @@
         <v>20</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>-32.03222855103682</v>
+        <v>-57.22677848155779</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>3.634931165476722</v>
+        <v>4.074919032696357</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>-61.68221697632772</v>
+        <v>-61.68221725619855</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>3.072201626186711</v>
+        <v>3.072239846264772</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-4.129828257485446</v>
+        <v>-4.129837336721345</v>
       </c>
       <c r="L48" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>1.027887114164888</v>
+        <v>1.027823400131732</v>
       </c>
       <c r="N48" s="11" t="n">
-        <v>34.26101755343705</v>
+        <v>16.44738048713932</v>
       </c>
       <c r="O48" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P48" s="11" t="n">
-        <v>-0.4595429104099366</v>
+        <v>0.0601652247500013</v>
       </c>
       <c r="Q48" s="11" t="n">
-        <v>-0.4812008706607052</v>
+        <v>-7.862104375777235</v>
       </c>
       <c r="R48" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S48" s="11" t="n">
-        <v>-0.005614664464942</v>
+        <v>-0.0853094384501584</v>
       </c>
     </row>
     <row r="49">
@@ -4389,49 +4389,49 @@
         <v>20</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>-34.19891848619663</v>
+        <v>-58.98110196950307</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>1.468241230316913</v>
+        <v>2.320595544751086</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>-62.06120494598523</v>
+        <v>-62.0612082193985</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>2.693213656529202</v>
+        <v>2.693248883064818</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-5.312440206371054</v>
+        <v>-5.31248320249437</v>
       </c>
       <c r="L49" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>-0.1547248347207199</v>
+        <v>-0.1548224656412928</v>
       </c>
       <c r="N49" s="11" t="n">
-        <v>33.65654284366002</v>
+        <v>16.24498741120727</v>
       </c>
       <c r="O49" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P49" s="11" t="n">
-        <v>-1.064017620186966</v>
+        <v>-0.1422278511820529</v>
       </c>
       <c r="Q49" s="11" t="n">
-        <v>-0.4818161775003655</v>
+        <v>-7.852397958817491</v>
       </c>
       <c r="R49" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S49" s="11" t="n">
-        <v>-0.0062299713046023</v>
+        <v>-0.0756030214904148</v>
       </c>
     </row>
     <row r="50">
@@ -4450,49 +4450,49 @@
         <v>20</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>-34.8244516817598</v>
+        <v>-57.32641850564892</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>0.8427080347537412</v>
+        <v>3.975279008605234</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>-63.57125952354222</v>
+        <v>-63.57125851827502</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>1.183159078972217</v>
+        <v>1.183198584188297</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-1.930816826139262</v>
+        <v>-1.930816636998069</v>
       </c>
       <c r="L50" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>3.226898545511072</v>
+        <v>3.226844099855008</v>
       </c>
       <c r="N50" s="11" t="n">
-        <v>31.15061932950357</v>
+        <v>15.92324349893895</v>
       </c>
       <c r="O50" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P50" s="11" t="n">
-        <v>-3.56994113434342</v>
+        <v>-0.4639717634503721</v>
       </c>
       <c r="Q50" s="11" t="n">
-        <v>-0.4729946615819038</v>
+        <v>-7.74758684931476</v>
       </c>
       <c r="R50" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S50" s="11" t="n">
-        <v>0.0025915446138594</v>
+        <v>0.0292080880123162</v>
       </c>
     </row>
     <row r="51">
@@ -4511,49 +4511,49 @@
         <v>20</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>-35.23151996864701</v>
+        <v>-59.29018530756962</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>0.4356397478665315</v>
+        <v>2.011512206684536</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>-65.14314657132917</v>
+        <v>-65.14314542364707</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>-0.3887279688147345</v>
+        <v>-0.3886883211837499</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-3.574490107605979</v>
+        <v>-3.57445247042646</v>
       </c>
       <c r="L51" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>1.583225264044355</v>
+        <v>1.583208266426618</v>
       </c>
       <c r="N51" s="11" t="n">
-        <v>33.97512156694386</v>
+        <v>17.34289575945123</v>
       </c>
       <c r="O51" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P51" s="11" t="n">
-        <v>-0.7454388969031243</v>
+        <v>0.9556804970619126</v>
       </c>
       <c r="Q51" s="11" t="n">
-        <v>-0.4890048566557481</v>
+        <v>-7.915483172947316</v>
       </c>
       <c r="R51" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S51" s="11" t="n">
-        <v>-0.0134186504599849</v>
+        <v>-0.1386882356202399</v>
       </c>
     </row>
     <row r="52">
@@ -4572,49 +4572,49 @@
         <v>20</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>-42.41999023004849</v>
+        <v>-60.92781963333002</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>-6.752830513534946</v>
+        <v>0.3738778809241267</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>-66.08428334539479</v>
+        <v>-66.08428336858883</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>-1.32986474288036</v>
+        <v>-1.329826266125508</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-7.526626481533643</v>
+        <v>-7.526608386800825</v>
       </c>
       <c r="L52" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>-2.368911109883309</v>
+        <v>-2.368947649947748</v>
       </c>
       <c r="N52" s="11" t="n">
-        <v>31.67404870914</v>
+        <v>20.45188934807567</v>
       </c>
       <c r="O52" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P52" s="11" t="n">
-        <v>-3.046511754706987</v>
+        <v>4.064674085686356</v>
       </c>
       <c r="Q52" s="11" t="n">
-        <v>-0.4831291122600635</v>
+        <v>-7.768817226016043</v>
       </c>
       <c r="R52" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S52" s="11" t="n">
-        <v>-0.0075429060643003</v>
+        <v>0.007977711311033499</v>
       </c>
     </row>
     <row r="53">
@@ -4633,49 +4633,49 @@
         <v>20</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>-40.40611279466181</v>
+        <v>-60.03717708665371</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G53" s="11" t="n">
-        <v>-4.738953078148263</v>
+        <v>1.264520427600445</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>-65.2535351830397</v>
+        <v>-65.2535346094882</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>-0.4991165805252677</v>
+        <v>-0.4990775070248787</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-4.929266779652279</v>
+        <v>-4.929226938275533</v>
       </c>
       <c r="L53" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.2284485919980552</v>
+        <v>0.2284337985775444</v>
       </c>
       <c r="N53" s="11" t="n">
-        <v>30.25536244275693</v>
+        <v>17.99467895500518</v>
       </c>
       <c r="O53" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P53" s="11" t="n">
-        <v>-4.465198021090057</v>
+        <v>1.607463692615866</v>
       </c>
       <c r="Q53" s="11" t="n">
-        <v>-0.4786732747267582</v>
+        <v>-7.849094493895142</v>
       </c>
       <c r="R53" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S53" s="11" t="n">
-        <v>-0.0030870685309949</v>
+        <v>-0.0722995565680655</v>
       </c>
     </row>
     <row r="54">
@@ -4694,49 +4694,49 @@
         <v>20</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>-35.58460223821974</v>
+        <v>-59.52295414933317</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>0.08255747829380761</v>
+        <v>1.778743364920985</v>
       </c>
       <c r="H54" s="11" t="n">
-        <v>-64.54829921068942</v>
+        <v>-64.54830116705351</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>0.2061193918250126</v>
+        <v>0.2061559354098108</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-5.615339624614445</v>
+        <v>-5.615366617463552</v>
       </c>
       <c r="L54" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>-0.457624252964111</v>
+        <v>-0.457705880610475</v>
       </c>
       <c r="N54" s="11" t="n">
-        <v>35.0578973500724</v>
+        <v>18.46999812080573</v>
       </c>
       <c r="O54" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P54" s="11" t="n">
-        <v>0.3373368862254153</v>
+        <v>2.082782858416412</v>
       </c>
       <c r="Q54" s="11" t="n">
-        <v>-0.4788607529882719</v>
+        <v>-7.829284485621844</v>
       </c>
       <c r="R54" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S54" s="11" t="n">
-        <v>-0.0032745467925087</v>
+        <v>-0.0524895482947682</v>
       </c>
     </row>
     <row r="55">
@@ -4755,49 +4755,49 @@
         <v>20</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>-28.77601474245147</v>
+        <v>-56.00069335881275</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>-35.66715971651355</v>
+        <v>-61.30169751425415</v>
       </c>
       <c r="G55" s="11" t="n">
-        <v>6.891144974062083</v>
+        <v>5.301004155441404</v>
       </c>
       <c r="H55" s="11" t="n">
-        <v>-61.09097125119852</v>
+        <v>-61.0909700221228</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>-64.75441860251443</v>
+        <v>-64.75445710246332</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>3.663447351315917</v>
+        <v>3.663487080340517</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>-6.314582497323864</v>
+        <v>-6.314540527644309</v>
       </c>
       <c r="L55" s="11" t="n">
-        <v>-5.157715371650334</v>
+        <v>-5.157660736853077</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>-1.15686712567353</v>
+        <v>-1.156879790791232</v>
       </c>
       <c r="N55" s="11" t="n">
-        <v>39.10854988184759</v>
+        <v>19.3043982321628</v>
       </c>
       <c r="O55" s="11" t="n">
-        <v>34.72056046384699</v>
+        <v>16.38721526238932</v>
       </c>
       <c r="P55" s="11" t="n">
-        <v>4.3879894180006</v>
+        <v>2.917182969773478</v>
       </c>
       <c r="Q55" s="11" t="n">
-        <v>-0.4790108757766665</v>
+        <v>-7.899581041208417</v>
       </c>
       <c r="R55" s="11" t="n">
-        <v>-0.4755862061957632</v>
+        <v>-7.776794937327076</v>
       </c>
       <c r="S55" s="11" t="n">
-        <v>-0.0034246695809033</v>
+        <v>-0.1227861038813404</v>
       </c>
     </row>
   </sheetData>

--- a/manuscript/Supplementary-Table-3.xlsx
+++ b/manuscript/Supplementary-Table-3.xlsx
@@ -3181,7 +3181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3343,158 +3343,174 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>V106A</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>1.757</v>
+          <t>G190E</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.512</v>
+        <v>1.767</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Y318F</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>11</v>
+          <t>V106A</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>9.6</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>1.41</v>
+        <v>1.757</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.445</v>
+        <v>0.512</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>K103N+M230L</t>
+          <t>Y318F</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>0.587</v>
+        <v>1.41</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.407</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>A98G+F227C</t>
+          <t>K103N+M230L</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-1.527</v>
+        <v>0.587</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.873</v>
+        <v>0.407</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>V106I+F227C</t>
+          <t>A98G+F227C</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>1.753</v>
+        <v>-1.527</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1.162</v>
+        <v>0.873</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>V106A+F227L</t>
+          <t>V106I+F227C</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>4.393</v>
+        <v>1.753</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1.003</v>
+        <v>1.162</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Y188L</t>
+          <t>V106A+F227L</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>4.52</v>
+        <v>4.393</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.486</v>
+        <v>1.003</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>V106A+P225H</t>
+          <t>Y188L</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>3.707</v>
+        <v>4.52</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1.126</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>V106A+L234I</t>
+          <t>V106A+P225H</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>3.723</v>
+        <v>3.707</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1.099</v>
+        <v>1.126</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>V106A+L234I</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>3.723</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>1.099</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>F227C</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr"/>
-      <c r="C19" s="7" t="n">
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="7" t="n">
         <v>-0.303</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D20" s="7" t="n">
         <v>0.8129999999999999</v>
       </c>
     </row>

--- a/manuscript/Supplementary-Table-3.xlsx
+++ b/manuscript/Supplementary-Table-3.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -475,11 +475,6 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -510,47 +505,22 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Total Energy SEM (kcal/mol)</t>
+          <t>van der Waals (kcal/mol)</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>van der Waals (kcal/mol)</t>
+          <t>Electrostatic (kcal/mol)</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>van der Waals SEM (kcal/mol)</t>
+          <t>GB polar solvation (kcal/mol)</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>Electrostatic (kcal/mol)</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Electrostatic SEM (kcal/mol)</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>GB polar solvation (kcal/mol)</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>GB polar solvation SEM (kcal/mol)</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
           <t>Nonpolar SA (kcal/mol)</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Nonpolar SA SEM (kcal/mol)</t>
         </is>
       </c>
     </row>
@@ -571,31 +541,16 @@
         <v>-66.41186736104038</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.2501736311299715</v>
+        <v>-68.68663238187065</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-68.68663238187065</v>
+        <v>-7.005816458032588</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.2077076702296222</v>
+        <v>16.99900066419496</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-7.005816458032588</v>
-      </c>
-      <c r="J2" s="6" t="n">
-        <v>0.1475013522280399</v>
-      </c>
-      <c r="K2" s="6" t="n">
-        <v>16.99900066419496</v>
-      </c>
-      <c r="L2" s="6" t="n">
-        <v>0.1648717757154271</v>
-      </c>
-      <c r="M2" s="6" t="n">
         <v>-7.718419185332086</v>
-      </c>
-      <c r="N2" s="6" t="n">
-        <v>0.0051185480668549</v>
       </c>
     </row>
     <row r="3">
@@ -615,31 +570,16 @@
         <v>-61.49999328430591</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.5577992883046078</v>
+        <v>-64.83560997899107</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-64.83560997899107</v>
+        <v>-6.253771707739446</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.4637622321645526</v>
+        <v>17.27782494707272</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-6.253771707739446</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>0.2602831917262053</v>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>17.27782494707272</v>
-      </c>
-      <c r="L3" s="6" t="n">
-        <v>0.253716764465854</v>
-      </c>
-      <c r="M3" s="6" t="n">
         <v>-7.688436544648092</v>
-      </c>
-      <c r="N3" s="6" t="n">
-        <v>0.0142491862222135</v>
       </c>
     </row>
     <row r="4">
@@ -659,31 +599,16 @@
         <v>-66.16427425033113</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.2690594686436728</v>
+        <v>-68.25282248562766</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-68.25282248562766</v>
+        <v>-9.040890960916244</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.2655127542298742</v>
+        <v>18.85339425125268</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-9.040890960916244</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>0.3519392587818529</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>18.85339425125268</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>0.3520366099789214</v>
-      </c>
-      <c r="M4" s="6" t="n">
         <v>-7.723955055039881</v>
-      </c>
-      <c r="N4" s="6" t="n">
-        <v>0.0117051808491836</v>
       </c>
     </row>
     <row r="5">
@@ -705,31 +630,16 @@
         <v>-60.40815400796441</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.3675132598876143</v>
+        <v>-63.44334564664064</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-63.44334564664064</v>
+        <v>-7.351850007577332</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.2720708364268121</v>
+        <v>18.07155203408994</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-7.351850007577332</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>0.2904084744939325</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>18.07155203408994</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>0.2543843332719268</v>
-      </c>
-      <c r="M5" s="6" t="n">
         <v>-7.684510387836405</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>0.0197100221250747</v>
       </c>
     </row>
     <row r="6">
@@ -751,31 +661,16 @@
         <v>-61.76776035313105</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.6026111764411346</v>
+        <v>-65.41322837904237</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-65.41322837904237</v>
+        <v>-6.539088162909104</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.5212273477722329</v>
+        <v>17.84675677465435</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-6.539088162909104</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>0.2901088856898565</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>17.84675677465435</v>
-      </c>
-      <c r="L6" s="6" t="n">
-        <v>0.2525207773521938</v>
-      </c>
-      <c r="M6" s="6" t="n">
         <v>-7.662200585833927</v>
-      </c>
-      <c r="N6" s="6" t="n">
-        <v>0.0257697876940597</v>
       </c>
     </row>
     <row r="7">
@@ -797,31 +692,16 @@
         <v>-64.58400657916043</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.3065499332336658</v>
+        <v>-67.66918259663913</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-67.66918259663913</v>
+        <v>-7.180154835992631</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.2942678344050362</v>
+        <v>18.12584778546831</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-7.180154835992631</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>0.2767019201169717</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>18.12584778546831</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>0.2255957294546892</v>
-      </c>
-      <c r="M7" s="6" t="n">
         <v>-7.860516931996973</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>0.0167014602982324</v>
       </c>
     </row>
     <row r="8">
@@ -843,31 +723,16 @@
         <v>-64.45114051904513</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.369271113023214</v>
+        <v>-67.45540251103827</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-67.45540251103827</v>
+        <v>-10.27039954078637</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.3361041374425011</v>
+        <v>21.00861719871798</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-10.27039954078637</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>0.5746244901093264</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>21.00861719871798</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>0.4859741514051435</v>
-      </c>
-      <c r="M8" s="6" t="n">
         <v>-7.733955665938485</v>
-      </c>
-      <c r="N8" s="6" t="n">
-        <v>0.0160021364820533</v>
       </c>
     </row>
     <row r="9">
@@ -889,31 +754,16 @@
         <v>-65.25044366774296</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.4202866025323145</v>
+        <v>-67.648259263501</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-67.648259263501</v>
+        <v>-9.480856196237664</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.340433370340627</v>
+        <v>19.65072045590636</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-9.480856196237664</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>0.2395901066843916</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>19.65072045590636</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>0.1475442378434241</v>
-      </c>
-      <c r="M9" s="6" t="n">
         <v>-7.772048663910671</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>0.0154429083000143</v>
       </c>
     </row>
     <row r="10">
@@ -935,31 +785,16 @@
         <v>-65.792661442929</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.262901391344</v>
+        <v>-68.60718573345586</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-68.60718573345586</v>
+        <v>-9.361331040638747</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2568610975673325</v>
+        <v>19.9526052857904</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-9.361331040638747</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>0.3863851394155409</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>19.9526052857904</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>0.3663277485365367</v>
-      </c>
-      <c r="M10" s="6" t="n">
         <v>-7.776749954624795</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>0.013272825799688</v>
       </c>
     </row>
     <row r="11">
@@ -981,31 +816,16 @@
         <v>-62.95778207084517</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.5640860237385258</v>
+        <v>-66.36487946428976</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-66.36487946428976</v>
+        <v>-7.813498958324842</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.4681451323629643</v>
+        <v>18.96053080804945</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-7.813498958324842</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>0.3164950650026531</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>18.96053080804945</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>0.3503864745002161</v>
-      </c>
-      <c r="M11" s="6" t="n">
         <v>-7.739934456280039</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>0.0139729832749934</v>
       </c>
     </row>
     <row r="12">
@@ -1027,31 +847,16 @@
         <v>-63.72598756336726</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.5904646116069365</v>
+        <v>-67.01210475757534</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-67.01210475757534</v>
+        <v>-8.786756058091623</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.4945763936133265</v>
+        <v>19.74771164115482</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-8.786756058091623</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>0.3451653565119702</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>19.74771164115482</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>0.2723659557420447</v>
-      </c>
-      <c r="M12" s="6" t="n">
         <v>-7.674838388855098</v>
-      </c>
-      <c r="N12" s="6" t="n">
-        <v>0.0167167779755452</v>
       </c>
     </row>
     <row r="13">
@@ -1073,31 +878,16 @@
         <v>-61.96079965810659</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.4977093949227552</v>
+        <v>-65.35201240881888</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-65.35201240881888</v>
+        <v>-8.034026906184669</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.4910313264317263</v>
+        <v>19.08418270643537</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-8.034026906184669</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>0.3109183632837264</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>19.08418270643537</v>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>0.3048273547151532</v>
-      </c>
-      <c r="M13" s="6" t="n">
         <v>-7.658943049538432</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>0.0142281431815664</v>
       </c>
     </row>
     <row r="14">
@@ -1119,31 +909,16 @@
         <v>-62.4624803430334</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.3944644163474043</v>
+        <v>-66.05485797771564</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-66.05485797771564</v>
+        <v>-7.641005064456341</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.2979389634206008</v>
+        <v>18.92588275340502</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-7.641005064456341</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>0.3316824232993127</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>18.92588275340502</v>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>0.3259496943822239</v>
-      </c>
-      <c r="M14" s="6" t="n">
         <v>-7.692500054266439</v>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>0.0132358671868691</v>
       </c>
     </row>
     <row r="15">
@@ -1165,31 +940,16 @@
         <v>-62.61053655090234</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.3045442882834627</v>
+        <v>-65.70152832786376</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-65.70152832786376</v>
+        <v>-6.272605387229088</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.3191815595701992</v>
+        <v>17.07663618127885</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-6.272605387229088</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>0.1652920981530136</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>17.07663618127885</v>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>0.1497079500495073</v>
-      </c>
-      <c r="M15" s="6" t="n">
         <v>-7.713039017088327</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>0.0103840075127636</v>
       </c>
     </row>
     <row r="16">
@@ -1211,31 +971,16 @@
         <v>-63.80051328473958</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.3414909697377296</v>
+        <v>-66.75195903615305</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-66.75195903615305</v>
+        <v>-6.614831913019093</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.3145790838471175</v>
+        <v>17.34024083409209</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-6.614831913019093</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>0.2485599941772361</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>17.34024083409209</v>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>0.2065387030897631</v>
-      </c>
-      <c r="M16" s="6" t="n">
         <v>-7.773963169659528</v>
-      </c>
-      <c r="N16" s="6" t="n">
-        <v>0.007963687964430199</v>
       </c>
     </row>
     <row r="17">
@@ -1257,31 +1002,16 @@
         <v>-60.75560140632334</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.4846263357154521</v>
+        <v>-64.55375301375172</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-64.55375301375172</v>
+        <v>-7.134752521162296</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.4060010564802302</v>
+        <v>18.51566977528267</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-7.134752521162296</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>0.2873169018829133</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>18.51566977528267</v>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>0.2382273797753166</v>
-      </c>
-      <c r="M17" s="6" t="n">
         <v>-7.582765646691988</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>0.0155648753739879</v>
       </c>
     </row>
     <row r="18">
@@ -1303,31 +1033,16 @@
         <v>-61.9343561463299</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.5265035578328614</v>
+        <v>-65.0136774373922</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-65.0136774373922</v>
+        <v>-9.048143798403812</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.3920486723362195</v>
+        <v>19.90167866701378</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-9.048143798403812</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>0.3969239806692735</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>19.90167866701378</v>
-      </c>
-      <c r="L18" s="6" t="n">
-        <v>0.3130554862382755</v>
-      </c>
-      <c r="M18" s="6" t="n">
         <v>-7.774213577547675</v>
-      </c>
-      <c r="N18" s="6" t="n">
-        <v>0.0181751882075332</v>
       </c>
     </row>
     <row r="19">
@@ -1349,31 +1064,16 @@
         <v>-61.64330800475344</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.3330149569106333</v>
+        <v>-65.19674052305882</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-65.19674052305882</v>
+        <v>-6.359447409131056</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.2907398659540229</v>
+        <v>17.57099227285294</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-6.359447409131056</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>0.4228065412369481</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>17.57099227285294</v>
-      </c>
-      <c r="L19" s="6" t="n">
-        <v>0.3025939179809981</v>
-      </c>
-      <c r="M19" s="6" t="n">
         <v>-7.658112345416504</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>0.0131936483160985</v>
       </c>
     </row>
     <row r="20">
@@ -1395,31 +1095,16 @@
         <v>-59.76489069548006</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.4842878060128098</v>
+        <v>-64.82381835438861</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-64.82381835438861</v>
+        <v>-5.433080729931698</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.488482957487839</v>
+        <v>18.06768409152788</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-5.433080729931698</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>0.3719845412907313</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>18.06768409152788</v>
-      </c>
-      <c r="L20" s="6" t="n">
-        <v>0.229834250118799</v>
-      </c>
-      <c r="M20" s="6" t="n">
         <v>-7.57567570268766</v>
-      </c>
-      <c r="N20" s="6" t="n">
-        <v>0.0134339645038495</v>
       </c>
     </row>
     <row r="21">
@@ -1441,31 +1126,16 @@
         <v>-63.94669710583119</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.2617318695906275</v>
+        <v>-67.39882823002668</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-67.39882823002668</v>
+        <v>-7.017787213456882</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2472724887856621</v>
+        <v>18.19134661162104</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-7.017787213456882</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>0.1540922369668712</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>18.19134661162104</v>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>0.1299097065353233</v>
-      </c>
-      <c r="M21" s="6" t="n">
         <v>-7.721428273968668</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>0.0135172739129965</v>
       </c>
     </row>
     <row r="22">
@@ -1487,31 +1157,16 @@
         <v>-60.13946200749179</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.3264354956895269</v>
+        <v>-64.30238051167346</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-64.30238051167346</v>
+        <v>-5.391323535092177</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.3529223917278021</v>
+        <v>17.31593590621511</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-5.391323535092177</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0.2386079197485046</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>17.31593590621511</v>
-      </c>
-      <c r="L22" s="6" t="n">
-        <v>0.2224583799921943</v>
-      </c>
-      <c r="M22" s="6" t="n">
         <v>-7.761693866941259</v>
-      </c>
-      <c r="N22" s="6" t="n">
-        <v>0.0148885642145274</v>
       </c>
     </row>
     <row r="23">
@@ -1533,31 +1188,16 @@
         <v>-64.27584209331889</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.2467767977344025</v>
+        <v>-66.76002895873832</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-66.76002895873832</v>
+        <v>-11.23395150476626</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.2087996723106582</v>
+        <v>21.52100630517672</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-11.23395150476626</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>0.2636836414073727</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>21.52100630517672</v>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0.1729996645358444</v>
-      </c>
-      <c r="M23" s="6" t="n">
         <v>-7.802867934991022</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>0.0119577471159902</v>
       </c>
     </row>
     <row r="24">
@@ -1579,31 +1219,16 @@
         <v>-67.09708682146669</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.2311825015556177</v>
+        <v>-68.85254065622728</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-68.85254065622728</v>
+        <v>-11.02698025584098</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.1868165318261761</v>
+        <v>20.55442310428072</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-11.02698025584098</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0.1502416006718126</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>20.55442310428072</v>
-      </c>
-      <c r="L24" s="6" t="n">
-        <v>0.1491215608133562</v>
-      </c>
-      <c r="M24" s="6" t="n">
         <v>-7.771989013679168</v>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>0.007682969009058</v>
       </c>
     </row>
     <row r="25">
@@ -1625,31 +1250,16 @@
         <v>-65.6315586982531</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.2926847045201603</v>
+        <v>-69.20409704793151</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-69.20409704793151</v>
+        <v>-8.381723528574087</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.3232548168368995</v>
+        <v>19.7261222689831</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-8.381723528574087</v>
-      </c>
-      <c r="J25" s="6" t="n">
-        <v>0.330363421736956</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>19.7261222689831</v>
-      </c>
-      <c r="L25" s="6" t="n">
-        <v>0.2483093643463391</v>
-      </c>
-      <c r="M25" s="6" t="n">
         <v>-7.771860390730615</v>
-      </c>
-      <c r="N25" s="6" t="n">
-        <v>0.0109815500424103</v>
       </c>
     </row>
     <row r="26">
@@ -1671,31 +1281,16 @@
         <v>-62.28110152311058</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.5023491199432191</v>
+        <v>-65.49890916272631</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-65.49890916272631</v>
+        <v>-8.617056242832012</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.4450739021315487</v>
+        <v>19.54350289149676</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-8.617056242832012</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <v>0.3027305279478962</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>19.54350289149676</v>
-      </c>
-      <c r="L26" s="6" t="n">
-        <v>0.2284132531593597</v>
-      </c>
-      <c r="M26" s="6" t="n">
         <v>-7.708639009049016</v>
-      </c>
-      <c r="N26" s="6" t="n">
-        <v>0.0184210013039476</v>
       </c>
     </row>
     <row r="27">
@@ -1717,31 +1312,16 @@
         <v>-65.28186510769953</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.3641023806052068</v>
+        <v>-68.2650433521606</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-68.2650433521606</v>
+        <v>-10.51925011851476</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.3746729985082482</v>
+        <v>21.29935456963387</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-10.51925011851476</v>
-      </c>
-      <c r="J27" s="6" t="n">
-        <v>0.374469531778074</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>21.29935456963387</v>
-      </c>
-      <c r="L27" s="6" t="n">
-        <v>0.3724703428851262</v>
-      </c>
-      <c r="M27" s="6" t="n">
         <v>-7.796926206658036</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>0.0137691631748621</v>
       </c>
     </row>
     <row r="28">
@@ -1763,31 +1343,16 @@
         <v>-63.66131155480423</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.240363558018953</v>
+        <v>-67.7657268224678</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-67.7657268224678</v>
+        <v>-6.453373468158327</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.1630663572080876</v>
+        <v>18.36398400038652</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-6.453373468158327</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>0.2625115653283921</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>18.36398400038652</v>
-      </c>
-      <c r="L28" s="6" t="n">
-        <v>0.1679806306267879</v>
-      </c>
-      <c r="M28" s="6" t="n">
         <v>-7.806195264564645</v>
-      </c>
-      <c r="N28" s="6" t="n">
-        <v>0.008643608723759201</v>
       </c>
     </row>
     <row r="29">
@@ -1809,31 +1374,16 @@
         <v>-57.38008470734459</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.8264437497973969</v>
+        <v>-62.72151398173793</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-62.72151398173793</v>
+        <v>-6.392180482656252</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.7130296553495895</v>
+        <v>19.52829046413502</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-6.392180482656252</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>0.4096025249826887</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>19.52829046413502</v>
-      </c>
-      <c r="L29" s="6" t="n">
-        <v>0.3544315792152682</v>
-      </c>
-      <c r="M29" s="6" t="n">
         <v>-7.794680707085429</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>0.0298800998408776</v>
       </c>
     </row>
     <row r="30">
@@ -1855,31 +1405,16 @@
         <v>-55.53307693845253</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0.6225255017582174</v>
+        <v>-59.54655137765724</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-59.54655137765724</v>
+        <v>-7.127701082514587</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.5649312302458522</v>
+        <v>18.75110898829327</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-7.127701082514587</v>
-      </c>
-      <c r="J30" s="6" t="n">
-        <v>0.3402118939855104</v>
-      </c>
-      <c r="K30" s="6" t="n">
-        <v>18.75110898829327</v>
-      </c>
-      <c r="L30" s="6" t="n">
-        <v>0.3283946465399486</v>
-      </c>
-      <c r="M30" s="6" t="n">
         <v>-7.609933466573974</v>
-      </c>
-      <c r="N30" s="6" t="n">
-        <v>0.0232818252428724</v>
       </c>
     </row>
     <row r="31">
@@ -1901,31 +1436,16 @@
         <v>-63.93414284051009</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.3704406976280771</v>
+        <v>-67.48864896870118</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-67.48864896870118</v>
+        <v>-9.25581805838562</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.422234358645035</v>
+        <v>20.60836943340119</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-9.25581805838562</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>0.3799099749529664</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>20.60836943340119</v>
-      </c>
-      <c r="L31" s="6" t="n">
-        <v>0.3131458364589387</v>
-      </c>
-      <c r="M31" s="6" t="n">
         <v>-7.798045246824479</v>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v>0.013313726903497</v>
       </c>
     </row>
     <row r="32">
@@ -1947,31 +1467,16 @@
         <v>-61.22991977330631</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.4011178834272818</v>
+        <v>-64.26225314436225</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-64.26225314436225</v>
+        <v>-8.857603995116015</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.4072735119102237</v>
+        <v>19.53291979620151</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-8.857603995116015</v>
-      </c>
-      <c r="J32" s="6" t="n">
-        <v>0.2978652788625612</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>19.53291979620151</v>
-      </c>
-      <c r="L32" s="6" t="n">
-        <v>0.2794505672944661</v>
-      </c>
-      <c r="M32" s="6" t="n">
         <v>-7.642982430029553</v>
-      </c>
-      <c r="N32" s="6" t="n">
-        <v>0.0141518266537451</v>
       </c>
     </row>
     <row r="33">
@@ -1993,31 +1498,16 @@
         <v>-62.27982366724785</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.3544993790518945</v>
+        <v>-66.09613947758405</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-66.09613947758405</v>
+        <v>-7.658326934147537</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.4503467867350433</v>
+        <v>19.1504311151304</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-7.658326934147537</v>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>0.282079357664591</v>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>19.1504311151304</v>
-      </c>
-      <c r="L33" s="6" t="n">
-        <v>0.1570788775575243</v>
-      </c>
-      <c r="M33" s="6" t="n">
         <v>-7.675788370646664</v>
-      </c>
-      <c r="N33" s="6" t="n">
-        <v>0.0142927401609042</v>
       </c>
     </row>
     <row r="34">
@@ -2039,31 +1529,16 @@
         <v>-62.1962470841568</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.4600720893340544</v>
+        <v>-65.6497284173828</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-65.6497284173828</v>
+        <v>-8.129586442686289</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.4670373809807657</v>
+        <v>19.22535403964624</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-8.129586442686289</v>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v>0.3089446322690917</v>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v>19.22535403964624</v>
-      </c>
-      <c r="L34" s="6" t="n">
-        <v>0.2635730391001749</v>
-      </c>
-      <c r="M34" s="6" t="n">
         <v>-7.64228626373393</v>
-      </c>
-      <c r="N34" s="6" t="n">
-        <v>0.0125082001300856</v>
       </c>
     </row>
     <row r="35">
@@ -2085,31 +1560,16 @@
         <v>-64.44003183381932</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.3909243224104524</v>
+        <v>-66.48651887073969</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-66.48651887073969</v>
+        <v>-8.528535327745253</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.3675625639893592</v>
+        <v>18.38335480334426</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-8.528535327745253</v>
-      </c>
-      <c r="J35" s="6" t="n">
-        <v>0.2921894490955456</v>
-      </c>
-      <c r="K35" s="6" t="n">
-        <v>18.38335480334426</v>
-      </c>
-      <c r="L35" s="6" t="n">
-        <v>0.323917326043437</v>
-      </c>
-      <c r="M35" s="6" t="n">
         <v>-7.808332438678631</v>
-      </c>
-      <c r="N35" s="6" t="n">
-        <v>0.0227890214953635</v>
       </c>
     </row>
     <row r="36">
@@ -2131,31 +1591,16 @@
         <v>-61.40734173417953</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.6426635953926475</v>
+        <v>-64.53652688583327</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-64.53652688583327</v>
+        <v>-8.700640827692087</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.5401077954076715</v>
+        <v>19.6601162904991</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-8.700640827692087</v>
-      </c>
-      <c r="J36" s="6" t="n">
-        <v>0.4287224028726124</v>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>19.6601162904991</v>
-      </c>
-      <c r="L36" s="6" t="n">
-        <v>0.4244024469769036</v>
-      </c>
-      <c r="M36" s="6" t="n">
         <v>-7.830290311153258</v>
-      </c>
-      <c r="N36" s="6" t="n">
-        <v>0.0298785433478462</v>
       </c>
     </row>
     <row r="37">
@@ -2177,31 +1622,16 @@
         <v>-59.84600296582544</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.4915718705559426</v>
+        <v>-63.36437103676406</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-63.36437103676406</v>
+        <v>-6.305163035204239</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.4254379884456531</v>
+        <v>17.52642573179752</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-6.305163035204239</v>
-      </c>
-      <c r="J37" s="6" t="n">
-        <v>0.314704590309062</v>
-      </c>
-      <c r="K37" s="6" t="n">
-        <v>17.52642573179752</v>
-      </c>
-      <c r="L37" s="6" t="n">
-        <v>0.285344397884309</v>
-      </c>
-      <c r="M37" s="6" t="n">
         <v>-7.702894625654641</v>
-      </c>
-      <c r="N37" s="6" t="n">
-        <v>0.0170957428259763</v>
       </c>
     </row>
     <row r="38">
@@ -2223,31 +1653,16 @@
         <v>-66.30504766559341</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.4010503834471617</v>
+        <v>-68.38616329170409</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-68.38616329170409</v>
+        <v>-11.37902648945127</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.4202331275203383</v>
+        <v>21.28379540963109</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-11.37902648945127</v>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v>0.2048171972922946</v>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>21.28379540963109</v>
-      </c>
-      <c r="L38" s="6" t="n">
-        <v>0.202780851474425</v>
-      </c>
-      <c r="M38" s="6" t="n">
         <v>-7.823653294069134</v>
-      </c>
-      <c r="N38" s="6" t="n">
-        <v>0.011928108990112</v>
       </c>
     </row>
     <row r="39">
@@ -2269,31 +1684,16 @@
         <v>-63.43280365428983</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.3976095272968037</v>
+        <v>-65.80800289795776</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-65.80800289795776</v>
+        <v>-8.913692429192212</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.3918575434130489</v>
+        <v>19.02037118178708</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-8.913692429192212</v>
-      </c>
-      <c r="J39" s="6" t="n">
-        <v>0.4541330702240242</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>19.02037118178708</v>
-      </c>
-      <c r="L39" s="6" t="n">
-        <v>0.3936284193403915</v>
-      </c>
-      <c r="M39" s="6" t="n">
         <v>-7.731479508926945</v>
-      </c>
-      <c r="N39" s="6" t="n">
-        <v>0.0183738693297608</v>
       </c>
     </row>
     <row r="40">
@@ -2315,31 +1715,16 @@
         <v>-67.73235479061719</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.2486875849210532</v>
+        <v>-69.6635012781677</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-69.6635012781677</v>
+        <v>-10.7515047550576</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0.2477903506951057</v>
+        <v>20.44037783351045</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-10.7515047550576</v>
-      </c>
-      <c r="J40" s="6" t="n">
-        <v>0.1717692603603414</v>
-      </c>
-      <c r="K40" s="6" t="n">
-        <v>20.44037783351045</v>
-      </c>
-      <c r="L40" s="6" t="n">
-        <v>0.179868920351618</v>
-      </c>
-      <c r="M40" s="6" t="n">
         <v>-7.757726590902353</v>
-      </c>
-      <c r="N40" s="6" t="n">
-        <v>0.010188158031236</v>
       </c>
     </row>
     <row r="41">
@@ -2361,31 +1746,16 @@
         <v>-61.90023933641923</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.3354640570202644</v>
+        <v>-64.80987174198351</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-64.80987174198351</v>
+        <v>-7.994813228953026</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.3120208451047603</v>
+        <v>18.58446365560674</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-7.994813228953026</v>
-      </c>
-      <c r="J41" s="6" t="n">
-        <v>0.3702243430190786</v>
-      </c>
-      <c r="K41" s="6" t="n">
-        <v>18.58446365560674</v>
-      </c>
-      <c r="L41" s="6" t="n">
-        <v>0.2935505826460415</v>
-      </c>
-      <c r="M41" s="6" t="n">
         <v>-7.680018021089396</v>
-      </c>
-      <c r="N41" s="6" t="n">
-        <v>0.0109208392381533</v>
       </c>
     </row>
     <row r="42">
@@ -2407,31 +1777,16 @@
         <v>-66.2657577285962</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0.6763575249971697</v>
+        <v>-69.49180190846108</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-69.49180190846108</v>
+        <v>-7.812051980914379</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.5814740515947311</v>
+        <v>18.75753585056867</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-7.812051980914379</v>
-      </c>
-      <c r="J42" s="6" t="n">
-        <v>0.3806725826593526</v>
-      </c>
-      <c r="K42" s="6" t="n">
-        <v>18.75753585056867</v>
-      </c>
-      <c r="L42" s="6" t="n">
-        <v>0.2435758213758726</v>
-      </c>
-      <c r="M42" s="6" t="n">
         <v>-7.719439689789401</v>
-      </c>
-      <c r="N42" s="6" t="n">
-        <v>0.0173012054563359</v>
       </c>
     </row>
     <row r="43">
@@ -2453,31 +1808,16 @@
         <v>-62.63181740762563</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.5344550787173911</v>
+        <v>-65.41136114401274</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-65.41136114401274</v>
+        <v>-7.962329169613958</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.4767882929363601</v>
+        <v>18.42533484471688</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-7.962329169613958</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>0.2911505772625051</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>18.42533484471688</v>
-      </c>
-      <c r="L43" s="6" t="n">
-        <v>0.2665076068197298</v>
-      </c>
-      <c r="M43" s="6" t="n">
         <v>-7.6834619387158</v>
-      </c>
-      <c r="N43" s="6" t="n">
-        <v>0.0152927948336822</v>
       </c>
     </row>
     <row r="44">
@@ -2499,31 +1839,16 @@
         <v>-62.94888087946065</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.2679627463821973</v>
+        <v>-65.62317624511584</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-65.62317624511584</v>
+        <v>-7.20673199916682</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>0.2761726998573366</v>
+        <v>17.57069035196395</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-7.20673199916682</v>
-      </c>
-      <c r="J44" s="6" t="n">
-        <v>0.2450170518633391</v>
-      </c>
-      <c r="K44" s="6" t="n">
-        <v>17.57069035196395</v>
-      </c>
-      <c r="L44" s="6" t="n">
-        <v>0.2411221766266958</v>
-      </c>
-      <c r="M44" s="6" t="n">
         <v>-7.689662987141945</v>
-      </c>
-      <c r="N44" s="6" t="n">
-        <v>0.0138274527590365</v>
       </c>
     </row>
     <row r="45">
@@ -2545,31 +1870,16 @@
         <v>-61.40438469545907</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0.6709988652096974</v>
+        <v>-65.2733120128117</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-65.2733120128117</v>
+        <v>-7.409375493491372</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0.5228493405098865</v>
+        <v>18.96220639376521</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-7.409375493491372</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>0.320623605048383</v>
-      </c>
-      <c r="K45" s="6" t="n">
-        <v>18.96220639376521</v>
-      </c>
-      <c r="L45" s="6" t="n">
-        <v>0.3015101349592198</v>
-      </c>
-      <c r="M45" s="6" t="n">
         <v>-7.683903582921219</v>
-      </c>
-      <c r="N45" s="6" t="n">
-        <v>0.0174560922186853</v>
       </c>
     </row>
     <row r="46">
@@ -2591,31 +1901,16 @@
         <v>-63.19230418506081</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.2472260497116094</v>
+        <v>-66.20473053403269</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-66.20473053403269</v>
+        <v>-7.076692341409451</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.2361754163382634</v>
+        <v>17.82094716569889</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-7.076692341409451</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>0.3031348803388227</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>17.82094716569889</v>
-      </c>
-      <c r="L46" s="6" t="n">
-        <v>0.3101249906821607</v>
-      </c>
-      <c r="M46" s="6" t="n">
         <v>-7.731828475317581</v>
-      </c>
-      <c r="N46" s="6" t="n">
-        <v>0.0163753580637401</v>
       </c>
     </row>
     <row r="47">
@@ -2637,31 +1932,16 @@
         <v>-63.35721956917848</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.25180398932215</v>
+        <v>-67.67987633666645</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-67.67987633666645</v>
+        <v>-6.095138710100167</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0.2870561349935407</v>
+        <v>18.1542399736481</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-6.095138710100167</v>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>0.2863554698553281</v>
-      </c>
-      <c r="K47" s="6" t="n">
-        <v>18.1542399736481</v>
-      </c>
-      <c r="L47" s="6" t="n">
-        <v>0.2682349799451302</v>
-      </c>
-      <c r="M47" s="6" t="n">
         <v>-7.736444496059964</v>
-      </c>
-      <c r="N47" s="6" t="n">
-        <v>0.0075265003792922</v>
       </c>
     </row>
     <row r="48">
@@ -2683,31 +1963,16 @@
         <v>-59.55520977055865</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.274503990108459</v>
+        <v>-64.0270493709659</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-64.0270493709659</v>
+        <v>-6.150344192954273</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0.3283493015290168</v>
+        <v>18.26673082822139</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-6.150344192954273</v>
-      </c>
-      <c r="J48" s="6" t="n">
-        <v>0.337377299593615</v>
-      </c>
-      <c r="K48" s="6" t="n">
-        <v>18.26673082822139</v>
-      </c>
-      <c r="L48" s="6" t="n">
-        <v>0.2352665867629829</v>
-      </c>
-      <c r="M48" s="6" t="n">
         <v>-7.644547034859885</v>
-      </c>
-      <c r="N48" s="6" t="n">
-        <v>0.0077348458151149</v>
       </c>
     </row>
     <row r="49">
@@ -2729,31 +1994,16 @@
         <v>-63.72570167745989</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.329180548744189</v>
+        <v>-68.2600395098287</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-68.2600395098287</v>
+        <v>-7.34224626990441</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>0.3943037313056645</v>
+        <v>19.60760512269934</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-7.34224626990441</v>
-      </c>
-      <c r="J49" s="6" t="n">
-        <v>0.3073126211837542</v>
-      </c>
-      <c r="K49" s="6" t="n">
-        <v>19.60760512269934</v>
-      </c>
-      <c r="L49" s="6" t="n">
-        <v>0.3323197244453233</v>
-      </c>
-      <c r="M49" s="6" t="n">
         <v>-7.73102102042612</v>
-      </c>
-      <c r="N49" s="6" t="n">
-        <v>0.0141174918717571</v>
       </c>
     </row>
     <row r="50">
@@ -2775,31 +2025,16 @@
         <v>-55.45246827565062</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1.291166250041184</v>
+        <v>-60.55706626460938</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-60.55706626460938</v>
+        <v>-5.766204048843763</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>1.104913672349412</v>
+        <v>18.55162776451038</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-5.766204048843763</v>
-      </c>
-      <c r="J50" s="6" t="n">
-        <v>0.4392104564361799</v>
-      </c>
-      <c r="K50" s="6" t="n">
-        <v>18.55162776451038</v>
-      </c>
-      <c r="L50" s="6" t="n">
-        <v>0.2976747204738641</v>
-      </c>
-      <c r="M50" s="6" t="n">
         <v>-7.680825726707853</v>
-      </c>
-      <c r="N50" s="6" t="n">
-        <v>0.0246730436309743</v>
       </c>
     </row>
     <row r="51">
@@ -2821,31 +2056,16 @@
         <v>-60.8872567611179</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.323708207500287</v>
+        <v>-64.69616904534712</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-64.69616904534712</v>
+        <v>-6.247226210273294</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>0.2843281944362268</v>
+        <v>17.85157328581947</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-6.247226210273294</v>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>0.3980698180496459</v>
-      </c>
-      <c r="K51" s="6" t="n">
-        <v>17.85157328581947</v>
-      </c>
-      <c r="L51" s="6" t="n">
-        <v>0.321058212552932</v>
-      </c>
-      <c r="M51" s="6" t="n">
         <v>-7.795434791316948</v>
-      </c>
-      <c r="N51" s="6" t="n">
-        <v>0.0160234008558855</v>
       </c>
     </row>
     <row r="52">
@@ -2867,31 +2087,16 @@
         <v>-62.7668789994903</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.4336779983467582</v>
+        <v>-64.73279836068136</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-64.73279836068136</v>
+        <v>-7.981150633842973</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0.3551412693924899</v>
+        <v>17.71071732158186</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-7.981150633842973</v>
-      </c>
-      <c r="J52" s="6" t="n">
-        <v>0.1922342552823163</v>
-      </c>
-      <c r="K52" s="6" t="n">
-        <v>17.71071732158186</v>
-      </c>
-      <c r="L52" s="6" t="n">
-        <v>0.218119434551866</v>
-      </c>
-      <c r="M52" s="6" t="n">
         <v>-7.76364732654783</v>
-      </c>
-      <c r="N52" s="6" t="n">
-        <v>0.0121826808258197</v>
       </c>
     </row>
     <row r="53">
@@ -2913,31 +2118,16 @@
         <v>-62.16006825689269</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>0.3018707701534328</v>
+        <v>-66.85539957943936</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-66.85539957943936</v>
+        <v>-4.879801745837087</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>0.2978967633356237</v>
+        <v>17.26802083775828</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-4.879801745837087</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>0.2125517332246305</v>
-      </c>
-      <c r="K53" s="6" t="n">
-        <v>17.26802083775828</v>
-      </c>
-      <c r="L53" s="6" t="n">
-        <v>0.1387305538404565</v>
-      </c>
-      <c r="M53" s="6" t="n">
         <v>-7.69288776937452</v>
-      </c>
-      <c r="N53" s="6" t="n">
-        <v>0.0185606665983285</v>
       </c>
     </row>
     <row r="54">
@@ -2959,31 +2149,16 @@
         <v>-63.32545624788224</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0.2661506068529594</v>
+        <v>-67.96568699806456</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-67.96568699806456</v>
+        <v>-5.992840976913921</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0.3003555108220358</v>
+        <v>18.48468744048197</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-5.992840976913921</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>0.2596211555122859</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>18.48468744048197</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0.2269983540090486</v>
-      </c>
-      <c r="M54" s="6" t="n">
         <v>-7.851615713385733</v>
-      </c>
-      <c r="N54" s="6" t="n">
-        <v>0.0103476349936178</v>
       </c>
     </row>
     <row r="55">
@@ -3005,31 +2180,16 @@
         <v>-65.12076076262976</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.3271894589658367</v>
+        <v>-69.33634336106626</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-69.33634336106626</v>
+        <v>-10.03393573859443</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0.3368331109361758</v>
+        <v>21.96725545376254</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-10.03393573859443</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>0.4164755599673412</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>21.96725545376254</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>0.4161573396748931</v>
-      </c>
-      <c r="M55" s="6" t="n">
         <v>-7.717737116731603</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>0.0134989498156546</v>
       </c>
     </row>
     <row r="56">
@@ -3051,31 +2211,16 @@
         <v>-64.6850967772248</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.3353512921010612</v>
+        <v>-69.13721382001846</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-69.13721382001846</v>
+        <v>-6.378324080191335</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0.3404845126441378</v>
+        <v>18.60180220230131</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-6.378324080191335</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>0.3010036281599519</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>18.60180220230131</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>0.294829127899382</v>
-      </c>
-      <c r="M56" s="6" t="n">
         <v>-7.771361079316294</v>
-      </c>
-      <c r="N56" s="6" t="n">
-        <v>0.0093003813986799</v>
       </c>
     </row>
     <row r="57">
@@ -3097,31 +2242,16 @@
         <v>-63.05652470329457</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>0.3382179511022948</v>
+        <v>-67.13420568172613</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-67.13420568172613</v>
+        <v>-7.336078162874113</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0.4369682726205002</v>
+        <v>19.19969582420918</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-7.336078162874113</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>0.2937789345886142</v>
-      </c>
-      <c r="K57" s="6" t="n">
-        <v>19.19969582420918</v>
-      </c>
-      <c r="L57" s="6" t="n">
-        <v>0.1892371223319822</v>
-      </c>
-      <c r="M57" s="6" t="n">
         <v>-7.785936682903515</v>
-      </c>
-      <c r="N57" s="6" t="n">
-        <v>0.0156461645234307</v>
       </c>
     </row>
     <row r="58">
@@ -3143,31 +2273,16 @@
         <v>-59.46617083640571</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0.3826314738374842</v>
+        <v>-63.43835733377851</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-63.43835733377851</v>
+        <v>-7.894189984677216</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>0.3775570145322826</v>
+        <v>19.64945588011586</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-7.894189984677216</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>0.2548322795017418</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>19.64945588011586</v>
-      </c>
-      <c r="L58" s="6" t="n">
-        <v>0.263614607900249</v>
-      </c>
-      <c r="M58" s="6" t="n">
         <v>-7.783079398065863</v>
-      </c>
-      <c r="N58" s="6" t="n">
-        <v>0.0163560871275674</v>
       </c>
     </row>
   </sheetData>
@@ -3181,13 +2296,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3198,17 +2315,27 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>DOR fold reduction</t>
+          <t>Alchemical leg</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>ddG bind (kcal/mol)</t>
+          <t>Replicate</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>ddG SEM (kcal/mol)</t>
+          <t>dG holo (kcal/mol)</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>dG apo (kcal/mol)</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Leg ddG bind (kcal/mol)</t>
         </is>
       </c>
     </row>
@@ -3218,300 +2345,1942 @@
           <t>V106I</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C2" s="7" t="n">
-        <v>2.27</v>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106I</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0.737</v>
+        <v>20.63</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>0.9100000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>K103N</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>0.54</v>
+          <t>V106I</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106I</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>0.227</v>
+        <v>21.94</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>3.440000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Y181C</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>-0.657</v>
+          <t>V106I</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106I</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>1.06</v>
+        <v>21.43</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>2.460000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>G190A</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>0.27</v>
+          <t>K103N</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_K103N</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0.168</v>
+        <v>-78.09</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>-78.18000000000001</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0.09000000000000341</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>V106M</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>6.097</v>
+          <t>K103N</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_K103N</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.162</v>
+        <v>-78.8</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>-79.62</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>0.8200000000000074</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>G190S</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>2.013</v>
+          <t>K103N</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_K103N</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.342</v>
+        <v>-77.09999999999999</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>-77.81</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0.710000000000008</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>L100I+K103N</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>0.193</v>
+          <t>Y181C</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_Y181C</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.681</v>
+        <v>14.95</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>-2.57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>K103N+P225H</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>1.757</v>
+          <t>Y181C</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_Y181C</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.788</v>
+        <v>18.16</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>1.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>G190E</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>18</v>
+          <t>Y181C</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_Y181C</t>
+        </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1.767</v>
+        <v>16.54</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>-0.490000000000002</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>V106A</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>1.757</v>
+          <t>G190A</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_G190A</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.512</v>
+        <v>7.46</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>0.3799999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Y318F</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>1.41</v>
+          <t>G190A</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_G190A</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.445</v>
+        <v>7.36</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0.4900000000000002</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>K103N+M230L</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>0.587</v>
+          <t>G190A</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_G190A</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.407</v>
+        <v>7.24</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>-0.05999999999999961</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>A98G+F227C</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>-1.527</v>
+          <t>V106M</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106M</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.873</v>
+        <v>22.09</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>5.93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>V106I+F227C</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>1.753</v>
+          <t>V106M</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106M</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1.162</v>
+        <v>20.78</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>5.940000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>V106A+F227L</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>4.393</v>
+          <t>V106M</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106M</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1.003</v>
+        <v>22.39</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>6.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Y188L</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>4.52</v>
+          <t>G190S</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_G190S</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.486</v>
+        <v>0.1</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>1.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>V106A+P225H</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>153</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>3.707</v>
+          <t>G190S</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_G190S</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1.126</v>
+        <v>6.54</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>2.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>V106A+L234I</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>3.723</v>
+          <t>G190S</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_G190S</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1.099</v>
+        <v>-0.5</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>L100I+K103N</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>K103N_to_L100I_K103N</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>-1.609999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>L100I+K103N</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>K103N_to_L100I_K103N</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>0.4800000000000004</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>L100I+K103N</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>K103N_to_L100I_K103N</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0.08999999999999986</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>L100I+K103N</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_K103N</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>-78.09</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>-78.18000000000001</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>0.09000000000000341</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>L100I+K103N</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_K103N</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>-78.8</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>-79.62</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0.8200000000000074</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>L100I+K103N</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_K103N</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>-77.09999999999999</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>-77.81</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>0.710000000000008</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>K103N+P225H</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>K103N_to_K103N_P225H</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>-40.17</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>-42.88</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>2.710000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>K103N+P225H</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>K103N_to_K103N_P225H</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>-42.1</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>-42.38</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>0.2800000000000011</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>K103N+P225H</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>K103N_to_K103N_P225H</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>-43.02</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>-43.68</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>0.6599999999999966</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>K103N+P225H</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_K103N</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>-78.09</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>-78.18000000000001</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>0.09000000000000341</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>K103N+P225H</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_K103N</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>-78.8</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>-79.62</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>0.8200000000000074</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>K103N+P225H</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_K103N</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>-77.09999999999999</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>-77.81</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>0.710000000000008</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>G190E</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_G190E</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>-60.32</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>-59.61</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>-0.7100000000000009</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>G190E</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_G190E</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>-49.65</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>-51.04</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>1.390000000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>G190E</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_G190E</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>-47.69</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>-53.01</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>V106A</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106A</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>V106A</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106A</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>2.609999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>V106A</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106A</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>0.8399999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Y318F</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_Y318F</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1.370000000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Y318F</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_Y318F</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>2.199999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Y318F</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_Y318F</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>0.6600000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>K103N+M230L</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>K103N_to_K103N_M230L</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>-18.55</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>0.5800000000000018</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>K103N+M230L</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>K103N_to_K103N_M230L</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>-12.39</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>-11.81</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>-0.5800000000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>K103N+M230L</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>K103N_to_K103N_M230L</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>-11.91</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>-12.05</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>0.1400000000000006</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>K103N+M230L</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_K103N</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>-78.09</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>-78.18000000000001</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>0.09000000000000341</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>K103N+M230L</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_K103N</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>-78.8</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>-79.62</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>0.8200000000000074</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>K103N+M230L</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_K103N</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>-77.09999999999999</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>-77.81</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>0.710000000000008</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>A98G+F227C</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>F227C_to_A98G_F227C</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>-8.49</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>-7.89</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>-0.6000000000000005</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>A98G+F227C</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>F227C_to_A98G_F227C</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>-9.43</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>A98G+F227C</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>F227C_to_A98G_F227C</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>-7.37</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>A98G+F227C</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_F227C</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>A98G+F227C</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_F227C</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>A98G+F227C</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_F227C</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>V106I+F227C</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>V106I_to_V106I_F227C</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>-2.98</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>V106I+F227C</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>V106I_to_V106I_F227C</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>V106I+F227C</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>V106I_to_V106I_F227C</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>V106I+F227C</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106I</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>0.9100000000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>V106I+F227C</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106I</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>3.440000000000001</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>V106I+F227C</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106I</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>2.460000000000001</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>V106A+F227L</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>V106A_to_V106A_F227L</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>-20.43</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>-22.79</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>2.359999999999999</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>V106A+F227L</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>V106A_to_V106A_F227L</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>-19.74</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>-21.04</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>1.300000000000001</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>V106A+F227L</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>V106A_to_V106A_F227L</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>-19.44</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>-23.69</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>V106A+F227L</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106A</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>V106A+F227L</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106A</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>2.609999999999999</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>V106A+F227L</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106A</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>0.8399999999999999</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Y188L</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_Y188L</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E65" s="7" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>5.42</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Y188L</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_Y188L</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>4.390000000000001</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Y188L</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_Y188L</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>V106A+P225H</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>V106A_to_V106A_P225H</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>-41.54</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>-43.38</v>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>1.840000000000003</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>V106A+P225H</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>V106A_to_V106A_P225H</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>-43.02</v>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>-43.29</v>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>0.269999999999996</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>V106A+P225H</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>V106A_to_V106A_P225H</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>-40.21</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>-43.95</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>3.740000000000002</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>V106A+P225H</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106A</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>V106A+P225H</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106A</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>2.609999999999999</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>V106A+P225H</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106A</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>0.8399999999999999</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>V106A+L234I</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>V106A_to_V106A_L234I</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>1.050000000000001</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>V106A+L234I</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>V106A_to_V106A_L234I</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>0.9399999999999977</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>V106A+L234I</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>V106A_to_V106A_L234I</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>V106A+L234I</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106A</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>V106A+L234I</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106A</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="F78" s="7" t="n">
+        <v>2.609999999999999</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>V106A+L234I</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_V106A</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="F79" s="7" t="n">
+        <v>0.8399999999999999</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
           <t>F227C</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr"/>
-      <c r="C20" s="7" t="n">
-        <v>-0.303</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>0.8129999999999999</v>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_F227C</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>F227C</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_F227C</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>F227C</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>wt_to_F227C</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F82" s="7" t="n">
+        <v>-1.93</v>
       </c>
     </row>
   </sheetData>
@@ -3525,7 +4294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3583,24 +4352,36 @@
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Two kinds of SEM</t>
+          <t>Uncertainties</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>On the MMGBSA sheet, SEM is over the sampled snapshots WITHIN one replicate. The across-replicate SEM -- the uncertainty quoted in the manuscript table -- is computed from the three replicate rows and is a different, larger quantity. On the FEP sheet, SEM is across the three pmx replicates.</t>
+          <t>Both sheets give raw per-replicate values only. The uncertainty quoted in the manuscript table is the SEM across the three replicates and is computed from these rows; no SEM is tabulated here, to avoid confusion with the within-replicate snapshot SEM, which is a different and smaller quantity.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
+          <t>Compound genotypes</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Eight genotypes are reached by two sequential alchemical legs, and ddG_bind is the sum of the two LEG means. A per-replicate genotype ddG therefore does not exist for them: replicate i of one leg and replicate i of the other are independent simulations of different transformations. The FEP sheet lists legs separately for this reason; ddG_bind for a genotype is the sum of its legs' means.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>The FEP sheet lists only genotypes with a completed pmx leg; any genotype still running is omitted rather than shown blank, and is added once its ddG lands.</t>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>The FEP sheet lists only genotypes whose legs have completed. Leg ddG is the BAR free energy of the holo leg minus that of the apo leg; the analytical net-charge correction (~1e-4 kcal/mol for these box sizes) is not included and does not affect the reported values.</t>
         </is>
       </c>
     </row>

--- a/manuscript/Supplementary-Table-3.xlsx
+++ b/manuscript/Supplementary-Table-3.xlsx
@@ -2296,7 +2296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2305,6 +2305,12 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2325,17 +2331,47 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>dG holo (kcal/mol)</t>
+          <t>dG holo, BAR (kcal/mol)</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>dG apo (kcal/mol)</t>
+          <t>dG apo, BAR (kcal/mol)</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Leg ddG bind (kcal/mol)</t>
+          <t>Leg ddG bind, BAR (kcal/mol)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>dG holo, CGI (kcal/mol)</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>dG apo, CGI (kcal/mol)</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Leg ddG bind, CGI (kcal/mol)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>dG holo, Jarzynski (kcal/mol)</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>dG apo, Jarzynski (kcal/mol)</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Leg ddG bind, Jarzynski (kcal/mol)</t>
         </is>
       </c>
     </row>
@@ -2362,6 +2398,24 @@
       <c r="F2" s="7" t="n">
         <v>0.9100000000000001</v>
       </c>
+      <c r="G2" s="7" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>0.5599999999999987</v>
+      </c>
+      <c r="J2" s="7" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="K2" s="7" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="L2" s="7" t="n">
+        <v>1.48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2386,6 +2440,24 @@
       <c r="F3" s="7" t="n">
         <v>3.440000000000001</v>
       </c>
+      <c r="G3" s="7" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L3" s="7" t="n">
+        <v>3.399999999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2410,6 +2482,24 @@
       <c r="F4" s="7" t="n">
         <v>2.460000000000001</v>
       </c>
+      <c r="G4" s="7" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>2.530000000000001</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>2.34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -2434,6 +2524,24 @@
       <c r="F5" s="7" t="n">
         <v>0.09000000000000341</v>
       </c>
+      <c r="G5" s="7" t="n">
+        <v>-78.33</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>-77.61</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>-0.7199999999999989</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>-78.09999999999999</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>-78.06999999999999</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>-0.03000000000000114</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -2458,6 +2566,24 @@
       <c r="F6" s="7" t="n">
         <v>0.8200000000000074</v>
       </c>
+      <c r="G6" s="7" t="n">
+        <v>-77.87</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>-79.34</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1.469999999999999</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>-78.90000000000001</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>-79.67</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>0.769999999999996</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2482,6 +2608,24 @@
       <c r="F7" s="7" t="n">
         <v>0.710000000000008</v>
       </c>
+      <c r="G7" s="7" t="n">
+        <v>-76.86</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>-77.72</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.8599999999999994</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>-77.8</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>-77.70999999999999</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>-0.09000000000000341</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2506,6 +2650,24 @@
       <c r="F8" s="7" t="n">
         <v>-2.57</v>
       </c>
+      <c r="G8" s="7" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>-2.43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2530,6 +2692,24 @@
       <c r="F9" s="7" t="n">
         <v>1.09</v>
       </c>
+      <c r="G9" s="7" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>-0.2100000000000009</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0.7699999999999996</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2554,6 +2734,24 @@
       <c r="F10" s="7" t="n">
         <v>-0.490000000000002</v>
       </c>
+      <c r="G10" s="7" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>-0.8900000000000006</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2578,6 +2776,24 @@
       <c r="F11" s="7" t="n">
         <v>0.3799999999999999</v>
       </c>
+      <c r="G11" s="7" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.3700000000000001</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0.2999999999999998</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2602,6 +2818,24 @@
       <c r="F12" s="7" t="n">
         <v>0.4900000000000002</v>
       </c>
+      <c r="G12" s="7" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.6799999999999997</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.5700000000000003</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2626,6 +2860,24 @@
       <c r="F13" s="7" t="n">
         <v>-0.05999999999999961</v>
       </c>
+      <c r="G13" s="7" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>-0.1699999999999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2650,6 +2902,24 @@
       <c r="F14" s="7" t="n">
         <v>5.93</v>
       </c>
+      <c r="G14" s="7" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>6.120000000000001</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2674,6 +2944,24 @@
       <c r="F15" s="7" t="n">
         <v>5.940000000000001</v>
       </c>
+      <c r="G15" s="7" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>6.029999999999999</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>5.679999999999998</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2698,6 +2986,24 @@
       <c r="F16" s="7" t="n">
         <v>6.42</v>
       </c>
+      <c r="G16" s="7" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>6.050000000000001</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>6.850000000000001</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -2722,6 +3028,24 @@
       <c r="F17" s="7" t="n">
         <v>1.35</v>
       </c>
+      <c r="G17" s="7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -2746,6 +3070,24 @@
       <c r="F18" s="7" t="n">
         <v>2.49</v>
       </c>
+      <c r="G18" s="7" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>2.399999999999999</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>2.67</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -2770,6 +3112,24 @@
       <c r="F19" s="7" t="n">
         <v>2.2</v>
       </c>
+      <c r="G19" s="7" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>2.81</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -2794,6 +3154,24 @@
       <c r="F20" s="7" t="n">
         <v>-1.609999999999999</v>
       </c>
+      <c r="G20" s="7" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>-0.7699999999999996</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -2818,6 +3196,24 @@
       <c r="F21" s="7" t="n">
         <v>0.4800000000000004</v>
       </c>
+      <c r="G21" s="7" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0.2399999999999984</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>0.8499999999999979</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -2842,6 +3238,24 @@
       <c r="F22" s="7" t="n">
         <v>0.08999999999999986</v>
       </c>
+      <c r="G22" s="7" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.240000000000002</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>0.2800000000000011</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -2866,6 +3280,24 @@
       <c r="F23" s="7" t="n">
         <v>0.09000000000000341</v>
       </c>
+      <c r="G23" s="7" t="n">
+        <v>-78.33</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>-77.61</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>-0.7199999999999989</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>-78.09999999999999</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>-78.06999999999999</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>-0.03000000000000114</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -2890,6 +3322,24 @@
       <c r="F24" s="7" t="n">
         <v>0.8200000000000074</v>
       </c>
+      <c r="G24" s="7" t="n">
+        <v>-77.87</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>-79.34</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>1.469999999999999</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>-78.90000000000001</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>-79.67</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0.769999999999996</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -2914,6 +3364,24 @@
       <c r="F25" s="7" t="n">
         <v>0.710000000000008</v>
       </c>
+      <c r="G25" s="7" t="n">
+        <v>-76.86</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>-77.72</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>0.8599999999999994</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>-77.8</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>-77.70999999999999</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>-0.09000000000000341</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -2938,6 +3406,24 @@
       <c r="F26" s="7" t="n">
         <v>2.710000000000001</v>
       </c>
+      <c r="G26" s="7" t="n">
+        <v>-40.41</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>-42.5</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>2.090000000000003</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>-40.13</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>-43.68</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>3.549999999999997</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -2962,6 +3448,24 @@
       <c r="F27" s="7" t="n">
         <v>0.2800000000000011</v>
       </c>
+      <c r="G27" s="7" t="n">
+        <v>-41.65</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>-42.42</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0.7700000000000031</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>-40.93</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>-42.12</v>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>1.189999999999998</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2986,6 +3490,24 @@
       <c r="F28" s="7" t="n">
         <v>0.6599999999999966</v>
       </c>
+      <c r="G28" s="7" t="n">
+        <v>-43.46</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>-44.09</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>0.6300000000000026</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>-42.71</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>-43.58</v>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>0.8699999999999974</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -3010,6 +3532,24 @@
       <c r="F29" s="7" t="n">
         <v>0.09000000000000341</v>
       </c>
+      <c r="G29" s="7" t="n">
+        <v>-78.33</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>-77.61</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>-0.7199999999999989</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>-78.09999999999999</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>-78.06999999999999</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>-0.03000000000000114</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -3034,6 +3574,24 @@
       <c r="F30" s="7" t="n">
         <v>0.8200000000000074</v>
       </c>
+      <c r="G30" s="7" t="n">
+        <v>-77.87</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>-79.34</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>1.469999999999999</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>-78.90000000000001</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>-79.67</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>0.769999999999996</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -3058,6 +3616,24 @@
       <c r="F31" s="7" t="n">
         <v>0.710000000000008</v>
       </c>
+      <c r="G31" s="7" t="n">
+        <v>-76.86</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>-77.72</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>0.8599999999999994</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>-77.8</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>-77.70999999999999</v>
+      </c>
+      <c r="L31" s="7" t="n">
+        <v>-0.09000000000000341</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -3082,6 +3658,24 @@
       <c r="F32" s="7" t="n">
         <v>-0.7100000000000009</v>
       </c>
+      <c r="G32" s="7" t="n">
+        <v>-60.92</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>-59.54</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>-1.380000000000003</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>-60.32</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>-59.14</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>-1.18</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -3106,6 +3700,24 @@
       <c r="F33" s="7" t="n">
         <v>1.390000000000001</v>
       </c>
+      <c r="G33" s="7" t="n">
+        <v>-49.33</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>-51.93</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>2.600000000000001</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>-49.67</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>-51.07</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>1.399999999999999</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -3130,6 +3742,24 @@
       <c r="F34" s="7" t="n">
         <v>5.32</v>
       </c>
+      <c r="G34" s="7" t="n">
+        <v>-48.62</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>-55.08</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>6.460000000000001</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>-47.94</v>
+      </c>
+      <c r="K34" s="7" t="n">
+        <v>-53.01</v>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>5.07</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -3154,6 +3784,24 @@
       <c r="F35" s="7" t="n">
         <v>1.82</v>
       </c>
+      <c r="G35" s="7" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>1.190000000000001</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="L35" s="7" t="n">
+        <v>1.719999999999999</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -3178,6 +3826,24 @@
       <c r="F36" s="7" t="n">
         <v>2.609999999999999</v>
       </c>
+      <c r="G36" s="7" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>2.709999999999997</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="L36" s="7" t="n">
+        <v>3.050000000000001</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -3202,6 +3868,24 @@
       <c r="F37" s="7" t="n">
         <v>0.8399999999999999</v>
       </c>
+      <c r="G37" s="7" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>0.9000000000000021</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="L37" s="7" t="n">
+        <v>1.16</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -3226,6 +3910,24 @@
       <c r="F38" s="7" t="n">
         <v>1.370000000000001</v>
       </c>
+      <c r="G38" s="7" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="K38" s="7" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="L38" s="7" t="n">
+        <v>1.41</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -3250,6 +3952,24 @@
       <c r="F39" s="7" t="n">
         <v>2.199999999999999</v>
       </c>
+      <c r="G39" s="7" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>22.03</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="K39" s="7" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="L39" s="7" t="n">
+        <v>2.239999999999998</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -3274,6 +3994,24 @@
       <c r="F40" s="7" t="n">
         <v>0.6600000000000001</v>
       </c>
+      <c r="G40" s="7" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>0.6799999999999997</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="K40" s="7" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="L40" s="7" t="n">
+        <v>0.7299999999999969</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -3298,6 +4036,24 @@
       <c r="F41" s="7" t="n">
         <v>0.5800000000000018</v>
       </c>
+      <c r="G41" s="7" t="n">
+        <v>-18.04</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>-18.46</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>0.4200000000000017</v>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>-17.84</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>-18.66</v>
+      </c>
+      <c r="L41" s="7" t="n">
+        <v>0.8200000000000003</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -3322,6 +4078,24 @@
       <c r="F42" s="7" t="n">
         <v>-0.5800000000000001</v>
       </c>
+      <c r="G42" s="7" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>-11.82</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>-12.46</v>
+      </c>
+      <c r="K42" s="7" t="n">
+        <v>-11.82</v>
+      </c>
+      <c r="L42" s="7" t="n">
+        <v>-0.6400000000000006</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -3346,6 +4120,24 @@
       <c r="F43" s="7" t="n">
         <v>0.1400000000000006</v>
       </c>
+      <c r="G43" s="7" t="n">
+        <v>-11.69</v>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>-11.88</v>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>0.1900000000000013</v>
+      </c>
+      <c r="J43" s="7" t="n">
+        <v>-11.76</v>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>-11.91</v>
+      </c>
+      <c r="L43" s="7" t="n">
+        <v>0.1500000000000004</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -3370,6 +4162,24 @@
       <c r="F44" s="7" t="n">
         <v>0.09000000000000341</v>
       </c>
+      <c r="G44" s="7" t="n">
+        <v>-78.33</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>-77.61</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>-0.7199999999999989</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>-78.09999999999999</v>
+      </c>
+      <c r="K44" s="7" t="n">
+        <v>-78.06999999999999</v>
+      </c>
+      <c r="L44" s="7" t="n">
+        <v>-0.03000000000000114</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -3394,6 +4204,24 @@
       <c r="F45" s="7" t="n">
         <v>0.8200000000000074</v>
       </c>
+      <c r="G45" s="7" t="n">
+        <v>-77.87</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>-79.34</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>1.469999999999999</v>
+      </c>
+      <c r="J45" s="7" t="n">
+        <v>-78.90000000000001</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>-79.67</v>
+      </c>
+      <c r="L45" s="7" t="n">
+        <v>0.769999999999996</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -3418,6 +4246,24 @@
       <c r="F46" s="7" t="n">
         <v>0.710000000000008</v>
       </c>
+      <c r="G46" s="7" t="n">
+        <v>-76.86</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>-77.72</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>0.8599999999999994</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>-77.8</v>
+      </c>
+      <c r="K46" s="7" t="n">
+        <v>-77.70999999999999</v>
+      </c>
+      <c r="L46" s="7" t="n">
+        <v>-0.09000000000000341</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -3442,6 +4288,24 @@
       <c r="F47" s="7" t="n">
         <v>-0.6000000000000005</v>
       </c>
+      <c r="G47" s="7" t="n">
+        <v>-7.73</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>-7.78</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>0.04999999999999982</v>
+      </c>
+      <c r="J47" s="7" t="n">
+        <v>-8.449999999999999</v>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>-7.69</v>
+      </c>
+      <c r="L47" s="7" t="n">
+        <v>-0.7599999999999989</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -3466,6 +4330,24 @@
       <c r="F48" s="7" t="n">
         <v>-1.44</v>
       </c>
+      <c r="G48" s="7" t="n">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>-7.74</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>-1.720000000000001</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>-9.32</v>
+      </c>
+      <c r="K48" s="7" t="n">
+        <v>-8.06</v>
+      </c>
+      <c r="L48" s="7" t="n">
+        <v>-1.26</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -3490,6 +4372,24 @@
       <c r="F49" s="7" t="n">
         <v>-1.63</v>
       </c>
+      <c r="G49" s="7" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>-7.87</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>-1.329999999999999</v>
+      </c>
+      <c r="J49" s="7" t="n">
+        <v>-8.93</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>-7.21</v>
+      </c>
+      <c r="L49" s="7" t="n">
+        <v>-1.72</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -3514,6 +4414,24 @@
       <c r="F50" s="7" t="n">
         <v>0.51</v>
       </c>
+      <c r="G50" s="7" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L50" s="7" t="n">
+        <v>-0.06999999999999999</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -3538,6 +4456,24 @@
       <c r="F51" s="7" t="n">
         <v>0.51</v>
       </c>
+      <c r="G51" s="7" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>0.7499999999999998</v>
+      </c>
+      <c r="J51" s="7" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="L51" s="7" t="n">
+        <v>-0.3599999999999999</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -3562,6 +4498,24 @@
       <c r="F52" s="7" t="n">
         <v>-1.93</v>
       </c>
+      <c r="G52" s="7" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I52" s="7" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="K52" s="7" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="L52" s="7" t="n">
+        <v>-1.7</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -3586,6 +4540,24 @@
       <c r="F53" s="7" t="n">
         <v>-1.79</v>
       </c>
+      <c r="G53" s="7" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="J53" s="7" t="n">
+        <v>-3.84</v>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="L53" s="7" t="n">
+        <v>-2.24</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -3610,6 +4582,24 @@
       <c r="F54" s="7" t="n">
         <v>1.22</v>
       </c>
+      <c r="G54" s="7" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="K54" s="7" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="L54" s="7" t="n">
+        <v>1.37</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -3634,6 +4624,24 @@
       <c r="F55" s="7" t="n">
         <v>-0.98</v>
       </c>
+      <c r="G55" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="J55" s="7" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="K55" s="7" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="L55" s="7" t="n">
+        <v>-1.05</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -3658,6 +4666,24 @@
       <c r="F56" s="7" t="n">
         <v>0.9100000000000001</v>
       </c>
+      <c r="G56" s="7" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>0.5599999999999987</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="K56" s="7" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="L56" s="7" t="n">
+        <v>1.48</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -3682,6 +4708,24 @@
       <c r="F57" s="7" t="n">
         <v>3.440000000000001</v>
       </c>
+      <c r="G57" s="7" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K57" s="7" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L57" s="7" t="n">
+        <v>3.399999999999999</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -3706,6 +4750,24 @@
       <c r="F58" s="7" t="n">
         <v>2.460000000000001</v>
       </c>
+      <c r="G58" s="7" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>2.530000000000001</v>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="K58" s="7" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="L58" s="7" t="n">
+        <v>2.34</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -3730,6 +4792,24 @@
       <c r="F59" s="7" t="n">
         <v>2.359999999999999</v>
       </c>
+      <c r="G59" s="7" t="n">
+        <v>-20.41</v>
+      </c>
+      <c r="H59" s="7" t="n">
+        <v>-22.78</v>
+      </c>
+      <c r="I59" s="7" t="n">
+        <v>2.370000000000001</v>
+      </c>
+      <c r="J59" s="7" t="n">
+        <v>-20.17</v>
+      </c>
+      <c r="K59" s="7" t="n">
+        <v>-22.19</v>
+      </c>
+      <c r="L59" s="7" t="n">
+        <v>2.02</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -3754,6 +4834,24 @@
       <c r="F60" s="7" t="n">
         <v>1.300000000000001</v>
       </c>
+      <c r="G60" s="7" t="n">
+        <v>-19.98</v>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>-21.58</v>
+      </c>
+      <c r="I60" s="7" t="n">
+        <v>1.599999999999998</v>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>-19.82</v>
+      </c>
+      <c r="K60" s="7" t="n">
+        <v>-20.99</v>
+      </c>
+      <c r="L60" s="7" t="n">
+        <v>1.169999999999998</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -3778,6 +4876,24 @@
       <c r="F61" s="7" t="n">
         <v>4.25</v>
       </c>
+      <c r="G61" s="7" t="n">
+        <v>-19.94</v>
+      </c>
+      <c r="H61" s="7" t="n">
+        <v>-24.08</v>
+      </c>
+      <c r="I61" s="7" t="n">
+        <v>4.139999999999997</v>
+      </c>
+      <c r="J61" s="7" t="n">
+        <v>-19.32</v>
+      </c>
+      <c r="K61" s="7" t="n">
+        <v>-22.96</v>
+      </c>
+      <c r="L61" s="7" t="n">
+        <v>3.640000000000001</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -3802,6 +4918,24 @@
       <c r="F62" s="7" t="n">
         <v>1.82</v>
       </c>
+      <c r="G62" s="7" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="H62" s="7" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="I62" s="7" t="n">
+        <v>1.190000000000001</v>
+      </c>
+      <c r="J62" s="7" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="K62" s="7" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="L62" s="7" t="n">
+        <v>1.719999999999999</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -3826,6 +4960,24 @@
       <c r="F63" s="7" t="n">
         <v>2.609999999999999</v>
       </c>
+      <c r="G63" s="7" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="H63" s="7" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="I63" s="7" t="n">
+        <v>2.709999999999997</v>
+      </c>
+      <c r="J63" s="7" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="K63" s="7" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="L63" s="7" t="n">
+        <v>3.050000000000001</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -3850,6 +5002,24 @@
       <c r="F64" s="7" t="n">
         <v>0.8399999999999999</v>
       </c>
+      <c r="G64" s="7" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>0.9000000000000021</v>
+      </c>
+      <c r="J64" s="7" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="K64" s="7" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="L64" s="7" t="n">
+        <v>1.16</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -3874,6 +5044,24 @@
       <c r="F65" s="7" t="n">
         <v>5.42</v>
       </c>
+      <c r="G65" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="I65" s="7" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="J65" s="7" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="K65" s="7" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="L65" s="7" t="n">
+        <v>5.09</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -3898,6 +5086,24 @@
       <c r="F66" s="7" t="n">
         <v>4.390000000000001</v>
       </c>
+      <c r="G66" s="7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K66" s="7" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="L66" s="7" t="n">
+        <v>5.75</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -3922,6 +5128,24 @@
       <c r="F67" s="7" t="n">
         <v>3.75</v>
       </c>
+      <c r="G67" s="7" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>-4.94</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J67" s="7" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="K67" s="7" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="L67" s="7" t="n">
+        <v>2.86</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -3946,6 +5170,24 @@
       <c r="F68" s="7" t="n">
         <v>1.840000000000003</v>
       </c>
+      <c r="G68" s="7" t="n">
+        <v>-41.53</v>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>-43.82</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>2.289999999999999</v>
+      </c>
+      <c r="J68" s="7" t="n">
+        <v>-41.43</v>
+      </c>
+      <c r="K68" s="7" t="n">
+        <v>-42.61</v>
+      </c>
+      <c r="L68" s="7" t="n">
+        <v>1.18</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -3970,6 +5212,24 @@
       <c r="F69" s="7" t="n">
         <v>0.269999999999996</v>
       </c>
+      <c r="G69" s="7" t="n">
+        <v>-42.83</v>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>-43.26</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <v>0.4299999999999997</v>
+      </c>
+      <c r="J69" s="7" t="n">
+        <v>-43.32</v>
+      </c>
+      <c r="K69" s="7" t="n">
+        <v>-44.02</v>
+      </c>
+      <c r="L69" s="7" t="n">
+        <v>0.7000000000000028</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -3994,6 +5254,24 @@
       <c r="F70" s="7" t="n">
         <v>3.740000000000002</v>
       </c>
+      <c r="G70" s="7" t="n">
+        <v>-40.94</v>
+      </c>
+      <c r="H70" s="7" t="n">
+        <v>-43.79</v>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>2.850000000000001</v>
+      </c>
+      <c r="J70" s="7" t="n">
+        <v>-40.04</v>
+      </c>
+      <c r="K70" s="7" t="n">
+        <v>-44.12</v>
+      </c>
+      <c r="L70" s="7" t="n">
+        <v>4.079999999999998</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -4018,6 +5296,24 @@
       <c r="F71" s="7" t="n">
         <v>1.82</v>
       </c>
+      <c r="G71" s="7" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="H71" s="7" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="I71" s="7" t="n">
+        <v>1.190000000000001</v>
+      </c>
+      <c r="J71" s="7" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="K71" s="7" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="L71" s="7" t="n">
+        <v>1.719999999999999</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -4042,6 +5338,24 @@
       <c r="F72" s="7" t="n">
         <v>2.609999999999999</v>
       </c>
+      <c r="G72" s="7" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="H72" s="7" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="I72" s="7" t="n">
+        <v>2.709999999999997</v>
+      </c>
+      <c r="J72" s="7" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="K72" s="7" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="L72" s="7" t="n">
+        <v>3.050000000000001</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -4066,6 +5380,24 @@
       <c r="F73" s="7" t="n">
         <v>0.8399999999999999</v>
       </c>
+      <c r="G73" s="7" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>0.9000000000000021</v>
+      </c>
+      <c r="J73" s="7" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="K73" s="7" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="L73" s="7" t="n">
+        <v>1.16</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -4090,6 +5422,24 @@
       <c r="F74" s="7" t="n">
         <v>1.050000000000001</v>
       </c>
+      <c r="G74" s="7" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>1.059999999999999</v>
+      </c>
+      <c r="J74" s="7" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="K74" s="7" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="L74" s="7" t="n">
+        <v>1.219999999999999</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -4114,6 +5464,24 @@
       <c r="F75" s="7" t="n">
         <v>0.9399999999999977</v>
       </c>
+      <c r="G75" s="7" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>0.7199999999999989</v>
+      </c>
+      <c r="J75" s="7" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="K75" s="7" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="L75" s="7" t="n">
+        <v>1.129999999999999</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -4138,6 +5506,24 @@
       <c r="F76" s="7" t="n">
         <v>3.91</v>
       </c>
+      <c r="G76" s="7" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>3.309999999999999</v>
+      </c>
+      <c r="J76" s="7" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="K76" s="7" t="n">
+        <v>21.23</v>
+      </c>
+      <c r="L76" s="7" t="n">
+        <v>3.460000000000001</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -4162,6 +5548,24 @@
       <c r="F77" s="7" t="n">
         <v>1.82</v>
       </c>
+      <c r="G77" s="7" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>1.190000000000001</v>
+      </c>
+      <c r="J77" s="7" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="K77" s="7" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="L77" s="7" t="n">
+        <v>1.719999999999999</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -4186,6 +5590,24 @@
       <c r="F78" s="7" t="n">
         <v>2.609999999999999</v>
       </c>
+      <c r="G78" s="7" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <v>2.709999999999997</v>
+      </c>
+      <c r="J78" s="7" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="K78" s="7" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="L78" s="7" t="n">
+        <v>3.050000000000001</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -4210,6 +5632,24 @@
       <c r="F79" s="7" t="n">
         <v>0.8399999999999999</v>
       </c>
+      <c r="G79" s="7" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="H79" s="7" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="I79" s="7" t="n">
+        <v>0.9000000000000021</v>
+      </c>
+      <c r="J79" s="7" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="K79" s="7" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="L79" s="7" t="n">
+        <v>1.16</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -4234,6 +5674,24 @@
       <c r="F80" s="7" t="n">
         <v>0.51</v>
       </c>
+      <c r="G80" s="7" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H80" s="7" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="I80" s="7" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J80" s="7" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="K80" s="7" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L80" s="7" t="n">
+        <v>-0.06999999999999999</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -4258,6 +5716,24 @@
       <c r="F81" s="7" t="n">
         <v>0.51</v>
       </c>
+      <c r="G81" s="7" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="H81" s="7" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="I81" s="7" t="n">
+        <v>0.7499999999999998</v>
+      </c>
+      <c r="J81" s="7" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="K81" s="7" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="L81" s="7" t="n">
+        <v>-0.3599999999999999</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -4281,6 +5757,24 @@
       </c>
       <c r="F82" s="7" t="n">
         <v>-1.93</v>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="H82" s="7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I82" s="7" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="J82" s="7" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="K82" s="7" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="L82" s="7" t="n">
+        <v>-1.7</v>
       </c>
     </row>
   </sheetData>
@@ -4294,7 +5788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4328,58 +5822,70 @@
     <row r="3" ht="46" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>ddG (FEP sheet)</t>
+          <t>ddG estimators</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>pmx non-equilibrium FEP binding FREE ENERGY from alchemical switching. This is the quantity that corresponds to binding. ddE and ddG are different observables and should not be read as interchangeable.</t>
+          <t>pmx reports three free-energy estimators from the same switching work: BAR (Bennett acceptance ratio), CGI (Crooks Gaussian intersection) and Jarzynski. All three are given; the manuscript quotes BAR. Their agreement is one of the pipeline's confidence criteria -- here BAR and the other two differ by a median of ~0.2 kcal/mol per leg and replicate.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>ddE referencing</t>
+          <t>ddG (FEP sheet)</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Each mutant replicate is referenced to the mean of the three WT production replicates. WT's own three replicates are listed on the MMGBSA sheet; their ddE values are each replicate's deviation from that mean and therefore show the reference spread directly. WT-reference columns are omitted because they would repeat one constant on every row.</t>
+          <t>pmx non-equilibrium FEP binding FREE ENERGY from alchemical switching. This is the quantity that corresponds to binding. ddE and ddG are different observables and should not be read as interchangeable.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Uncertainties</t>
+          <t>ddE referencing</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Both sheets give raw per-replicate values only. The uncertainty quoted in the manuscript table is the SEM across the three replicates and is computed from these rows; no SEM is tabulated here, to avoid confusion with the within-replicate snapshot SEM, which is a different and smaller quantity.</t>
+          <t>Each mutant replicate is referenced to the mean of the three WT production replicates. WT's own three replicates are listed on the MMGBSA sheet; their ddE values are each replicate's deviation from that mean and therefore show the reference spread directly. WT-reference columns are omitted because they would repeat one constant on every row.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Compound genotypes</t>
+          <t>Uncertainties</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Eight genotypes are reached by two sequential alchemical legs, and ddG_bind is the sum of the two LEG means. A per-replicate genotype ddG therefore does not exist for them: replicate i of one leg and replicate i of the other are independent simulations of different transformations. The FEP sheet lists legs separately for this reason; ddG_bind for a genotype is the sum of its legs' means.</t>
+          <t>Both sheets give raw per-replicate values only. The uncertainty quoted in the manuscript table is the SEM across the three replicates and is computed from these rows; no SEM is tabulated here, to avoid confusion with the within-replicate snapshot SEM, which is a different and smaller quantity.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
+          <t>Compound genotypes</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Eight genotypes are reached by two sequential alchemical legs, and ddG_bind is the sum of the two LEG means. A per-replicate genotype ddG therefore does not exist for them: replicate i of one leg and replicate i of the other are independent simulations of different transformations. The FEP sheet lists legs separately for this reason; ddG_bind for a genotype is the sum of its legs' means.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>The FEP sheet lists only genotypes whose legs have completed. Leg ddG is the BAR free energy of the holo leg minus that of the apo leg; the analytical net-charge correction (~1e-4 kcal/mol for these box sizes) is not included and does not affect the reported values.</t>
         </is>

--- a/manuscript/Supplementary-Table-3.xlsx
+++ b/manuscript/Supplementary-Table-3.xlsx
@@ -535,22 +535,22 @@
       </c>
       <c r="C2" s="5" t="inlineStr"/>
       <c r="D2" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>-66.41186736104038</v>
+        <v>-67.09777727386125</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>-68.68663238187065</v>
+        <v>-69.55614303915033</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-7.005816458032588</v>
+        <v>-8.796058545034063</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>16.99900066419496</v>
+        <v>18.85121210583309</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-7.718419185332086</v>
+        <v>-7.596787795509937</v>
       </c>
     </row>
     <row r="3">
@@ -564,22 +564,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr"/>
       <c r="D3" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>-61.49999328430591</v>
+        <v>-66.63453948154265</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>-64.83560997899107</v>
+        <v>-69.1890813448113</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-6.253771707739446</v>
+        <v>-8.72120501379259</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>17.27782494707272</v>
+        <v>18.90241416872801</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-7.688436544648092</v>
+        <v>-7.626667291666764</v>
       </c>
     </row>
     <row r="4">
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>-66.16427425033113</v>
+        <v>-66.54819101102298</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-68.25282248562766</v>
+        <v>-68.62206315097293</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-9.040890960916244</v>
+        <v>-9.422941248495199</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>18.85339425125268</v>
+        <v>19.11685785873442</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-7.723955055039881</v>
+        <v>-7.62004447028924</v>
       </c>
     </row>
     <row r="5">
@@ -624,22 +624,22 @@
         <v>1.1</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>-60.40815400796441</v>
+        <v>-63.18324857397994</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-63.44334564664064</v>
+        <v>-66.02382924098322</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-7.351850007577332</v>
+        <v>-8.564124362369444</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>18.07155203408994</v>
+        <v>18.94216094372605</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-7.684510387836405</v>
+        <v>-7.537455914353321</v>
       </c>
     </row>
     <row r="6">
@@ -655,22 +655,22 @@
         <v>1.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>-61.76776035313105</v>
+        <v>-64.8607116214085</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-65.41322837904237</v>
+        <v>-67.62716478586684</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-6.539088162909104</v>
+        <v>-8.802448971576652</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>17.84675677465435</v>
+        <v>19.138141371324</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-7.662200585833927</v>
+        <v>-7.56923923528901</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>1.1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-64.58400657916043</v>
+        <v>-66.27582136462837</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-67.66918259663913</v>
+        <v>-68.68031669547415</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-7.180154835992631</v>
+        <v>-9.060258658889945</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>18.12584778546831</v>
+        <v>19.18362662167668</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-7.860516931996973</v>
+        <v>-7.718872631940968</v>
       </c>
     </row>
     <row r="8">
@@ -717,22 +717,22 @@
         <v>1.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-64.45114051904513</v>
+        <v>-67.70017615048951</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-67.45540251103827</v>
+        <v>-69.75040323703979</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-10.27039954078637</v>
+        <v>-11.31861515964937</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>21.00861719871798</v>
+        <v>21.0361664609745</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-7.733955665938485</v>
+        <v>-7.667324214774838</v>
       </c>
     </row>
     <row r="9">
@@ -748,22 +748,22 @@
         <v>1.2</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-65.25044366774296</v>
+        <v>-67.57488767861169</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-67.648259263501</v>
+        <v>-69.89434702387092</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-9.480856196237664</v>
+        <v>-11.21327683763739</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>19.65072045590636</v>
+        <v>21.20515270853134</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-7.772048663910671</v>
+        <v>-7.672416525634707</v>
       </c>
     </row>
     <row r="10">
@@ -779,22 +779,22 @@
         <v>1.2</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>-65.792661442929</v>
+        <v>-67.2488877012722</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-68.60718573345586</v>
+        <v>-69.51763444094004</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-9.361331040638747</v>
+        <v>-10.69606493186452</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>19.9526052857904</v>
+        <v>20.62331869770874</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-7.776749954624795</v>
+        <v>-7.658507026176379</v>
       </c>
     </row>
     <row r="11">
@@ -810,22 +810,22 @@
         <v>1.4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>-62.95778207084517</v>
+        <v>-65.32770321982775</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-66.36487946428976</v>
+        <v>-68.27940040187465</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-7.813498958324842</v>
+        <v>-8.906081613771629</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>18.96053080804945</v>
+        <v>19.49714798316445</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-7.739934456280039</v>
+        <v>-7.639369187345924</v>
       </c>
     </row>
     <row r="12">
@@ -841,22 +841,22 @@
         <v>1.4</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>-63.72598756336726</v>
+        <v>-65.37564845527885</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>-67.01210475757534</v>
+        <v>-67.8298437003639</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-8.786756058091623</v>
+        <v>-9.461386505511172</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>19.74771164115482</v>
+        <v>19.49272026295415</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-7.674838388855098</v>
+        <v>-7.577138512357927</v>
       </c>
     </row>
     <row r="13">
@@ -872,22 +872,22 @@
         <v>1.4</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-61.96079965810659</v>
+        <v>-65.84541189571661</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-65.35201240881888</v>
+        <v>-68.53128133300692</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-8.034026906184669</v>
+        <v>-9.89535856456135</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>19.08418270643537</v>
+        <v>20.17639463763848</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-7.658943049538432</v>
+        <v>-7.595166635786826</v>
       </c>
     </row>
     <row r="14">
@@ -903,22 +903,22 @@
         <v>2.7</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-62.4624803430334</v>
+        <v>-65.61663932477923</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-66.05485797771564</v>
+        <v>-68.45629387832098</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-7.641005064456341</v>
+        <v>-8.95372622843791</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>18.92588275340502</v>
+        <v>19.37789410979524</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-7.692500054266439</v>
+        <v>-7.584513327815564</v>
       </c>
     </row>
     <row r="15">
@@ -934,22 +934,22 @@
         <v>2.7</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-62.61053655090234</v>
+        <v>-65.12259538430436</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-65.70152832786376</v>
+        <v>-67.69013686663875</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-6.272605387229088</v>
+        <v>-8.764351866906523</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>17.07663618127885</v>
+        <v>18.94447794379969</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-7.713039017088327</v>
+        <v>-7.612584594558802</v>
       </c>
     </row>
     <row r="16">
@@ -965,22 +965,22 @@
         <v>2.7</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>-63.80051328473958</v>
+        <v>-64.83452668985116</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-66.75195903615305</v>
+        <v>-67.17576673737389</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-6.614831913019093</v>
+        <v>-8.190594067966973</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>17.34024083409209</v>
+        <v>18.13470179446568</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-7.773963169659528</v>
+        <v>-7.602867678975968</v>
       </c>
     </row>
     <row r="17">
@@ -996,22 +996,22 @@
         <v>3.4</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>-60.75560140632334</v>
+        <v>-66.04991469817796</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-64.55375301375172</v>
+        <v>-69.07355656661854</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-7.134752521162296</v>
+        <v>-8.476784377480383</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>18.51566977528267</v>
+        <v>19.06576687245706</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-7.582765646691988</v>
+        <v>-7.56534062653609</v>
       </c>
     </row>
     <row r="18">
@@ -1027,22 +1027,22 @@
         <v>3.4</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>-61.9343561463299</v>
+        <v>-64.46814623911486</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>-65.0136774373922</v>
+        <v>-67.81638702932558</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-9.048143798403812</v>
+        <v>-9.040078094002419</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>19.90167866701378</v>
+        <v>19.97486131824909</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-7.774213577547675</v>
+        <v>-7.586542434035934</v>
       </c>
     </row>
     <row r="19">
@@ -1058,22 +1058,22 @@
         <v>3.4</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-61.64330800475344</v>
+        <v>-62.24962425088203</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-65.19674052305882</v>
+        <v>-65.941716462158</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-6.359447409131056</v>
+        <v>-7.872536201069202</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>17.57099227285294</v>
+        <v>19.09421752105479</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-7.658112345416504</v>
+        <v>-7.529589108709623</v>
       </c>
     </row>
     <row r="20">
@@ -1089,22 +1089,22 @@
         <v>5.2</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-59.76489069548006</v>
+        <v>-62.69269305063899</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-64.82381835438861</v>
+        <v>-66.17054796113509</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-5.433080729931698</v>
+        <v>-8.949906261293433</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>18.06768409152788</v>
+        <v>19.99145198734495</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-7.57567570268766</v>
+        <v>-7.563690815555434</v>
       </c>
     </row>
     <row r="21">
@@ -1120,22 +1120,22 @@
         <v>5.2</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>-63.94669710583119</v>
+        <v>-66.01212816667055</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-67.39882823002668</v>
+        <v>-68.99154222354659</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-7.017787213456882</v>
+        <v>-8.998328801084355</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>18.19134661162104</v>
+        <v>19.61356762034487</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-7.721428273968668</v>
+        <v>-7.635824762384476</v>
       </c>
     </row>
     <row r="22">
@@ -1151,22 +1151,22 @@
         <v>5.2</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>-60.13946200749179</v>
+        <v>-62.55163294836785</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-64.30238051167346</v>
+        <v>-66.45581838380814</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-5.391323535092177</v>
+        <v>-8.305346513185407</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>17.31593590621511</v>
+        <v>19.86631074325532</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-7.761693866941259</v>
+        <v>-7.656778794629624</v>
       </c>
     </row>
     <row r="23">
@@ -1182,22 +1182,22 @@
         <v>6.8</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>-64.27584209331889</v>
+        <v>-65.75849507397595</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>-66.76002895873832</v>
+        <v>-68.59114156863215</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-11.23395150476626</v>
+        <v>-11.12838587679184</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>21.52100630517672</v>
+        <v>21.59381355883742</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-7.802867934991022</v>
+        <v>-7.632781187389366</v>
       </c>
     </row>
     <row r="24">
@@ -1213,22 +1213,22 @@
         <v>6.8</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>-67.09708682146669</v>
+        <v>-69.22046790936737</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-68.85254065622728</v>
+        <v>-70.49654372824862</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-11.02698025584098</v>
+        <v>-11.76090949184284</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>20.55442310428072</v>
+        <v>20.64339688813481</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-7.771989013679168</v>
+        <v>-7.606411577410724</v>
       </c>
     </row>
     <row r="25">
@@ -1244,22 +1244,22 @@
         <v>6.8</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-65.6315586982531</v>
+        <v>-67.06993400708348</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-69.20409704793151</v>
+        <v>-69.95657140009465</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-8.381723528574087</v>
+        <v>-9.520825404463729</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>19.7261222689831</v>
+        <v>20.06318361307877</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-7.771860390730615</v>
+        <v>-7.655720815603865</v>
       </c>
     </row>
     <row r="26">
@@ -1275,22 +1275,22 @@
         <v>7.8</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-62.28110152311058</v>
+        <v>-66.11675958383231</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-65.49890916272631</v>
+        <v>-68.5800664023991</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-8.617056242832012</v>
+        <v>-11.44890798576711</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>19.54350289149676</v>
+        <v>21.58077281018288</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-7.708639009049016</v>
+        <v>-7.668558005848988</v>
       </c>
     </row>
     <row r="27">
@@ -1306,22 +1306,22 @@
         <v>7.8</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>-65.28186510769953</v>
+        <v>-66.56314457982262</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-68.2650433521606</v>
+        <v>-68.99096631363946</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-10.51925011851476</v>
+        <v>-11.70401371225826</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>21.29935456963387</v>
+        <v>21.78319768741527</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-7.796926206658036</v>
+        <v>-7.651362241340184</v>
       </c>
     </row>
     <row r="28">
@@ -1337,22 +1337,22 @@
         <v>7.8</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>-63.66131155480423</v>
+        <v>-65.51164654573738</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>-67.7657268224678</v>
+        <v>-68.62801557173074</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-6.453373468158327</v>
+        <v>-10.00774011364053</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>18.36398400038652</v>
+        <v>20.79306617977515</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-7.806195264564645</v>
+        <v>-7.668957040141234</v>
       </c>
     </row>
     <row r="29">
@@ -1368,22 +1368,22 @@
         <v>18</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>-57.38008470734459</v>
+        <v>-64.35476105977115</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>-62.72151398173793</v>
+        <v>-68.32488048868106</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-6.392180482656252</v>
+        <v>-9.500856413210409</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>19.52829046413502</v>
+        <v>21.25965999143757</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-7.794680707085429</v>
+        <v>-7.788684149317258</v>
       </c>
     </row>
     <row r="30">
@@ -1399,22 +1399,22 @@
         <v>18</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>-55.53307693845253</v>
+        <v>-64.49514710743755</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-59.54655137765724</v>
+        <v>-67.15165534405288</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-7.127701082514587</v>
+        <v>-10.80424250733086</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>18.75110898829327</v>
+        <v>21.03105434724067</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-7.609933466573974</v>
+        <v>-7.570303603294475</v>
       </c>
     </row>
     <row r="31">
@@ -1430,22 +1430,22 @@
         <v>18</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-63.93414284051009</v>
+        <v>-65.61948241743548</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-67.48864896870118</v>
+        <v>-69.2568189571799</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-9.25581805838562</v>
+        <v>-10.75370691996366</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>20.60836943340119</v>
+        <v>22.09211337634756</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-7.798045246824479</v>
+        <v>-7.701069916639455</v>
       </c>
     </row>
     <row r="32">
@@ -1461,22 +1461,22 @@
         <v>9.6</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-61.22991977330631</v>
+        <v>-65.81739833036983</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-64.26225314436225</v>
+        <v>-68.77800040194332</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-8.857603995116015</v>
+        <v>-10.51244489405292</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>19.53291979620151</v>
+        <v>21.11306689209509</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-7.642982430029553</v>
+        <v>-7.640019926468683</v>
       </c>
     </row>
     <row r="33">
@@ -1492,22 +1492,22 @@
         <v>9.6</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>-62.27982366724785</v>
+        <v>-64.85279784013534</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-66.09613947758405</v>
+        <v>-68.27808134156015</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-7.658326934147537</v>
+        <v>-7.898231477045996</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>19.1504311151304</v>
+        <v>18.89590006257562</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-7.675788370646664</v>
+        <v>-7.572385084104812</v>
       </c>
     </row>
     <row r="34">
@@ -1523,22 +1523,22 @@
         <v>9.6</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>-62.1962470841568</v>
+        <v>-64.42025479212116</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-65.6497284173828</v>
+        <v>-68.1202473158055</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-8.129586442686289</v>
+        <v>-8.723291274832484</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>19.22535403964624</v>
+        <v>20.00690544084654</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-7.64228626373393</v>
+        <v>-7.583621642329724</v>
       </c>
     </row>
     <row r="35">
@@ -1554,22 +1554,22 @@
         <v>11</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>-64.44003183381932</v>
+        <v>-65.34933151421892</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>-66.48651887073969</v>
+        <v>-67.64399836106071</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-8.528535327745253</v>
+        <v>-10.10291752583729</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>18.38335480334426</v>
+        <v>20.0172792930676</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-7.808332438678631</v>
+        <v>-7.619694920388508</v>
       </c>
     </row>
     <row r="36">
@@ -1585,22 +1585,22 @@
         <v>11</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>-61.40734173417953</v>
+        <v>-64.82348015710922</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>-64.53652688583327</v>
+        <v>-67.34949459643211</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-8.700640827692087</v>
+        <v>-9.024705221186265</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>19.6601162904991</v>
+        <v>19.24850808502839</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-7.830290311153258</v>
+        <v>-7.697788424519234</v>
       </c>
     </row>
     <row r="37">
@@ -1616,22 +1616,22 @@
         <v>11</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>-59.84600296582544</v>
+        <v>-65.50532151518961</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-63.36437103676406</v>
+        <v>-68.16135663175464</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-6.305163035204239</v>
+        <v>-8.859356987231893</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>17.52642573179752</v>
+        <v>19.16226839244252</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-7.702894625654641</v>
+        <v>-7.646876288645581</v>
       </c>
     </row>
     <row r="38">
@@ -1647,22 +1647,22 @@
         <v>36</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>-66.30504766559341</v>
+        <v>-67.90934781691038</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-68.38616329170409</v>
+        <v>-69.94081432524486</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-11.37902648945127</v>
+        <v>-12.673219094893</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>21.28379540963109</v>
+        <v>22.38816920475568</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-7.823653294069134</v>
+        <v>-7.68348360152819</v>
       </c>
     </row>
     <row r="39">
@@ -1678,22 +1678,22 @@
         <v>36</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>-63.43280365428983</v>
+        <v>-67.17745334906068</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-65.80800289795776</v>
+        <v>-69.23032810360286</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-8.913692429192212</v>
+        <v>-10.73894613992163</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>19.02037118178708</v>
+        <v>20.47230368590492</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-7.731479508926945</v>
+        <v>-7.680482791441121</v>
       </c>
     </row>
     <row r="40">
@@ -1709,22 +1709,22 @@
         <v>36</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>-67.73235479061719</v>
+        <v>-69.45487799258538</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>-69.6635012781677</v>
+        <v>-71.04250211487761</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-10.7515047550576</v>
+        <v>-11.7570753753683</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>20.44037783351045</v>
+        <v>21.00903830154448</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-7.757726590902353</v>
+        <v>-7.664338803883947</v>
       </c>
     </row>
     <row r="41">
@@ -1740,22 +1740,22 @@
         <v>93</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>-61.90023933641923</v>
+        <v>-63.82111462913426</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>-64.80987174198351</v>
+        <v>-66.77364425108671</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-7.994813228953026</v>
+        <v>-8.997072084813125</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>18.58446365560674</v>
+        <v>19.47158641158737</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-7.680018021089396</v>
+        <v>-7.521984704821789</v>
       </c>
     </row>
     <row r="42">
@@ -1771,22 +1771,22 @@
         <v>93</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>-66.2657577285962</v>
+        <v>-64.57129879091609</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>-69.49180190846108</v>
+        <v>-67.56477246621237</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-7.812051980914379</v>
+        <v>-8.780551588955026</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>18.75753585056867</v>
+        <v>19.33869854214086</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-7.719439689789401</v>
+        <v>-7.564673277889565</v>
       </c>
     </row>
     <row r="43">
@@ -1802,22 +1802,22 @@
         <v>93</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>-62.63181740762563</v>
+        <v>-64.47872984530935</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>-65.41136114401274</v>
+        <v>-67.59546532473266</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-7.962329169613958</v>
+        <v>-8.258982847035872</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>18.42533484471688</v>
+        <v>18.97811788445905</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-7.6834619387158</v>
+        <v>-7.602399557999852</v>
       </c>
     </row>
     <row r="44">
@@ -1833,22 +1833,22 @@
         <v>105</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>-62.94888087946065</v>
+        <v>-64.78389758814367</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>-65.62317624511584</v>
+        <v>-67.03134999411152</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-7.20673199916682</v>
+        <v>-8.972130138034352</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>17.57069035196395</v>
+        <v>18.80314480506211</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-7.689662987141945</v>
+        <v>-7.583562261059908</v>
       </c>
     </row>
     <row r="45">
@@ -1864,22 +1864,22 @@
         <v>105</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>-61.40438469545907</v>
+        <v>-66.6308157636644</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>-65.2733120128117</v>
+        <v>-68.97920129867695</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-7.409375493491372</v>
+        <v>-9.493116946378748</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>18.96220639376521</v>
+        <v>19.4461961913975</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-7.683903582921219</v>
+        <v>-7.604693710006218</v>
       </c>
     </row>
     <row r="46">
@@ -1895,22 +1895,22 @@
         <v>105</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>-63.19230418506081</v>
+        <v>-65.89628285272188</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>-66.20473053403269</v>
+        <v>-68.22000597215091</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-7.076692341409451</v>
+        <v>-8.611375335354554</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>17.82094716569889</v>
+        <v>18.56426507063623</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-7.731828475317581</v>
+        <v>-7.629166615852662</v>
       </c>
     </row>
     <row r="47">
@@ -1926,22 +1926,22 @@
         <v>106</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>-63.35721956917848</v>
+        <v>-65.00963844142792</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>-67.67987633666645</v>
+        <v>-69.67403091029809</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-6.095138710100167</v>
+        <v>-7.197022955622635</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>18.1542399736481</v>
+        <v>19.49667685346439</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-7.736444496059964</v>
+        <v>-7.635261428971591</v>
       </c>
     </row>
     <row r="48">
@@ -1957,22 +1957,22 @@
         <v>106</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>-59.55520977055865</v>
+        <v>-62.99555030581424</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>-64.0270493709659</v>
+        <v>-66.57062987226591</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-6.150344192954273</v>
+        <v>-8.879200776248497</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>18.26673082822139</v>
+        <v>20.0426537128981</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-7.644547034859885</v>
+        <v>-7.588373370197944</v>
       </c>
     </row>
     <row r="49">
@@ -1988,22 +1988,22 @@
         <v>106</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>-63.72570167745989</v>
+        <v>-64.17700322708271</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>-68.2600395098287</v>
+        <v>-68.11181589841571</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-7.34224626990441</v>
+        <v>-8.562452293753527</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>19.60760512269934</v>
+        <v>20.09331957559968</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-7.73102102042612</v>
+        <v>-7.596054610513135</v>
       </c>
     </row>
     <row r="50">
@@ -2019,22 +2019,22 @@
         <v>149</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>-55.45246827565062</v>
+        <v>-64.09986954505132</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>-60.55706626460938</v>
+        <v>-67.18721287514228</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-5.766204048843763</v>
+        <v>-8.332220419233321</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>18.55162776451038</v>
+        <v>19.04459008751134</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-7.680825726707853</v>
+        <v>-7.625026338187047</v>
       </c>
     </row>
     <row r="51">
@@ -2050,22 +2050,22 @@
         <v>149</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>-60.8872567611179</v>
+        <v>-63.18961310303583</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>-64.69616904534712</v>
+        <v>-66.48846204107765</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-6.247226210273294</v>
+        <v>-8.486998523432524</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>17.85157328581947</v>
+        <v>19.45240004340732</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-7.795434791316948</v>
+        <v>-7.666552581932987</v>
       </c>
     </row>
     <row r="52">
@@ -2081,22 +2081,22 @@
         <v>149</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>-62.7668789994903</v>
+        <v>-64.64151632648895</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>-64.73279836068136</v>
+        <v>-66.94668297083321</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-7.981150633842973</v>
+        <v>-9.178247113942756</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>17.71071732158186</v>
+        <v>19.1660612354315</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-7.76364732654783</v>
+        <v>-7.682647477144493</v>
       </c>
     </row>
     <row r="53">
@@ -2112,22 +2112,22 @@
         <v>153</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>-62.16006825689269</v>
+        <v>-63.55126595214979</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>-66.85539957943936</v>
+        <v>-67.01531550068339</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-4.879801745837087</v>
+        <v>-6.97887773176843</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>17.26802083775828</v>
+        <v>18.04666218292645</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-7.69288776937452</v>
+        <v>-7.603734902624418</v>
       </c>
     </row>
     <row r="54">
@@ -2143,22 +2143,22 @@
         <v>153</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>-63.32545624788224</v>
+        <v>-66.22217767917377</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>-67.96568699806456</v>
+        <v>-70.43077248758739</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-5.992840976913921</v>
+        <v>-8.12642106200342</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>18.48468744048197</v>
+        <v>19.9940199514648</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-7.851615713385733</v>
+        <v>-7.659004081047743</v>
       </c>
     </row>
     <row r="55">
@@ -2174,22 +2174,22 @@
         <v>153</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>-65.12076076262976</v>
+        <v>-65.63288674488994</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>-69.33634336106626</v>
+        <v>-69.22376862527753</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-10.03393573859443</v>
+        <v>-9.283871444365424</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>21.96725545376254</v>
+        <v>20.48082559560043</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-7.717737116731603</v>
+        <v>-7.606072270847415</v>
       </c>
     </row>
     <row r="56">
@@ -2205,22 +2205,22 @@
         <v>161</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>-64.6850967772248</v>
+        <v>-63.96040883702542</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>-69.13721382001846</v>
+        <v>-67.51683470139947</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-6.378324080191335</v>
+        <v>-8.08585015465485</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>18.60180220230131</v>
+        <v>19.19171880353705</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-7.771361079316294</v>
+        <v>-7.549442784508145</v>
       </c>
     </row>
     <row r="57">
@@ -2236,22 +2236,22 @@
         <v>161</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>-63.05652470329457</v>
+        <v>-64.92406659240606</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>-67.13420568172613</v>
+        <v>-68.45964036484268</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-7.336078162874113</v>
+        <v>-9.329239480590443</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>19.19969582420918</v>
+        <v>20.50222604726058</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-7.785936682903515</v>
+        <v>-7.637412794233508</v>
       </c>
     </row>
     <row r="58">
@@ -2267,22 +2267,22 @@
         <v>161</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>-59.46617083640571</v>
+        <v>-64.29907857863724</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>-63.43835733377851</v>
+        <v>-69.03209850563611</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-7.894189984677216</v>
+        <v>-8.101767218400594</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>19.64945588011586</v>
+        <v>20.48318566601318</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-7.783079398065863</v>
+        <v>-7.64839852061372</v>
       </c>
     </row>
   </sheetData>

--- a/manuscript/Supplementary-Table-3.xlsx
+++ b/manuscript/Supplementary-Table-3.xlsx
@@ -3650,31 +3650,31 @@
         <v>1</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>-60.32</v>
+        <v>-56.26</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>-59.61</v>
+        <v>-55.69</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>-0.7100000000000009</v>
+        <v>-0.5700000000000003</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>-60.92</v>
+        <v>-57.35</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>-59.54</v>
+        <v>-54.75</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>-1.380000000000003</v>
+        <v>-2.600000000000001</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>-60.32</v>
+        <v>-56.26</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>-59.14</v>
+        <v>-55.73</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>-1.18</v>
+        <v>-0.5300000000000011</v>
       </c>
     </row>
     <row r="33">
@@ -3692,31 +3692,31 @@
         <v>2</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-49.65</v>
+        <v>-46.34</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-51.04</v>
+        <v>-50.58</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>1.390000000000001</v>
+        <v>4.239999999999995</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>-49.33</v>
+        <v>-47.94</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>-51.93</v>
+        <v>-51.71</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>2.600000000000001</v>
+        <v>3.770000000000003</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>-49.67</v>
+        <v>-45.14</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>-51.07</v>
+        <v>-50.57</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>1.399999999999999</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="34">
@@ -3734,31 +3734,31 @@
         <v>3</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>-47.69</v>
+        <v>-52.9</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>-53.01</v>
+        <v>-52.19</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>5.32</v>
+        <v>-0.7100000000000009</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>-48.62</v>
+        <v>-53.45</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>-55.08</v>
+        <v>-52.8</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>6.460000000000001</v>
+        <v>-0.6500000000000057</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>-47.94</v>
+        <v>-52.91</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>-53.01</v>
+        <v>-52.18</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>5.07</v>
+        <v>-0.7299999999999969</v>
       </c>
     </row>
     <row r="35">

--- a/manuscript/Supplementary-Table-3.xlsx
+++ b/manuscript/Supplementary-Table-3.xlsx
@@ -3692,31 +3692,31 @@
         <v>2</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-46.34</v>
+        <v>-52.36</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>-50.58</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>4.239999999999995</v>
+        <v>-1.780000000000001</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>-47.94</v>
+        <v>-53.86</v>
       </c>
       <c r="H33" s="7" t="n">
         <v>-51.71</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>3.770000000000003</v>
+        <v>-2.149999999999999</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>-45.14</v>
+        <v>-52.36</v>
       </c>
       <c r="K33" s="7" t="n">
         <v>-50.57</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>5.43</v>
+        <v>-1.789999999999999</v>
       </c>
     </row>
     <row r="34">
